--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
         <v>3.25</v>
@@ -966,7 +966,7 @@
         <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H6" t="n">
         <v>1.91</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J6" t="n">
         <v>2.98</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>2.52</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I8" t="n">
         <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
         <v>3.75</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I13" t="n">
         <v>2.64</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -3676,13 +3676,13 @@
         <v>6.4</v>
       </c>
       <c r="I17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="G22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.75</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="G24" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="H24" t="n">
-        <v>1.96</v>
+        <v>5.9</v>
       </c>
       <c r="I24" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G25" t="n">
         <v>3.85</v>
@@ -5228,7 +5228,7 @@
         <v>2.26</v>
       </c>
       <c r="I25" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>3.1</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G3" t="n">
         <v>2.72</v>
@@ -960,13 +960,13 @@
         <v>3.25</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I6" t="n">
         <v>2.48</v>
       </c>
       <c r="J6" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.52</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
         <v>2.88</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
         <v>2.04</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H12" t="n">
         <v>2.74</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I13" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
         <v>3.35</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
         <v>2.08</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3676,13 +3676,13 @@
         <v>6.4</v>
       </c>
       <c r="I17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
         <v>4.3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G18" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H18" t="n">
         <v>3.3</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q18" t="n">
         <v>2.28</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>2.94</v>
       </c>
       <c r="H22" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I22" t="n">
         <v>3.05</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>1.7</v>
       </c>
       <c r="G24" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="H24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
         <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K24" t="n">
         <v>3.9</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G25" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H25" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="I25" t="n">
         <v>2.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>2.56</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
         <v>5.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I6" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>2.88</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>3.45</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H12" t="n">
         <v>2.74</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
         <v>2.58</v>
       </c>
       <c r="I13" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
         <v>3.35</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
         <v>2.08</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H20" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
@@ -4282,7 +4282,7 @@
         <v>1.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
         <v>1.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
         <v>3.05</v>
       </c>
       <c r="J22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
         <v>3.7</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
         <v>1.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>3.95</v>
       </c>
       <c r="H25" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I25" t="n">
         <v>2.5</v>
@@ -5234,7 +5234,7 @@
         <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH25"/>
+  <dimension ref="A1:BH26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.01</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
         <v>3.45</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>NK Slovenska Bistrica</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Jesenice</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="G6" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1.93</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.16</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>85</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>1.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Connahs Quay</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barry Town Utd</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.62</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.08</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="I7" t="n">
-        <v>6.2</v>
+        <v>2.16</v>
       </c>
       <c r="J7" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11:15:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Leonesa</t>
+          <t>Connahs Quay</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Andorra CF</t>
+          <t>Barry Town Utd</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.52</v>
+        <v>1.62</v>
       </c>
       <c r="G8" t="n">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>2.78</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>7.8</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Leonesa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Andorra CF</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
@@ -2300,12 +2300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Forli</t>
+          <t>Pesaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>US Pianese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Forli</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>US Pianese</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="H13" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>2.64</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AZ Picerno ASD</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ASD Pineto Calcio</t>
+          <t>AZ Picerno ASD</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>ASD Pineto Calcio</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7</v>
+        <v>1.63</v>
       </c>
       <c r="H19" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.68</v>
+        <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>1.56</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="G20" t="n">
-        <v>1.92</v>
+        <v>2.68</v>
       </c>
       <c r="H20" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,31 +4434,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.96</v>
+        <v>1.56</v>
       </c>
       <c r="G21" t="n">
-        <v>2.74</v>
+        <v>1.91</v>
       </c>
       <c r="H21" t="n">
-        <v>3.15</v>
+        <v>2.14</v>
       </c>
       <c r="I21" t="n">
-        <v>5.4</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>5.9</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,36 +4623,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.62</v>
+        <v>1.96</v>
       </c>
       <c r="G22" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="I22" t="n">
-        <v>3.05</v>
+        <v>5.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,201 +5188,395 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 07:32:45</t>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Racing Club (Uru)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:47:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Deportivo Pasto</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Atletico Nacional Medellin</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="F26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G26" t="n">
         <v>3.95</v>
       </c>
-      <c r="H25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="H26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J26" t="n">
         <v>3.15</v>
       </c>
-      <c r="K25" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="K26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>2026-03-27 07:32:45</t>
+      <c r="Q26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:47:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH26"/>
+  <dimension ref="A1:BH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,118 +757,118 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="G2" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
         <v>1.03</v>
@@ -877,10 +877,10 @@
         <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
         <v>1.03</v>
@@ -889,22 +889,22 @@
         <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
         <v>1.03</v>
@@ -913,14 +913,14 @@
         <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H3" t="n">
         <v>3.3</v>
@@ -975,13 +975,13 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q3" t="n">
         <v>2.72</v>
@@ -1002,7 +1002,7 @@
         <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X3" t="n">
         <v>8.4</v>
@@ -1104,7 +1104,7 @@
         <v>14</v>
       </c>
       <c r="BE3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BF3" t="n">
         <v>34</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.01</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.01</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K6" t="n">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2</v>
+        <v>2.34</v>
       </c>
       <c r="T6" t="n">
         <v>1.83</v>
@@ -1581,10 +1581,10 @@
         <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>2.8</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.72</v>
+        <v>5.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT6" t="n">
         <v>5.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.56</v>
+        <v>3.95</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.63</v>
+        <v>4.1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.72</v>
+        <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.71</v>
+        <v>4.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.73</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.76</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.57</v>
+        <v>3.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -1739,22 +1739,22 @@
         <v>2.16</v>
       </c>
       <c r="J7" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="K7" t="n">
         <v>5.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
         <v>1.25</v>
@@ -1763,134 +1763,134 @@
         <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -1939,16 +1939,16 @@
         <v>7.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
         <v>1.92</v>
@@ -1957,134 +1957,134 @@
         <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G9" t="n">
         <v>2.68</v>
@@ -2133,16 +2133,16 @@
         <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P9" t="n">
         <v>1.87</v>
@@ -2151,141 +2151,141 @@
         <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,17 +2295,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pacos Ferreira</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Forli</t>
+          <t>Pesaro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>US Pianese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Forli</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>US Pianese</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H14" t="n">
         <v>3.05</v>
       </c>
-      <c r="G14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.5</v>
-      </c>
       <c r="I14" t="n">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.93</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>2.54</v>
       </c>
       <c r="I15" t="n">
-        <v>5.9</v>
+        <v>2.66</v>
       </c>
       <c r="J15" t="n">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.37</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AZ Picerno ASD</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3658,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>AZ Picerno ASD</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -3852,12 +3852,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ASD Pineto Calcio</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>ASD Pineto Calcio</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.22</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,31 +4240,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="G20" t="n">
-        <v>2.68</v>
+        <v>1.65</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
-        <v>2.74</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.44</v>
+        <v>2.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,36 +4429,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1.91</v>
+        <v>2.68</v>
       </c>
       <c r="H21" t="n">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,31 +4628,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.96</v>
+        <v>1.56</v>
       </c>
       <c r="G22" t="n">
-        <v>2.74</v>
+        <v>1.91</v>
       </c>
       <c r="H22" t="n">
-        <v>3.15</v>
+        <v>2.14</v>
       </c>
       <c r="I22" t="n">
-        <v>5.4</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="K22" t="n">
-        <v>5.9</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="G23" t="n">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="H23" t="n">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="I23" t="n">
-        <v>3.05</v>
+        <v>5.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="K23" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,36 +5205,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,36 +5399,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="G26" t="n">
-        <v>3.95</v>
+        <v>1.83</v>
       </c>
       <c r="H26" t="n">
-        <v>2.22</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>2.62</v>
+        <v>8</v>
       </c>
       <c r="J26" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="Q26" t="n">
         <v>2.1</v>
@@ -5576,7 +5576,201 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -760,7 +760,7 @@
         <v>1.57</v>
       </c>
       <c r="G2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H2" t="n">
         <v>6.2</v>
@@ -769,7 +769,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
         <v>5</v>
@@ -808,7 +808,7 @@
         <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X2" t="n">
         <v>17.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H3" t="n">
         <v>3.3</v>
@@ -963,7 +963,7 @@
         <v>3.45</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
         <v>3.1</v>
@@ -981,7 +981,7 @@
         <v>1.59</v>
       </c>
       <c r="P3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
         <v>2.72</v>
@@ -1002,7 +1002,7 @@
         <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
         <v>8.4</v>
@@ -1014,7 +1014,7 @@
         <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="n">
         <v>7.8</v>
@@ -1056,7 +1056,7 @@
         <v>44</v>
       </c>
       <c r="AO3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP3" t="n">
         <v>7.6</v>
@@ -1077,7 +1077,7 @@
         <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
         <v>13</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H5" t="n">
         <v>4.2</v>
@@ -1390,7 +1390,7 @@
         <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J6" t="n">
         <v>4.1</v>
@@ -1575,7 +1575,7 @@
         <v>2.34</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
         <v>2</v>
@@ -1644,59 +1644,59 @@
         <v>5.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
         <v>5.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY6" t="n">
         <v>4.1</v>
       </c>
       <c r="AZ6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA6" t="n">
         <v>5</v>
       </c>
-      <c r="BA6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BB6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC6" t="n">
         <v>4.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -1733,16 +1733,16 @@
         <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="I7" t="n">
         <v>2.16</v>
       </c>
       <c r="J7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="O7" t="n">
         <v>1.37</v>
@@ -1760,7 +1760,7 @@
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
         <v>1.2</v>
@@ -1769,10 +1769,10 @@
         <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.02</v>
       </c>
       <c r="V7" t="n">
         <v>1.86</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G9" t="n">
         <v>2.68</v>
@@ -2124,7 +2124,7 @@
         <v>2.88</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J9" t="n">
         <v>3.45</v>
@@ -2139,10 +2139,10 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
         <v>1.87</v>
@@ -2175,7 +2175,7 @@
         <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
         <v>50</v>
@@ -2202,10 +2202,10 @@
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK9" t="n">
         <v>30</v>
@@ -2244,7 +2244,7 @@
         <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
@@ -2256,29 +2256,29 @@
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
         <v>32</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BD9" t="n">
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF9" t="n">
         <v>19.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -3103,16 +3103,16 @@
         <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P14" t="n">
         <v>1.56</v>
@@ -3121,134 +3121,134 @@
         <v>2.42</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -3279,34 +3279,34 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
         <v>3.25</v>
       </c>
       <c r="H15" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I15" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
         <v>3.45</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P15" t="n">
         <v>1.84</v>
@@ -3315,134 +3315,134 @@
         <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
         <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G21" t="n">
         <v>2.68</v>
@@ -4458,7 +4458,7 @@
         <v>2.76</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G26" t="n">
         <v>1.83</v>
@@ -5428,7 +5428,7 @@
         <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 12:02:41</t>
+          <t>2026-03-27 14:19:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
         <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
         <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -790,16 +790,16 @@
         <v>1.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="U2" t="n">
         <v>1.88</v>
@@ -808,7 +808,7 @@
         <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X2" t="n">
         <v>17.5</v>
@@ -820,7 +820,7 @@
         <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB2" t="n">
         <v>8.199999999999999</v>
@@ -829,10 +829,10 @@
         <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
         <v>9.4</v>
@@ -847,16 +847,16 @@
         <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK2" t="n">
         <v>18</v>
       </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN2" t="n">
         <v>11</v>
@@ -877,7 +877,7 @@
         <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU2" t="n">
         <v>8.199999999999999</v>
@@ -913,14 +913,14 @@
         <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2" t="n">
         <v>110</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>3.45</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>3.1</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
         <v>1.63</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="G5" t="n">
         <v>2.02</v>
@@ -1354,7 +1354,7 @@
         <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>1.39</v>
       </c>
       <c r="G6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="I6" t="n">
         <v>11.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,25 +1557,25 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
         <v>2</v>
@@ -1584,7 +1584,7 @@
         <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1635,68 +1635,68 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.9</v>
+        <v>1.38</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>1.38</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.1</v>
+        <v>1.37</v>
       </c>
       <c r="AX6" t="n">
         <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="BA6" t="n">
-        <v>5</v>
+        <v>1.37</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.45</v>
+        <v>1.37</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>1.37</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="I7" t="n">
         <v>2.16</v>
@@ -1742,7 +1742,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1769,10 +1769,10 @@
         <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.02</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
         <v>1.86</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G9" t="n">
         <v>2.68</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2536,13 +2536,13 @@
         <v>1.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
         <v>1.43</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="P12" t="n">
         <v>1.43</v>
@@ -2805,52 +2805,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2999,52 +2999,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>3.05</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
         <v>2.98</v>
@@ -3127,13 +3127,13 @@
         <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
         <v>1.62</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>3.45</v>
       </c>
       <c r="L15" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -3306,7 +3306,7 @@
         <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
         <v>1.84</v>
@@ -3321,10 +3321,10 @@
         <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
         <v>1.62</v>
@@ -3384,7 +3384,7 @@
         <v>38</v>
       </c>
       <c r="AO15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP15" t="n">
         <v>11.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H20" t="n">
         <v>6</v>
@@ -4261,22 +4261,22 @@
         <v>6.8</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K20" t="n">
         <v>4.7</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P20" t="n">
         <v>2.32</v>
@@ -4285,134 +4285,134 @@
         <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
         <v>2.68</v>
@@ -4458,19 +4458,19 @@
         <v>2.76</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P21" t="n">
         <v>1.44</v>
@@ -4479,134 +4479,134 @@
         <v>2.28</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
         <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
         <v>950</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H2" t="n">
         <v>6.2</v>
@@ -772,7 +772,7 @@
         <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>1.32</v>
@@ -805,13 +805,13 @@
         <v>1.88</v>
       </c>
       <c r="V2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W2" t="n">
         <v>2.44</v>
       </c>
       <c r="X2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
         <v>22</v>
@@ -829,7 +829,7 @@
         <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
         <v>120</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -1145,55 +1145,55 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H4" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="I4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S4" t="n">
         <v>3.9</v>
       </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.02</v>
-      </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
         <v>1.53</v>
@@ -1253,37 +1253,37 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
         <v>1.03</v>
@@ -1301,14 +1301,14 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H5" t="n">
         <v>4.2</v>
@@ -1354,7 +1354,7 @@
         <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1375,10 +1375,10 @@
         <v>1.89</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>2.54</v>
+        <v>1.9</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1390,7 +1390,7 @@
         <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
         <v>2.1</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G9" t="n">
         <v>2.68</v>
@@ -2127,37 +2127,37 @@
         <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
         <v>1.94</v>
@@ -2178,7 +2178,7 @@
         <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB9" t="n">
         <v>10.5</v>
@@ -2196,16 +2196,16 @@
         <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
         <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AK9" t="n">
         <v>30</v>
@@ -2223,28 +2223,28 @@
         <v>34</v>
       </c>
       <c r="AP9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AT9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
         <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
@@ -2253,32 +2253,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
         <v>32</v>
       </c>
       <c r="BC9" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BD9" t="n">
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF9" t="n">
         <v>19.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I11" t="n">
         <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2533,16 +2533,16 @@
         <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2554,7 +2554,7 @@
         <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2730,13 +2730,13 @@
         <v>1.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2745,11 +2745,11 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.4</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X12" t="n">
         <v>1000</v>
       </c>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H13" t="n">
         <v>3.15</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="K13" t="n">
         <v>5.7</v>
@@ -2924,13 +2924,13 @@
         <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -2939,10 +2939,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -3091,10 +3091,10 @@
         <v>2.6</v>
       </c>
       <c r="H14" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J14" t="n">
         <v>2.98</v>
@@ -3106,13 +3106,13 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>1.56</v>
+        <v>2.64</v>
       </c>
       <c r="O14" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="P14" t="n">
         <v>1.56</v>
@@ -3121,134 +3121,134 @@
         <v>2.42</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
         <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V14" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
         <v>1.62</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG14" t="n">
         <v>15</v>
       </c>
-      <c r="Z14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AH14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV14" t="n">
         <v>11</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AW14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
+      <c r="AY14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG14" t="n">
         <v>50</v>
       </c>
-      <c r="AK14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
         <v>3.25</v>
@@ -3288,13 +3288,13 @@
         <v>2.56</v>
       </c>
       <c r="I15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3375,7 +3375,7 @@
         <v>40</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G17" t="n">
         <v>3.3</v>
@@ -3676,13 +3676,13 @@
         <v>2.84</v>
       </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3706,7 +3706,7 @@
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3715,10 +3715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -3864,16 +3864,16 @@
         <v>2.68</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H18" t="n">
         <v>2.36</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J18" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="K18" t="n">
         <v>5</v>
@@ -3900,7 +3900,7 @@
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G19" t="n">
         <v>3.05</v>
@@ -4070,7 +4070,7 @@
         <v>2.78</v>
       </c>
       <c r="K19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4094,7 +4094,7 @@
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -4249,34 +4249,34 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G20" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
         <v>4.7</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.32</v>
-      </c>
       <c r="O20" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
         <v>2.32</v>
@@ -4285,46 +4285,46 @@
         <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W20" t="n">
         <v>2.62</v>
       </c>
-      <c r="T20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.52</v>
-      </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA20" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="n">
         <v>11</v>
@@ -4333,10 +4333,10 @@
         <v>10</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ20" t="n">
         <v>16</v>
@@ -4348,40 +4348,40 @@
         <v>30</v>
       </c>
       <c r="AM20" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN20" t="n">
         <v>7.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AR20" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AT20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV20" t="n">
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY20" t="n">
         <v>9</v>
@@ -4390,29 +4390,29 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="BB20" t="n">
         <v>13.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
         <v>26</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF20" t="n">
         <v>6.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
         <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y21" t="n">
         <v>1000</v>
@@ -4551,52 +4551,52 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -4655,152 +4655,152 @@
         <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
         <v>1.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -4849,16 +4849,16 @@
         <v>5.9</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P23" t="n">
         <v>1.45</v>
@@ -4867,134 +4867,134 @@
         <v>2.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -5028,31 +5028,31 @@
         <v>2.6</v>
       </c>
       <c r="G24" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H24" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I24" t="n">
         <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K24" t="n">
         <v>3.7</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
         <v>1.8</v>
@@ -5061,134 +5061,134 @@
         <v>2.04</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="G26" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q26" t="n">
         <v>2.14</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>2.22</v>
       </c>
       <c r="I27" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="J27" t="n">
         <v>3.15</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 16:37:04</t>
+          <t>2026-03-27 18:53:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -975,13 +975,13 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="O3" t="n">
         <v>1.59</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q3" t="n">
         <v>2.72</v>
@@ -993,7 +993,7 @@
         <v>5.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
         <v>1.76</v>
@@ -1008,7 +1008,7 @@
         <v>8.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z3" t="n">
         <v>21</v>
@@ -1017,7 +1017,7 @@
         <v>70</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3" t="n">
         <v>7.2</v>
@@ -1050,7 +1050,7 @@
         <v>70</v>
       </c>
       <c r="AM3" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
         <v>44</v>
@@ -1068,7 +1068,7 @@
         <v>18.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1080,7 +1080,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX3" t="n">
         <v>13.5</v>
@@ -1092,29 +1092,29 @@
         <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
         <v>34</v>
       </c>
       <c r="BG3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G4" t="n">
         <v>2.88</v>
@@ -1154,7 +1154,7 @@
         <v>2.84</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
@@ -1175,13 +1175,13 @@
         <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
         <v>3.9</v>
@@ -1190,10 +1190,10 @@
         <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
         <v>1.53</v>
@@ -1265,7 +1265,7 @@
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
         <v>5.9</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
         <v>1.89</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
         <v>1.53</v>
@@ -1548,7 +1548,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,7 +1557,7 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
         <v>1.22</v>
@@ -1575,16 +1575,16 @@
         <v>2.54</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="V6" t="n">
         <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AT6" t="n">
         <v>4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AX6" t="n">
         <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BC6" t="n">
         <v>4.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I7" t="n">
         <v>2.16</v>
@@ -1742,7 +1742,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1769,7 +1769,7 @@
         <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
         <v>2.88</v>
@@ -2127,13 +2127,13 @@
         <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
         <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2163,10 +2163,10 @@
         <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X9" t="n">
         <v>14</v>
@@ -2208,7 +2208,7 @@
         <v>48</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
         <v>44</v>
@@ -2217,10 +2217,10 @@
         <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP9" t="n">
         <v>11.5</v>
@@ -2244,7 +2244,7 @@
         <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
@@ -2256,29 +2256,29 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9" t="n">
         <v>32</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD9" t="n">
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF9" t="n">
         <v>19.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
         <v>2.08</v>
@@ -2324,7 +2324,7 @@
         <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="O11" t="n">
         <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" t="n">
         <v>2.08</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -2721,13 +2721,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
         <v>1.49</v>
       </c>
       <c r="P12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q12" t="n">
         <v>2.32</v>
@@ -2736,7 +2736,7 @@
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G15" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H15" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I15" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,10 +3303,10 @@
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P15" t="n">
         <v>1.84</v>
@@ -3315,7 +3315,7 @@
         <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
         <v>3.6</v>
@@ -3324,28 +3324,28 @@
         <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
         <v>13.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
         <v>16.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
         <v>7.8</v>
@@ -3372,25 +3372,25 @@
         <v>55</v>
       </c>
       <c r="AK15" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP15" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR15" t="n">
         <v>14</v>
@@ -3423,26 +3423,26 @@
         <v>36</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC15" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF15" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BG15" t="n">
         <v>21</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="G17" t="n">
         <v>3.3</v>
       </c>
       <c r="H17" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="J17" t="n">
         <v>2.56</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3715,7 +3715,7 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
         <v>1.44</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>2.68</v>
       </c>
       <c r="G18" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="H18" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="I18" t="n">
         <v>3.35</v>
@@ -3876,7 +3876,7 @@
         <v>2.74</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3888,7 +3888,7 @@
         <v>1.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.52</v>
+        <v>1.02</v>
       </c>
       <c r="P18" t="n">
         <v>1.39</v>
@@ -3912,7 +3912,7 @@
         <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>2.16</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
         <v>2.62</v>
@@ -4082,7 +4082,7 @@
         <v>1.41</v>
       </c>
       <c r="O19" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="P19" t="n">
         <v>1.4</v>
@@ -4106,7 +4106,7 @@
         <v>1.31</v>
       </c>
       <c r="W19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>1.57</v>
       </c>
       <c r="G20" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H20" t="n">
         <v>6.2</v>
@@ -4264,7 +4264,7 @@
         <v>4.4</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4273,52 +4273,52 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="T20" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U20" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
         <v>1.16</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA20" t="n">
         <v>170</v>
       </c>
       <c r="AB20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC20" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>10</v>
       </c>
       <c r="AD20" t="n">
         <v>25</v>
@@ -4333,10 +4333,10 @@
         <v>10</v>
       </c>
       <c r="AH20" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
         <v>16</v>
@@ -4345,43 +4345,43 @@
         <v>16</v>
       </c>
       <c r="AL20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM20" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
         <v>85</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS20" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>12</v>
       </c>
       <c r="AT20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV20" t="n">
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY20" t="n">
         <v>9</v>
@@ -4390,7 +4390,7 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
         <v>13.5</v>
@@ -4402,17 +4402,17 @@
         <v>26</v>
       </c>
       <c r="BE20" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.12</v>
       </c>
       <c r="G21" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H21" t="n">
         <v>3.3</v>
@@ -4470,7 +4470,7 @@
         <v>1.44</v>
       </c>
       <c r="O21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P21" t="n">
         <v>1.44</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="G22" t="n">
         <v>1.91</v>
       </c>
       <c r="H22" t="n">
-        <v>2.14</v>
+        <v>4.7</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
         <v>950</v>
@@ -4661,22 +4661,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="O22" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4745,52 +4745,52 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
         <v>1.01</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
         <v>1.45</v>
       </c>
       <c r="O23" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="P23" t="n">
         <v>1.45</v>
@@ -4939,52 +4939,52 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
         <v>1.01</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>2.96</v>
       </c>
       <c r="H24" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I24" t="n">
         <v>3.05</v>
@@ -5040,19 +5040,19 @@
         <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P24" t="n">
         <v>1.8</v>
@@ -5061,16 +5061,16 @@
         <v>2.04</v>
       </c>
       <c r="R24" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U24" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="V24" t="n">
         <v>1.48</v>
@@ -5079,116 +5079,116 @@
         <v>1.51</v>
       </c>
       <c r="X24" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE24" t="n">
         <v>40</v>
       </c>
       <c r="AF24" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG24" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI24" t="n">
         <v>55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK24" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.86</v>
+        <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.76</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AS24" t="n">
-        <v>28</v>
+        <v>7.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.76</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.54</v>
+        <v>6.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.86</v>
+        <v>10.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY24" t="n">
-        <v>2.86</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>29</v>
+        <v>7.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="BD24" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.5</v>
+        <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
@@ -5237,159 +5237,159 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P25" t="n">
         <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,31 +5404,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="G26" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="H26" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="J26" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,201 +5576,395 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 18:53:15</t>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Racing Club (Uru)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-27 21:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Deportivo Pasto</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Atletico Nacional Medellin</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F28" t="n">
         <v>3.35</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G28" t="n">
         <v>3.95</v>
       </c>
-      <c r="H27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="H28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BB28" t="n">
         <v>3.15</v>
       </c>
-      <c r="K27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-03-27 18:53:15</t>
+      <c r="BC28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-27 21:09:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -811,7 +811,7 @@
         <v>2.44</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
         <v>22</v>
@@ -823,10 +823,10 @@
         <v>240</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
         <v>28</v>
@@ -835,10 +835,10 @@
         <v>120</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>24</v>
@@ -847,10 +847,10 @@
         <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AK2" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AL2" t="n">
         <v>42</v>
@@ -868,13 +868,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="AT2" t="n">
         <v>7</v>
@@ -883,44 +883,44 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>2.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I3" t="n">
         <v>3.45</v>
@@ -984,7 +984,7 @@
         <v>1.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1095,7 +1095,7 @@
         <v>14.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BC3" t="n">
         <v>12.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.39</v>
@@ -1187,10 +1187,10 @@
         <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
         <v>1.46</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -2121,13 +2121,13 @@
         <v>2.7</v>
       </c>
       <c r="H9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I9" t="n">
         <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
         <v>3.6</v>
@@ -2142,19 +2142,19 @@
         <v>3.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
         <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R9" t="n">
         <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
         <v>1.85</v>
@@ -2190,7 +2190,7 @@
         <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF9" t="n">
         <v>17</v>
@@ -2268,7 +2268,7 @@
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9" t="n">
         <v>19.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
         <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>1.49</v>
+        <v>1.02</v>
       </c>
       <c r="P12" t="n">
         <v>1.44</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>3.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
         <v>2.98</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
         <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X15" t="n">
         <v>13.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>2.44</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H17" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="I17" t="n">
         <v>3.75</v>
       </c>
       <c r="J17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,22 +3691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
         <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="G18" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H18" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,22 +3885,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.4</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.39</v>
-      </c>
       <c r="Q18" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3912,7 +3912,7 @@
         <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -4061,13 +4061,13 @@
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J19" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="K19" t="n">
         <v>6.4</v>
@@ -4079,22 +4079,22 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>1.57</v>
       </c>
       <c r="G20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H20" t="n">
         <v>6.2</v>
@@ -4264,7 +4264,7 @@
         <v>4.4</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4276,25 +4276,25 @@
         <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T20" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V20" t="n">
         <v>1.16</v>
@@ -4306,7 +4306,7 @@
         <v>20</v>
       </c>
       <c r="Y20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z20" t="n">
         <v>55</v>
@@ -4324,7 +4324,7 @@
         <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF20" t="n">
         <v>11</v>
@@ -4333,10 +4333,10 @@
         <v>10</v>
       </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ20" t="n">
         <v>16</v>
@@ -4354,10 +4354,10 @@
         <v>8</v>
       </c>
       <c r="AO20" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>21</v>
@@ -4366,19 +4366,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AV20" t="n">
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX20" t="n">
         <v>9.199999999999999</v>
@@ -4390,7 +4390,7 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB20" t="n">
         <v>13.5</v>
@@ -4408,11 +4408,11 @@
         <v>6.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -4485,10 +4485,10 @@
         <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V21" t="n">
         <v>1.24</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -4643,10 +4643,10 @@
         <v>1.91</v>
       </c>
       <c r="H22" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I22" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
         <v>3.35</v>
@@ -4661,10 +4661,10 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.87</v>
+        <v>2.96</v>
       </c>
       <c r="O22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P22" t="n">
         <v>1.73</v>
@@ -4673,16 +4673,16 @@
         <v>1.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V22" t="n">
         <v>1.14</v>
@@ -4691,10 +4691,10 @@
         <v>2.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4703,10 +4703,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4715,22 +4715,22 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
         <v>2.12</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
         <v>4.4</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -5607,118 +5607,118 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G27" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H27" t="n">
         <v>6.6</v>
       </c>
       <c r="I27" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P27" t="n">
         <v>1.68</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V27" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y27" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AD27" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF27" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG27" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ27" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR27" t="n">
         <v>1.03</v>
@@ -5727,50 +5727,50 @@
         <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW27" t="n">
         <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA27" t="n">
         <v>1.03</v>
       </c>
       <c r="BB27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF27" t="n">
         <v>10</v>
       </c>
-      <c r="BC27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>160</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>
@@ -5822,13 +5822,13 @@
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>1.79</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
         <v>1.76</v>
@@ -5837,22 +5837,22 @@
         <v>2.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V28" t="n">
         <v>1.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X28" t="n">
         <v>14.5</v>
@@ -5861,110 +5861,110 @@
         <v>10.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA28" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AB28" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF28" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AG28" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK28" t="n">
         <v>60</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.58</v>
+        <v>5.2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.42</v>
+        <v>4.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>20</v>
+        <v>2.52</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="AU28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA28" t="n">
         <v>2.34</v>
       </c>
-      <c r="AV28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.98</v>
-      </c>
       <c r="BB28" t="n">
-        <v>3.15</v>
+        <v>2.04</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="BE28" t="n">
-        <v>3.15</v>
+        <v>2.06</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>3.15</v>
+        <v>16.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-27 21:09:21</t>
+          <t>2026-03-27 23:24:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH28"/>
+  <dimension ref="A1:BH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,13 +760,13 @@
         <v>1.56</v>
       </c>
       <c r="G2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H2" t="n">
         <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>3.75</v>
@@ -775,7 +775,7 @@
         <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -820,7 +820,7 @@
         <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
@@ -862,34 +862,34 @@
         <v>11</v>
       </c>
       <c r="AO2" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="AR2" t="n">
         <v>2.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AT2" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="AU2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.92</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AY2" t="n">
         <v>4.9</v>
@@ -898,7 +898,7 @@
         <v>3.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BB2" t="n">
         <v>5.8</v>
@@ -907,20 +907,20 @@
         <v>6</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.94</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
         <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -972,10 +972,10 @@
         <v>1.56</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O3" t="n">
         <v>1.59</v>
@@ -984,13 +984,13 @@
         <v>1.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T3" t="n">
         <v>2.18</v>
@@ -1005,7 +1005,7 @@
         <v>1.6</v>
       </c>
       <c r="X3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
         <v>9</v>
@@ -1068,7 +1068,7 @@
         <v>18.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1080,7 +1080,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>13.5</v>
+        <v>46</v>
       </c>
       <c r="AX3" t="n">
         <v>13.5</v>
@@ -1089,32 +1089,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
         <v>34</v>
       </c>
       <c r="BC3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF3" t="n">
         <v>34</v>
       </c>
       <c r="BG3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="G4" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
@@ -1166,7 +1166,7 @@
         <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
         <v>3.2</v>
@@ -1187,16 +1187,16 @@
         <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1256,34 +1256,34 @@
         <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
         <v>1.03</v>
@@ -1301,14 +1301,14 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BG4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -1339,118 +1339,118 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G5" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.2</v>
       </c>
-      <c r="I5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.8</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
         <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.89</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
         <v>1.03</v>
@@ -1459,34 +1459,34 @@
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
         <v>1.03</v>
@@ -1495,14 +1495,14 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H6" t="n">
         <v>6.6</v>
@@ -1551,13 +1551,13 @@
         <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>1.22</v>
@@ -1584,7 +1584,7 @@
         <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1650,7 +1650,7 @@
         <v>1.37</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AT6" t="n">
         <v>4</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -1769,10 +1769,10 @@
         <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
         <v>1.86</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.62</v>
+        <v>1.02</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>2.78</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>7.8</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,22 +1945,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I9" t="n">
         <v>3.1</v>
@@ -2130,7 +2130,7 @@
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,70 +2139,70 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
         <v>1.47</v>
       </c>
       <c r="W9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA9" t="n">
         <v>55</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
         <v>38</v>
       </c>
       <c r="AF9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
         <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
         <v>48</v>
@@ -2211,7 +2211,7 @@
         <v>32</v>
       </c>
       <c r="AL9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM9" t="n">
         <v>120</v>
@@ -2235,7 +2235,7 @@
         <v>42</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
@@ -2244,41 +2244,41 @@
         <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BB9" t="n">
         <v>32</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BD9" t="n">
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF9" t="n">
         <v>19.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -2333,16 +2333,16 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O10" t="n">
         <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R10" t="n">
         <v>1.29</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -2503,145 +2503,145 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="H11" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S11" t="n">
         <v>4.3</v>
       </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.08</v>
-      </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
         <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
         <v>1.03</v>
@@ -2659,14 +2659,14 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>2.48</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>2.86</v>
@@ -2724,7 +2724,7 @@
         <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="P12" t="n">
         <v>1.44</v>
@@ -2745,7 +2745,7 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
         <v>1.4</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -2891,118 +2891,118 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="G13" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>1.54</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR13" t="n">
         <v>1.03</v>
@@ -3011,25 +3011,25 @@
         <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
         <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA13" t="n">
         <v>1.03</v>
@@ -3047,14 +3047,14 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H14" t="n">
         <v>3.2</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>2.98</v>
@@ -3112,46 +3112,46 @@
         <v>2.64</v>
       </c>
       <c r="O14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R14" t="n">
         <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA14" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC14" t="n">
         <v>8.800000000000001</v>
@@ -3160,13 +3160,13 @@
         <v>19</v>
       </c>
       <c r="AE14" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF14" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
         <v>27</v>
@@ -3187,22 +3187,22 @@
         <v>210</v>
       </c>
       <c r="AN14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO14" t="n">
         <v>90</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ14" t="n">
         <v>7.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
         <v>5.9</v>
@@ -3214,7 +3214,7 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3223,32 +3223,32 @@
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>3.15</v>
@@ -3300,10 +3300,10 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
         <v>1.35</v>
@@ -3315,7 +3315,7 @@
         <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
         <v>3.6</v>
@@ -3324,7 +3324,7 @@
         <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
         <v>1.6</v>
@@ -3363,7 +3363,7 @@
         <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI15" t="n">
         <v>44</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="H16" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="I16" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G17" t="n">
         <v>3.25</v>
@@ -3682,7 +3682,7 @@
         <v>2.58</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -4252,10 +4252,10 @@
         <v>1.57</v>
       </c>
       <c r="G20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I20" t="n">
         <v>7.2</v>
@@ -4276,19 +4276,19 @@
         <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
         <v>1.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T20" t="n">
         <v>1.8</v>
@@ -4327,7 +4327,7 @@
         <v>90</v>
       </c>
       <c r="AF20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG20" t="n">
         <v>10</v>
@@ -4354,7 +4354,7 @@
         <v>8</v>
       </c>
       <c r="AO20" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP20" t="n">
         <v>14.5</v>
@@ -4363,13 +4363,13 @@
         <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU20" t="n">
         <v>9</v>
@@ -4378,7 +4378,7 @@
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX20" t="n">
         <v>9.199999999999999</v>
@@ -4390,7 +4390,7 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB20" t="n">
         <v>13.5</v>
@@ -4402,17 +4402,17 @@
         <v>26</v>
       </c>
       <c r="BE20" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF20" t="n">
         <v>6.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>10.5</v>
+        <v>65</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
         <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
         <v>1.64</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -4640,16 +4640,16 @@
         <v>1.64</v>
       </c>
       <c r="G22" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="H22" t="n">
-        <v>4.9</v>
+        <v>1.09</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="K22" t="n">
         <v>950</v>
@@ -4658,7 +4658,7 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
         <v>2.96</v>
@@ -4667,7 +4667,7 @@
         <v>1.32</v>
       </c>
       <c r="P22" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
         <v>1.8</v>
@@ -4676,7 +4676,7 @@
         <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="T22" t="n">
         <v>1.78</v>
@@ -4691,55 +4691,55 @@
         <v>2.08</v>
       </c>
       <c r="X22" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Y22" t="n">
         <v>28</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AG22" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="n">
         <v>28</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
@@ -4793,14 +4793,14 @@
         <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG22" t="n">
         <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5028,10 @@
         <v>2.6</v>
       </c>
       <c r="G24" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I24" t="n">
         <v>3.05</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G26" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H26" t="n">
         <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G27" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H27" t="n">
         <v>6.6</v>
@@ -5619,13 +5619,13 @@
         <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K27" t="n">
         <v>4.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
@@ -5634,10 +5634,10 @@
         <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P27" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q27" t="n">
         <v>2.18</v>
@@ -5658,13 +5658,13 @@
         <v>1.14</v>
       </c>
       <c r="W27" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X27" t="n">
         <v>14</v>
       </c>
       <c r="Y27" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z27" t="n">
         <v>75</v>
@@ -5673,7 +5673,7 @@
         <v>310</v>
       </c>
       <c r="AB27" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="AC27" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
         <v>170</v>
       </c>
       <c r="AF27" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AG27" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
         <v>28</v>
@@ -5697,7 +5697,7 @@
         <v>170</v>
       </c>
       <c r="AJ27" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AK27" t="n">
         <v>21</v>
@@ -5706,25 +5706,25 @@
         <v>65</v>
       </c>
       <c r="AM27" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN27" t="n">
         <v>16.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AP27" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
         <v>5.8</v>
@@ -5733,10 +5733,10 @@
         <v>7.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
         <v>7.4</v>
@@ -5745,32 +5745,32 @@
         <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>160</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 23:24:36</t>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H28" t="n">
         <v>2.2</v>
@@ -5813,7 +5813,7 @@
         <v>2.44</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
         <v>3.65</v>
@@ -5825,19 +5825,19 @@
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
         <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
         <v>3.7</v>
@@ -5846,19 +5846,19 @@
         <v>1.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>1.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X28" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Y28" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
         <v>970</v>
@@ -5891,13 +5891,13 @@
         <v>46</v>
       </c>
       <c r="AJ28" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK28" t="n">
         <v>60</v>
       </c>
       <c r="AL28" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM28" t="n">
         <v>130</v>
@@ -5909,62 +5909,256 @@
         <v>23</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ28" t="n">
         <v>4.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU28" t="n">
         <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="AX28" t="n">
         <v>3.9</v>
       </c>
       <c r="AY28" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ28" t="n">
         <v>6</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="BB28" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.06</v>
+        <v>1.55</v>
       </c>
       <c r="BF28" t="n">
         <v>7.6</v>
       </c>
       <c r="BG28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-28 01:39:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X29" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX29" t="n">
         <v>16.5</v>
       </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>2026-03-27 23:24:36</t>
+      <c r="AY29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-28 01:39:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="H2" t="n">
         <v>6.2</v>
@@ -772,28 +772,28 @@
         <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
         <v>3.3</v>
@@ -808,10 +808,10 @@
         <v>1.14</v>
       </c>
       <c r="W2" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
         <v>22</v>
@@ -820,7 +820,7 @@
         <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
@@ -862,65 +862,65 @@
         <v>11</v>
       </c>
       <c r="AO2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP2" t="n">
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.62</v>
+        <v>15.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>2.94</v>
       </c>
       <c r="AX2" t="n">
         <v>7.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BB2" t="n">
         <v>5.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
         <v>2.26</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -969,22 +969,22 @@
         <v>3.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>1.13</v>
       </c>
       <c r="N3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P3" t="n">
         <v>1.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -993,10 +993,10 @@
         <v>5.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
         <v>1.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1187,22 +1187,22 @@
         <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1265,7 +1265,7 @@
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
         <v>6.4</v>
@@ -1277,10 +1277,10 @@
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.03</v>
@@ -1292,7 +1292,7 @@
         <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>1.03</v>
@@ -1301,14 +1301,14 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="BG4" t="n">
         <v>30</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.35</v>
@@ -1363,13 +1363,13 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -1378,58 +1378,58 @@
         <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V5" t="n">
         <v>1.19</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
         <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
         <v>25</v>
@@ -1441,7 +1441,7 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1450,13 +1450,13 @@
         <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
@@ -1465,44 +1465,44 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC5" t="n">
         <v>14.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>70</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O6" t="n">
         <v>1.22</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>2.8</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2077,14 +2077,14 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG8" t="n">
         <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.54</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H9" t="n">
         <v>2.94</v>
@@ -2145,16 +2145,16 @@
         <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
         <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
         <v>1.87</v>
@@ -2163,10 +2163,10 @@
         <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
         <v>13</v>
@@ -2235,10 +2235,10 @@
         <v>42</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
         <v>11.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G10" t="n">
         <v>2.08</v>
@@ -2324,7 +2324,7 @@
         <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>2.26</v>
       </c>
       <c r="G11" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H11" t="n">
         <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
@@ -2521,7 +2521,7 @@
         <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
@@ -2530,13 +2530,13 @@
         <v>2.96</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
         <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
@@ -2545,13 +2545,13 @@
         <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
         <v>1.65</v>
@@ -2563,7 +2563,7 @@
         <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
         <v>90</v>
@@ -2578,13 +2578,13 @@
         <v>18.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
         <v>25</v>
@@ -2605,7 +2605,7 @@
         <v>170</v>
       </c>
       <c r="AN11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO11" t="n">
         <v>75</v>
@@ -2620,10 +2620,10 @@
         <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU11" t="n">
         <v>5.6</v>
@@ -2632,7 +2632,7 @@
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -2644,29 +2644,29 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF11" t="n">
         <v>20</v>
       </c>
       <c r="BG11" t="n">
-        <v>42</v>
+        <v>4.1</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -2700,19 +2700,19 @@
         <v>2.56</v>
       </c>
       <c r="G12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I12" t="n">
         <v>3.5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>2.86</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>3.7</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>2.88</v>
@@ -2927,7 +2927,7 @@
         <v>2.28</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
         <v>4.4</v>
@@ -2942,7 +2942,7 @@
         <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X13" t="n">
         <v>12.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>2.36</v>
       </c>
       <c r="G14" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I14" t="n">
         <v>3.8</v>
@@ -3124,7 +3124,7 @@
         <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
         <v>2</v>
@@ -3136,13 +3136,13 @@
         <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
         <v>28</v>
@@ -3202,7 +3202,7 @@
         <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT14" t="n">
         <v>5.9</v>
@@ -3214,7 +3214,7 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3226,29 +3226,29 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>3.15</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I15" t="n">
         <v>2.66</v>
@@ -3303,34 +3303,34 @@
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
         <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T15" t="n">
         <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
         <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
         <v>13.5</v>
@@ -3342,7 +3342,7 @@
         <v>16.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB15" t="n">
         <v>12</v>
@@ -3429,20 +3429,20 @@
         <v>30</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE15" t="n">
         <v>11</v>
       </c>
       <c r="BF15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG15" t="n">
         <v>21</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>3.05</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -3667,64 +3667,64 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="G17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="I17" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="J17" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>2.52</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P17" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3733,10 +3733,10 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
@@ -3775,13 +3775,13 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS17" t="n">
         <v>1.03</v>
@@ -3790,7 +3790,7 @@
         <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV17" t="n">
         <v>1.03</v>
@@ -3802,7 +3802,7 @@
         <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>1.03</v>
@@ -3823,14 +3823,14 @@
         <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>2.58</v>
       </c>
       <c r="G18" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H18" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J18" t="n">
         <v>2.56</v>
       </c>
       <c r="K18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3888,7 +3888,7 @@
         <v>1.41</v>
       </c>
       <c r="O18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P18" t="n">
         <v>1.4</v>
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -4255,10 +4255,10 @@
         <v>1.63</v>
       </c>
       <c r="H20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J20" t="n">
         <v>4.4</v>
@@ -4273,22 +4273,22 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="T20" t="n">
         <v>1.8</v>
@@ -4315,7 +4315,7 @@
         <v>170</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AC20" t="n">
         <v>10.5</v>
@@ -4324,7 +4324,7 @@
         <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="n">
         <v>10.5</v>
@@ -4336,7 +4336,7 @@
         <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
         <v>16</v>
@@ -4351,34 +4351,34 @@
         <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP20" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR20" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS20" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV20" t="n">
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
         <v>9.199999999999999</v>
@@ -4390,7 +4390,7 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BB20" t="n">
         <v>13.5</v>
@@ -4402,17 +4402,17 @@
         <v>26</v>
       </c>
       <c r="BE20" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BF20" t="n">
         <v>6.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>65</v>
+        <v>9.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -4637,46 +4637,46 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="H22" t="n">
         <v>1.09</v>
       </c>
       <c r="I22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J22" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="K22" t="n">
         <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="R22" t="n">
         <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="T22" t="n">
         <v>1.78</v>
@@ -4685,28 +4685,28 @@
         <v>1.75</v>
       </c>
       <c r="V22" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
         <v>2.08</v>
       </c>
       <c r="X22" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Y22" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD22" t="n">
         <v>29</v>
@@ -4715,22 +4715,22 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AL22" t="n">
         <v>48</v>
@@ -4739,68 +4739,68 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="G23" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="H23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I23" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
         <v>2.76</v>
@@ -4855,22 +4855,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P23" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R23" t="n">
         <v>1.14</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4879,10 +4879,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="G24" t="n">
         <v>2.94</v>
@@ -5037,7 +5037,7 @@
         <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
         <v>3.5</v>
@@ -5049,13 +5049,13 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q24" t="n">
         <v>2.04</v>
@@ -5112,7 +5112,7 @@
         <v>18.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ24" t="n">
         <v>46</v>
@@ -5124,10 +5124,10 @@
         <v>48</v>
       </c>
       <c r="AM24" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN24" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO24" t="n">
         <v>34</v>
@@ -5142,7 +5142,7 @@
         <v>16</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT24" t="n">
         <v>9</v>
@@ -5154,7 +5154,7 @@
         <v>10.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX24" t="n">
         <v>15</v>
@@ -5166,29 +5166,29 @@
         <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF24" t="n">
         <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -5327,52 +5327,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G26" t="n">
         <v>2.1</v>
@@ -5422,7 +5422,7 @@
         <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J26" t="n">
         <v>3.45</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G27" t="n">
         <v>1.7</v>
@@ -5622,10 +5622,10 @@
         <v>3.7</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
@@ -5634,7 +5634,7 @@
         <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P27" t="n">
         <v>1.69</v>
@@ -5661,7 +5661,7 @@
         <v>2.42</v>
       </c>
       <c r="X27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y27" t="n">
         <v>970</v>
@@ -5718,13 +5718,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AT27" t="n">
         <v>5.8</v>
@@ -5733,10 +5733,10 @@
         <v>7.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AX27" t="n">
         <v>7.4</v>
@@ -5745,32 +5745,32 @@
         <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="G28" t="n">
         <v>3.85</v>
@@ -5810,10 +5810,10 @@
         <v>2.2</v>
       </c>
       <c r="I28" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
         <v>3.65</v>
@@ -5825,31 +5825,31 @@
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P28" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R28" t="n">
         <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="T28" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W28" t="n">
         <v>1.35</v>
@@ -5885,7 +5885,7 @@
         <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI28" t="n">
         <v>46</v>
@@ -5909,37 +5909,37 @@
         <v>23</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ28" t="n">
         <v>4.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU28" t="n">
         <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="AX28" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="AY28" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA28" t="n">
         <v>1.93</v>
@@ -5951,20 +5951,20 @@
         <v>1.95</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BE28" t="n">
         <v>1.55</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>3.2</v>
       </c>
       <c r="H29" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I29" t="n">
         <v>2.88</v>
@@ -6010,34 +6010,34 @@
         <v>3.2</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T29" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U29" t="n">
         <v>2.04</v>
@@ -6049,7 +6049,7 @@
         <v>1.45</v>
       </c>
       <c r="X29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y29" t="n">
         <v>11</v>
@@ -6112,7 +6112,7 @@
         <v>14.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT29" t="n">
         <v>9.199999999999999</v>
@@ -6124,7 +6124,7 @@
         <v>10.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX29" t="n">
         <v>16.5</v>
@@ -6136,29 +6136,29 @@
         <v>15</v>
       </c>
       <c r="BA29" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB29" t="n">
         <v>40</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD29" t="n">
         <v>40</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF29" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG29" t="n">
         <v>21</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH29"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>South Korean K3 League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,84 +743,84 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Chuncheon</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Changwon City</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.72</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>6.2</v>
+        <v>1.65</v>
       </c>
       <c r="I2" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S2" t="n">
         <v>3.75</v>
       </c>
-      <c r="K2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T2" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="V2" t="n">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.38</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>250</v>
+        <v>23</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
@@ -829,105 +829,105 @@
         <v>970</v>
       </c>
       <c r="AD2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE2" t="n">
         <v>28</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
         <v>120</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AL2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
         <v>970</v>
       </c>
-      <c r="AG2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>180</v>
-      </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>3.65</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.5</v>
+        <v>3.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW2" t="n">
         <v>4.4</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AX2" t="n">
         <v>4.7</v>
       </c>
-      <c r="AV2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AY2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BD2" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.26</v>
+        <v>4.1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>South Korean K3 League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Yeoju FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Ulsan Citizen FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="G3" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.56</v>
+        <v>1.51</v>
       </c>
       <c r="O3" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.76</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>5.9</v>
+        <v>2.14</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trapani</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG4" t="n">
         <v>2.26</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>30</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.78</v>
+        <v>2.58</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92</v>
+        <v>2.64</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="O5" t="n">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="P5" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG5" t="n">
         <v>13</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE5" t="n">
         <v>16.5</v>
       </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NK Slovenska Bistrica</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jesenice</t>
+          <t>Trapani</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.55</v>
       </c>
-      <c r="H6" t="n">
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS6" t="n">
         <v>6.6</v>
       </c>
-      <c r="I6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AT6" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.35</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.36</v>
+        <v>6.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.36</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.36</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.36</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>1.78</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4</v>
+        <v>1.93</v>
       </c>
       <c r="H7" t="n">
-        <v>1.93</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2.16</v>
+        <v>6.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.86</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>2.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,73 +1907,73 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Connahs Quay</t>
+          <t>NK Slovenska Bistrica</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barry Town Utd</t>
+          <t>Jesenice</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="J8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W8" t="n">
         <v>2.8</v>
       </c>
-      <c r="K8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.92</v>
-      </c>
       <c r="X8" t="n">
         <v>1000</v>
       </c>
@@ -2029,69 +2029,69 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.37</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.37</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11:15:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Leonesa</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Andorra CF</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.66</v>
+        <v>5.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.94</v>
+        <v>1.93</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>2.16</v>
       </c>
       <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.4</v>
       </c>
-      <c r="K9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.9</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,69 +2295,69 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Connahs Quay</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pacos Ferreira</t>
+          <t>Barry Town Utd</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="G10" t="n">
         <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="K10" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>1.82</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W10" t="n">
         <v>1.92</v>
@@ -2465,21 +2465,21 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:15:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Leonesa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Andorra CF</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="I11" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
         <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="U11" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW11" t="n">
         <v>30</v>
       </c>
-      <c r="AA11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="AX11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY11" t="n">
         <v>11</v>
       </c>
-      <c r="AW11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.1</v>
+        <v>40</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.9</v>
+        <v>32</v>
       </c>
       <c r="BC11" t="n">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD11" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BF11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pesaro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pacos Ferreira</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.56</v>
+        <v>1.72</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="H12" t="n">
-        <v>2.52</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,22 +2721,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32</v>
+        <v>1.77</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.92</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
@@ -2882,46 +2882,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Forli</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>US Pianese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="J13" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
         <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
         <v>2.28</v>
@@ -2930,138 +2930,138 @@
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="X13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA13" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE13" t="n">
         <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AK13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN13" t="n">
         <v>34</v>
       </c>
-      <c r="AL13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>29</v>
-      </c>
       <c r="AO13" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT13" t="n">
         <v>6.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>50</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Pesaro</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G14" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="H14" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.64</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>2.34</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="X14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Forli</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>US Pianese</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="H15" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>2.66</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.79</v>
       </c>
-      <c r="U15" t="n">
-        <v>2.12</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="X15" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AB15" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AK15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL15" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM15" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="AN15" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO15" t="n">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="AP15" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>14</v>
+        <v>4.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>32</v>
+        <v>4.9</v>
       </c>
       <c r="AT15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX15" t="n">
         <v>10</v>
       </c>
-      <c r="AU15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>18</v>
-      </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
         <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>36</v>
+        <v>4.8</v>
       </c>
       <c r="BB15" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>30</v>
+        <v>4.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BF15" t="n">
-        <v>28</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>21</v>
+        <v>4.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="G16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2.36</v>
       </c>
-      <c r="H16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.72</v>
-      </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AZ Picerno ASD</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="I17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.45</v>
       </c>
-      <c r="J17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>2.52</v>
+        <v>3.65</v>
       </c>
       <c r="O17" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.51</v>
+        <v>1.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="T17" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="W17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV17" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BF17" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BG17" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,184 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="G18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K18" t="n">
         <v>3.55</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.51</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Q18" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
@@ -4046,67 +4046,67 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ASD Pineto Calcio</t>
+          <t>AZ Picerno ASD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.16</v>
+        <v>2.98</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="I19" t="n">
-        <v>4.2</v>
+        <v>2.96</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="K19" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>2.54</v>
       </c>
       <c r="O19" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="P19" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>2.24</v>
+        <v>4.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V19" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
@@ -4163,69 +4163,69 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>2.62</v>
       </c>
       <c r="G20" t="n">
-        <v>1.63</v>
+        <v>3.55</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2</v>
+        <v>2.52</v>
       </c>
       <c r="I20" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>1.41</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>1.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>2.74</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z20" t="n">
         <v>25</v>
       </c>
-      <c r="Z20" t="n">
-        <v>55</v>
-      </c>
       <c r="AA20" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AX20" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU20" t="n">
+      <c r="AY20" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AV20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.4</v>
+        <v>2.36</v>
       </c>
       <c r="BB20" t="n">
-        <v>13.5</v>
+        <v>2.36</v>
       </c>
       <c r="BC20" t="n">
-        <v>14</v>
+        <v>2.36</v>
       </c>
       <c r="BD20" t="n">
-        <v>26</v>
+        <v>2.36</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.6</v>
+        <v>2.36</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.8</v>
+        <v>2.36</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.4</v>
+        <v>2.36</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,78 +4429,78 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>ASD Pineto Calcio</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="K21" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N21" t="n">
-        <v>1.44</v>
+        <v>2.54</v>
       </c>
       <c r="O21" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="P21" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="V21" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
@@ -4509,10 +4509,10 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD21" t="n">
         <v>1000</v>
@@ -4524,7 +4524,7 @@
         <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH21" t="n">
         <v>1000</v>
@@ -4551,69 +4551,69 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G22" t="n">
         <v>1.61</v>
       </c>
-      <c r="G22" t="n">
-        <v>1.92</v>
-      </c>
       <c r="H22" t="n">
-        <v>1.09</v>
+        <v>6.2</v>
       </c>
       <c r="I22" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>2.94</v>
+        <v>4.4</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="T22" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="U22" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="V22" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W22" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="X22" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="Z22" t="n">
         <v>55</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AG22" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD22" t="n">
         <v>26</v>
       </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BE22" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>3.9</v>
+        <v>9.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="G23" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I23" t="n">
         <v>5.2</v>
       </c>
       <c r="J23" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="K23" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,37 +4855,37 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="O23" t="n">
         <v>1.02</v>
       </c>
       <c r="P23" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="R23" t="n">
         <v>1.14</v>
       </c>
       <c r="S23" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W23" t="n">
         <v>1.6</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y23" t="n">
         <v>1000</v>
@@ -4939,7 +4939,7 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.03</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.68</v>
+        <v>1.67</v>
       </c>
       <c r="G24" t="n">
-        <v>2.94</v>
+        <v>1.9</v>
       </c>
       <c r="H24" t="n">
-        <v>2.72</v>
+        <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="J24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K24" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.04</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.65</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
         <v>1.78</v>
       </c>
       <c r="U24" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="W24" t="n">
-        <v>1.51</v>
+        <v>2.12</v>
       </c>
       <c r="X24" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y24" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AA24" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD24" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="AE24" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG24" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AI24" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="AK24" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AL24" t="n">
         <v>48</v>
       </c>
       <c r="AM24" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AO24" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>10.5</v>
+        <v>3.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="AR24" t="n">
-        <v>16</v>
+        <v>3.7</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>2.82</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.6</v>
+        <v>2.94</v>
       </c>
       <c r="AV24" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.2</v>
+        <v>3.85</v>
       </c>
       <c r="AX24" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>10.5</v>
+        <v>3</v>
       </c>
       <c r="AZ24" t="n">
-        <v>15</v>
+        <v>3.45</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.6</v>
+        <v>3.85</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.6</v>
+        <v>3.35</v>
       </c>
       <c r="BC24" t="n">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="BF24" t="n">
-        <v>21</v>
+        <v>3.15</v>
       </c>
       <c r="BG24" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,36 +5205,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5243,22 +5243,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="O25" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S25" t="n">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5267,10 +5267,10 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5327,52 +5327,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2.04</v>
       </c>
-      <c r="G26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="R26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S26" t="n">
         <v>3.65</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.18</v>
+        <v>1.39</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>4.3</v>
+        <v>1.39</v>
       </c>
       <c r="T27" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,378 +5787,766 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J28" t="n">
         <v>3.45</v>
-      </c>
-      <c r="G28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.3</v>
       </c>
       <c r="K28" t="n">
         <v>3.65</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Racing Club (Uru)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-28 06:09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X30" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-28 06:09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Llaneros FC</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Once Caldas</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F31" t="n">
         <v>2.8</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G31" t="n">
         <v>3.2</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H31" t="n">
         <v>2.58</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I31" t="n">
         <v>2.88</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J31" t="n">
         <v>3.2</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K31" t="n">
         <v>3.55</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="L31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M31" t="n">
         <v>1.08</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N31" t="n">
         <v>3.25</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O31" t="n">
         <v>1.38</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P31" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q31" t="n">
         <v>2.1</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R31" t="n">
         <v>1.28</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S31" t="n">
         <v>3.75</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T31" t="n">
         <v>1.8</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U31" t="n">
         <v>2.04</v>
       </c>
-      <c r="V29" t="n">
+      <c r="V31" t="n">
         <v>1.53</v>
       </c>
-      <c r="W29" t="n">
+      <c r="W31" t="n">
         <v>1.45</v>
       </c>
-      <c r="X29" t="n">
+      <c r="X31" t="n">
         <v>13</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Y31" t="n">
         <v>11</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="Z31" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AA31" t="n">
         <v>44</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AB31" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AC31" t="n">
         <v>8</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AD31" t="n">
         <v>13</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AE31" t="n">
         <v>34</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AF31" t="n">
         <v>21</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AG31" t="n">
         <v>14</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AH31" t="n">
         <v>19</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AI31" t="n">
         <v>48</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AJ31" t="n">
         <v>55</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AK31" t="n">
         <v>38</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AL31" t="n">
         <v>55</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AM31" t="n">
         <v>120</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AN31" t="n">
         <v>38</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AO31" t="n">
         <v>29</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AP31" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AQ31" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AR31" t="n">
         <v>14.5</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AS31" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AT31" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AU31" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AV31" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AW31" t="n">
         <v>7</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AX31" t="n">
         <v>16.5</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="AY31" t="n">
         <v>11</v>
       </c>
-      <c r="AZ29" t="n">
+      <c r="AZ31" t="n">
         <v>15</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BA31" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BB31" t="n">
         <v>40</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BC31" t="n">
         <v>7.2</v>
       </c>
-      <c r="BD29" t="n">
+      <c r="BD31" t="n">
         <v>40</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="BE31" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF29" t="n">
+      <c r="BF31" t="n">
         <v>7.2</v>
       </c>
-      <c r="BG29" t="n">
+      <c r="BG31" t="n">
         <v>21</v>
       </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-03-28 03:54:22</t>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -763,10 +763,10 @@
         <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -781,7 +781,7 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="O2" t="n">
         <v>1.42</v>
@@ -796,13 +796,13 @@
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
         <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -975,13 +975,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O3" t="n">
         <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
         <v>2.12</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H4" t="n">
         <v>6.2</v>
@@ -1163,7 +1163,7 @@
         <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1187,7 +1187,7 @@
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U4" t="n">
         <v>1.88</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.58</v>
       </c>
       <c r="G5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H5" t="n">
         <v>3.35</v>
@@ -1363,10 +1363,10 @@
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P5" t="n">
         <v>1.53</v>
@@ -1378,25 +1378,25 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="T5" t="n">
         <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V5" t="n">
         <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X5" t="n">
         <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
         <v>21</v>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
@@ -1435,28 +1435,28 @@
         <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
         <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP5" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR5" t="n">
         <v>18.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
         <v>6.8</v>
@@ -1468,7 +1468,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="AX5" t="n">
         <v>13.5</v>
@@ -1477,32 +1477,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE5" t="n">
         <v>15.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>16.5</v>
       </c>
       <c r="BF5" t="n">
         <v>34</v>
       </c>
       <c r="BG5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="n">
         <v>2.82</v>
       </c>
       <c r="H6" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="n">
         <v>3.25</v>
@@ -1560,19 +1560,19 @@
         <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
         <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
         <v>1.86</v>
@@ -1581,7 +1581,7 @@
         <v>1.98</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
         <v>1.55</v>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AR6" t="n">
         <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
@@ -1662,7 +1662,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
         <v>12</v>
@@ -1671,32 +1671,32 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BA6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG6" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
         <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS7" t="n">
         <v>4.2</v>
@@ -1877,10 +1877,10 @@
         <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
         <v>10</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -2115,46 +2115,46 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="G9" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="I9" t="n">
         <v>2.16</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.71</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
         <v>1.92</v>
@@ -2166,40 +2166,40 @@
         <v>1.86</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2220,65 +2220,65 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
         <v>1.19</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.4</v>
+        <v>3.15</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="H11" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J11" t="n">
         <v>3.4</v>
@@ -2527,40 +2527,40 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
         <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
         <v>19.5</v>
@@ -2593,10 +2593,10 @@
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
         <v>46</v>
@@ -2605,7 +2605,7 @@
         <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO11" t="n">
         <v>36</v>
@@ -2614,10 +2614,10 @@
         <v>11.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
         <v>42</v>
@@ -2629,19 +2629,19 @@
         <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
         <v>30</v>
       </c>
       <c r="AX11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
         <v>40</v>
@@ -2650,13 +2650,13 @@
         <v>32</v>
       </c>
       <c r="BC11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD11" t="n">
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
         <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>3.05</v>
@@ -2921,7 +2921,7 @@
         <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
         <v>2.28</v>
@@ -2930,19 +2930,19 @@
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T13" t="n">
         <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
         <v>13</v>
@@ -2972,7 +2972,7 @@
         <v>17.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
         <v>25</v>
@@ -2993,7 +2993,7 @@
         <v>170</v>
       </c>
       <c r="AN13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO13" t="n">
         <v>75</v>
@@ -3008,7 +3008,7 @@
         <v>17.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
         <v>6.2</v>
@@ -3032,29 +3032,29 @@
         <v>14.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>3.8</v>
       </c>
       <c r="BD13" t="n">
         <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.34</v>
       </c>
       <c r="G14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
         <v>2.58</v>
@@ -3136,7 +3136,7 @@
         <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="H15" t="n">
         <v>3.7</v>
@@ -3297,7 +3297,7 @@
         <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
         <v>1.1</v>
@@ -3330,7 +3330,7 @@
         <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
         <v>12.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="T16" t="n">
         <v>2.02</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H17" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J17" t="n">
         <v>3.35</v>
@@ -3691,19 +3691,19 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q17" t="n">
         <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
         <v>3.65</v>
@@ -3712,13 +3712,13 @@
         <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X17" t="n">
         <v>13.5</v>
@@ -3727,7 +3727,7 @@
         <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AA17" t="n">
         <v>46</v>
@@ -3778,7 +3778,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR17" t="n">
         <v>14</v>
@@ -3787,7 +3787,7 @@
         <v>32</v>
       </c>
       <c r="AT17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU17" t="n">
         <v>7.2</v>
@@ -3805,13 +3805,13 @@
         <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
         <v>36</v>
       </c>
       <c r="BB17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC17" t="n">
         <v>30</v>
@@ -3820,7 +3820,7 @@
         <v>10</v>
       </c>
       <c r="BE17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF17" t="n">
         <v>27</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -4079,13 +4079,13 @@
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
         <v>1.52</v>
       </c>
       <c r="P19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q19" t="n">
         <v>2.52</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -4646,13 +4646,13 @@
         <v>6.2</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,34 +4661,34 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
         <v>1.23</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="T22" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U22" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="X22" t="n">
         <v>20</v>
@@ -4703,7 +4703,7 @@
         <v>180</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC22" t="n">
         <v>10.5</v>
@@ -4715,10 +4715,10 @@
         <v>85</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH22" t="n">
         <v>21</v>
@@ -4733,13 +4733,13 @@
         <v>16</v>
       </c>
       <c r="AL22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
       </c>
       <c r="AN22" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO22" t="n">
         <v>90</v>
@@ -4748,59 +4748,59 @@
         <v>17.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR22" t="n">
         <v>40</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY22" t="n">
         <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BB22" t="n">
         <v>14</v>
       </c>
       <c r="BC22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.6</v>
+        <v>80</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -4942,59 +4942,59 @@
         <v>5.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -5034,10 +5034,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="K24" t="n">
         <v>950</v>
@@ -5049,22 +5049,22 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
         <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="R24" t="n">
         <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T24" t="n">
         <v>1.78</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.68</v>
       </c>
       <c r="G26" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H26" t="n">
         <v>2.72</v>
@@ -5464,7 +5464,7 @@
         <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X26" t="n">
         <v>13.5</v>
@@ -5524,7 +5524,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR26" t="n">
         <v>16</v>
@@ -5533,13 +5533,13 @@
         <v>7.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU26" t="n">
         <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW26" t="n">
         <v>7.4</v>
@@ -5563,20 +5563,20 @@
         <v>7.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BE26" t="n">
         <v>8.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG26" t="n">
         <v>7.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
         <v>4.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U29" t="n">
         <v>1.72</v>
@@ -6109,10 +6109,10 @@
         <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="AT29" t="n">
         <v>5.8</v>
@@ -6124,7 +6124,7 @@
         <v>6.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AX29" t="n">
         <v>7.4</v>
@@ -6133,10 +6133,10 @@
         <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="BB29" t="n">
         <v>5.8</v>
@@ -6145,20 +6145,20 @@
         <v>6.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BF29" t="n">
         <v>5.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -6225,10 +6225,10 @@
         <v>2.1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="T30" t="n">
         <v>1.83</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -760,16 +760,16 @@
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="I2" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>3.7</v>
@@ -778,43 +778,43 @@
         <v>1.54</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="Z2" t="n">
         <v>970</v>
@@ -832,16 +832,16 @@
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AG2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
         <v>60</v>
@@ -850,7 +850,7 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL2" t="n">
         <v>120</v>
@@ -865,62 +865,62 @@
         <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="AW2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA2" t="n">
         <v>5.8</v>
       </c>
-      <c r="AX2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BB2" t="n">
-        <v>6</v>
+        <v>2.06</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.9</v>
+        <v>2.52</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="BF2" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G3" t="n">
         <v>3.15</v>
       </c>
       <c r="H3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>3.45</v>
@@ -975,16 +975,16 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
@@ -993,16 +993,16 @@
         <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>1.89</v>
       </c>
       <c r="V3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.47</v>
       </c>
       <c r="X3" t="n">
         <v>11.5</v>
@@ -1011,16 +1011,16 @@
         <v>9.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
         <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
         <v>14</v>
@@ -1032,7 +1032,7 @@
         <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH3" t="n">
         <v>21</v>
@@ -1047,19 +1047,19 @@
         <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>7.8</v>
@@ -1068,7 +1068,7 @@
         <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -1080,7 +1080,7 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
         <v>15.5</v>
@@ -1092,19 +1092,19 @@
         <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB3" t="n">
         <v>38</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
         <v>32</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jeonbuk (Res)</t>
+          <t>Jeonbuk Hyundai Motors (Res)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1154,7 +1154,7 @@
         <v>2.38</v>
       </c>
       <c r="I4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
         <v>3.1</v>
@@ -1163,25 +1163,25 @@
         <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
         <v>4.3</v>
@@ -1214,7 +1214,7 @@
         <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
         <v>14</v>
@@ -1253,7 +1253,7 @@
         <v>34</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4" t="n">
         <v>7.6</v>
@@ -1271,13 +1271,13 @@
         <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="n">
         <v>13</v>
@@ -1286,29 +1286,29 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB4" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB4" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG4" t="n">
         <v>5.5</v>
       </c>
-      <c r="BG4" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
         <v>1.69</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I5" t="n">
         <v>7.8</v>
@@ -1363,13 +1363,13 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
         <v>1.94</v>
@@ -1381,22 +1381,22 @@
         <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Z5" t="n">
         <v>60</v>
@@ -1447,40 +1447,40 @@
         <v>170</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
         <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
         <v>13</v>
@@ -1489,20 +1489,20 @@
         <v>5.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF5" t="n">
         <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.42</v>
       </c>
       <c r="G6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H6" t="n">
         <v>7.6</v>
@@ -1551,7 +1551,7 @@
         <v>5.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1572,7 +1572,7 @@
         <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
         <v>1.91</v>
@@ -1644,13 +1644,13 @@
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT6" t="n">
         <v>6.6</v>
@@ -1659,10 +1659,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
         <v>6.8</v>
@@ -1671,32 +1671,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
         <v>9.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -1733,13 +1733,13 @@
         <v>1.82</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I7" t="n">
         <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
         <v>4.8</v>
@@ -1754,7 +1754,7 @@
         <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
         <v>2.1</v>
@@ -1769,7 +1769,7 @@
         <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
         <v>2.04</v>
@@ -1796,7 +1796,7 @@
         <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
         <v>24</v>
@@ -1817,10 +1817,10 @@
         <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AL7" t="n">
         <v>38</v>
@@ -1829,25 +1829,25 @@
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO7" t="n">
         <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.7</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
         <v>3.75</v>
@@ -1856,41 +1856,41 @@
         <v>4.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA7" t="n">
         <v>5.4</v>
       </c>
       <c r="BB7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5</v>
-      </c>
       <c r="BE7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG7" t="n">
         <v>5.5</v>
       </c>
-      <c r="BF7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G8" t="n">
         <v>2.62</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
@@ -1963,7 +1963,7 @@
         <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U8" t="n">
         <v>1.81</v>
@@ -1975,7 +1975,7 @@
         <v>1.61</v>
       </c>
       <c r="X8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y8" t="n">
         <v>9.6</v>
@@ -1984,7 +1984,7 @@
         <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB8" t="n">
         <v>7.8</v>
@@ -2002,7 +2002,7 @@
         <v>14.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
         <v>24</v>
@@ -2023,19 +2023,19 @@
         <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AP8" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
         <v>29</v>
@@ -2059,10 +2059,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB8" t="n">
         <v>34</v>
@@ -2074,17 +2074,17 @@
         <v>55</v>
       </c>
       <c r="BE8" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG8" t="n">
-        <v>16.5</v>
+        <v>55</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -2115,100 +2115,100 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
-        <v>600</v>
+        <v>3.8</v>
       </c>
       <c r="H9" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="I9" t="n">
-        <v>2.98</v>
+        <v>2.66</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>2.96</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="P9" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2220,65 +2220,65 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.02</v>
+        <v>7.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.02</v>
+        <v>12.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.02</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.02</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.02</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.02</v>
+        <v>6.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.02</v>
+        <v>19.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.02</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.02</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.02</v>
+        <v>18.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.02</v>
+        <v>20</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.02</v>
+        <v>7.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.02</v>
+        <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.02</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.02</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.02</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G10" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H10" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
         <v>3.55</v>
@@ -2330,43 +2330,43 @@
         <v>1.46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
         <v>2.04</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="T10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
         <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.53</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
@@ -2378,7 +2378,7 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2387,10 +2387,10 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
         <v>1000</v>
@@ -2420,13 +2420,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AR10" t="n">
         <v>15.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
         <v>8.4</v>
@@ -2438,41 +2438,41 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="AY10" t="n">
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.99</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="n">
         <v>4.1</v>
@@ -2515,16 +2515,16 @@
         <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
         <v>2.96</v>
@@ -2536,25 +2536,25 @@
         <v>1.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="V11" t="n">
         <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -2575,7 +2575,7 @@
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
@@ -2590,7 +2590,7 @@
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
         <v>27</v>
@@ -2599,7 +2599,7 @@
         <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
@@ -2611,40 +2611,40 @@
         <v>110</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BB11" t="n">
         <v>19.5</v>
@@ -2653,20 +2653,20 @@
         <v>19</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF11" t="n">
         <v>16</v>
       </c>
       <c r="BG11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -2697,58 +2697,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="H12" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.15</v>
       </c>
-      <c r="K12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.58</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P12" t="n">
         <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2763,7 +2763,7 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.02</v>
+        <v>5.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.02</v>
+        <v>7.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.02</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.02</v>
+        <v>6.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.02</v>
+        <v>6.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.02</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.02</v>
+        <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.02</v>
+        <v>4.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -2921,13 +2921,13 @@
         <v>1.35</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
         <v>2.06</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
         <v>3.7</v>
@@ -2957,7 +2957,7 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>8.6</v>
@@ -2993,7 +2993,7 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
         <v>7</v>
@@ -3035,26 +3035,26 @@
         <v>50</v>
       </c>
       <c r="BB13" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF13" t="n">
         <v>11.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -3103,13 +3103,13 @@
         <v>3.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.41</v>
@@ -3127,10 +3127,10 @@
         <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V14" t="n">
         <v>1.9</v>
@@ -3139,10 +3139,10 @@
         <v>1.26</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z14" t="n">
         <v>14</v>
@@ -3154,10 +3154,10 @@
         <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>28</v>
@@ -3172,7 +3172,7 @@
         <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ14" t="n">
         <v>7</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AS14" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.8</v>
+        <v>40</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -3279,55 +3279,55 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="I15" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="R15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="T15" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U15" t="n">
         <v>1.69</v>
       </c>
       <c r="V15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="W15" t="n">
         <v>1.09</v>
@@ -3336,7 +3336,7 @@
         <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AT15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW15" t="n">
         <v>3.9</v>
       </c>
-      <c r="AU15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD15" t="n">
         <v>3.85</v>
       </c>
-      <c r="AX15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE15" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -3512,7 +3512,7 @@
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H17" t="n">
         <v>9.6</v>
@@ -3679,28 +3679,28 @@
         <v>13.5</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
@@ -3709,19 +3709,19 @@
         <v>3.35</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
         <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
         <v>29</v>
@@ -3736,7 +3736,7 @@
         <v>7.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD17" t="n">
         <v>46</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV17" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS17" t="n">
+      <c r="AW17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD17" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD17" t="n">
+      <c r="BE17" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE17" t="n">
-        <v>5</v>
-      </c>
       <c r="BF17" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G18" t="n">
         <v>1.27</v>
@@ -3873,10 +3873,10 @@
         <v>32</v>
       </c>
       <c r="J18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.36</v>
@@ -3885,22 +3885,22 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
         <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T18" t="n">
         <v>2.92</v>
@@ -3912,7 +3912,7 @@
         <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="X18" t="n">
         <v>19.5</v>
@@ -3927,7 +3927,7 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC18" t="n">
         <v>19</v>
@@ -3939,10 +3939,10 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>65</v>
@@ -3954,7 +3954,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AK18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
         <v>85</v>
@@ -3963,7 +3963,7 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3972,59 +3972,59 @@
         <v>13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.65</v>
+        <v>6.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G19" t="n">
         <v>1.54</v>
@@ -4070,31 +4070,31 @@
         <v>4.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>1.11</v>
       </c>
       <c r="O19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
         <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="T19" t="n">
         <v>1.84</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="BA19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD19" t="n">
         <v>4</v>
       </c>
-      <c r="AR19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE19" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -4258,10 +4258,10 @@
         <v>3.7</v>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
         <v>5.5</v>
@@ -4288,7 +4288,7 @@
         <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
         <v>1.68</v>
@@ -4357,62 +4357,62 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AS20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB20" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB20" t="n">
+      <c r="BC20" t="n">
         <v>3.65</v>
       </c>
-      <c r="BC20" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BD20" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BG20" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -4443,58 +4443,58 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>1.92</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N21" t="n">
-        <v>1.24</v>
+        <v>2.38</v>
       </c>
       <c r="O21" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R21" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>2.52</v>
       </c>
       <c r="G22" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H22" t="n">
         <v>3.05</v>
       </c>
       <c r="I22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
         <v>3.5</v>
@@ -4655,13 +4655,13 @@
         <v>3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O22" t="n">
         <v>1.36</v>
@@ -4676,19 +4676,19 @@
         <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X22" t="n">
         <v>12.5</v>
@@ -4721,10 +4721,10 @@
         <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ22" t="n">
         <v>38</v>
@@ -4733,7 +4733,7 @@
         <v>28</v>
       </c>
       <c r="AL22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -4754,7 +4754,7 @@
         <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>16.5</v>
+        <v>46</v>
       </c>
       <c r="AT22" t="n">
         <v>9.4</v>
@@ -4766,7 +4766,7 @@
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX22" t="n">
         <v>14.5</v>
@@ -4778,29 +4778,29 @@
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BB22" t="n">
         <v>32</v>
       </c>
       <c r="BC22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD22" t="n">
         <v>36</v>
       </c>
       <c r="BE22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BF22" t="n">
         <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>1.79</v>
       </c>
       <c r="G23" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H23" t="n">
         <v>4.6</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G24" t="n">
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
@@ -5049,7 +5049,7 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O24" t="n">
         <v>1.01</v>
@@ -5058,13 +5058,13 @@
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R24" t="n">
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -5133,62 +5133,62 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.71</v>
+        <v>1.02</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="H25" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="J25" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="K25" t="n">
         <v>3.65</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>1.74</v>
+        <v>3.15</v>
       </c>
       <c r="O25" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P25" t="n">
         <v>1.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>1.94</v>
+        <v>3.75</v>
       </c>
       <c r="T25" t="n">
-        <v>1.05</v>
+        <v>1.79</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W25" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.02</v>
+        <v>8.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.02</v>
+        <v>15.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.02</v>
+        <v>7.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.02</v>
+        <v>5.7</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.02</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.02</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.02</v>
+        <v>13</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.02</v>
+        <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.02</v>
+        <v>3.95</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.02</v>
+        <v>19.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>3.35</v>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J26" t="n">
         <v>3.1</v>
@@ -5446,7 +5446,7 @@
         <v>1.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R26" t="n">
         <v>1.25</v>
@@ -5479,10 +5479,10 @@
         <v>85</v>
       </c>
       <c r="AB26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD26" t="n">
         <v>18.5</v>
@@ -5497,13 +5497,13 @@
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ26" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK26" t="n">
         <v>32</v>
@@ -5518,10 +5518,10 @@
         <v>36</v>
       </c>
       <c r="AO26" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ26" t="n">
         <v>8.4</v>
@@ -5530,19 +5530,19 @@
         <v>17.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT26" t="n">
         <v>7.2</v>
       </c>
       <c r="AU26" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV26" t="n">
         <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
@@ -5554,29 +5554,29 @@
         <v>14.5</v>
       </c>
       <c r="BA26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC26" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF26" t="n">
         <v>20</v>
       </c>
       <c r="BG26" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -5607,31 +5607,31 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H27" t="n">
         <v>4.3</v>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J27" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M27" t="n">
         <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O27" t="n">
         <v>1.48</v>
@@ -5655,16 +5655,16 @@
         <v>1.79</v>
       </c>
       <c r="V27" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W27" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X27" t="n">
         <v>90</v>
       </c>
       <c r="Y27" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z27" t="n">
         <v>36</v>
@@ -5685,10 +5685,10 @@
         <v>85</v>
       </c>
       <c r="AF27" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG27" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
         <v>26</v>
@@ -5721,10 +5721,10 @@
         <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT27" t="n">
         <v>5.8</v>
@@ -5733,10 +5733,10 @@
         <v>6</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
@@ -5745,32 +5745,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF27" t="n">
-        <v>19.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG27" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>2.96</v>
       </c>
       <c r="H28" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I28" t="n">
         <v>3.2</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -5998,10 +5998,10 @@
         <v>2.2</v>
       </c>
       <c r="G29" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H29" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I29" t="n">
         <v>3.9</v>
@@ -6043,10 +6043,10 @@
         <v>2.06</v>
       </c>
       <c r="V29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X29" t="n">
         <v>14.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.2</v>
       </c>
       <c r="G30" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H30" t="n">
         <v>3.75</v>
@@ -6222,7 +6222,7 @@
         <v>1.66</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R30" t="n">
         <v>1.24</v>
@@ -6258,7 +6258,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD30" t="n">
         <v>19</v>
@@ -6300,13 +6300,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS30" t="n">
         <v>4</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>3.85</v>
       </c>
       <c r="AT30" t="n">
         <v>6.4</v>
@@ -6318,10 +6318,10 @@
         <v>12.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AY30" t="n">
         <v>8.800000000000001</v>
@@ -6330,29 +6330,29 @@
         <v>15.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB30" t="n">
         <v>6.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>21</v>
+        <v>5.1</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG30" t="n">
         <v>3.95</v>
       </c>
-      <c r="BF30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.4</v>
       </c>
       <c r="G31" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H31" t="n">
         <v>3.35</v>
@@ -6395,7 +6395,7 @@
         <v>3.7</v>
       </c>
       <c r="J31" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K31" t="n">
         <v>3.35</v>
@@ -6485,7 +6485,7 @@
         <v>210</v>
       </c>
       <c r="AN31" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AO31" t="n">
         <v>90</v>
@@ -6497,10 +6497,10 @@
         <v>7.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT31" t="n">
         <v>6</v>
@@ -6509,44 +6509,44 @@
         <v>6.2</v>
       </c>
       <c r="AV31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX31" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>4.4</v>
       </c>
       <c r="AY31" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD31" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF31" t="n">
         <v>25</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
         <v>3.05</v>
       </c>
       <c r="H32" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I32" t="n">
         <v>2.7</v>
@@ -6607,19 +6607,19 @@
         <v>1.35</v>
       </c>
       <c r="P32" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R32" t="n">
         <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T32" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U32" t="n">
         <v>2.18</v>
@@ -6658,7 +6658,7 @@
         <v>21</v>
       </c>
       <c r="AG32" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH32" t="n">
         <v>17</v>
@@ -6673,13 +6673,13 @@
         <v>36</v>
       </c>
       <c r="AL32" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM32" t="n">
         <v>95</v>
       </c>
       <c r="AN32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO32" t="n">
         <v>26</v>
@@ -6715,22 +6715,22 @@
         <v>12</v>
       </c>
       <c r="AZ32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA32" t="n">
         <v>36</v>
       </c>
       <c r="BB32" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="BC32" t="n">
         <v>29</v>
       </c>
       <c r="BD32" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="BE32" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BF32" t="n">
         <v>27</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
         <v>2.96</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
         <v>2.48</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
         <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -7019,10 +7019,10 @@
         <v>1.72</v>
       </c>
       <c r="X34" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y34" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z34" t="n">
         <v>34</v>
@@ -7031,10 +7031,10 @@
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD34" t="n">
         <v>22</v>
@@ -7043,10 +7043,10 @@
         <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG34" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH34" t="n">
         <v>32</v>
@@ -7082,7 +7082,7 @@
         <v>5.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AT34" t="n">
         <v>3.25</v>
@@ -7094,7 +7094,7 @@
         <v>4.7</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.02</v>
+        <v>1.59</v>
       </c>
       <c r="AX34" t="n">
         <v>4.2</v>
@@ -7106,7 +7106,7 @@
         <v>5.1</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BB34" t="n">
         <v>5.2</v>
@@ -7115,10 +7115,10 @@
         <v>5.3</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BF34" t="n">
         <v>5.3</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -7356,16 +7356,16 @@
         <v>1.04</v>
       </c>
       <c r="G36" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H36" t="n">
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J36" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K36" t="n">
         <v>950</v>
@@ -7386,7 +7386,7 @@
         <v>1.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R36" t="n">
         <v>1.16</v>
@@ -7395,10 +7395,10 @@
         <v>1.3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
@@ -7461,62 +7461,62 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G37" t="n">
         <v>2.36</v>
@@ -7577,10 +7577,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
         <v>990</v>
       </c>
       <c r="J38" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K38" t="n">
         <v>950</v>
@@ -7765,7 +7765,7 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O38" t="n">
         <v>1.01</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
         <v>990</v>
       </c>
       <c r="J39" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K39" t="n">
         <v>950</v>
@@ -7974,7 +7974,7 @@
         <v>1.12</v>
       </c>
       <c r="S39" t="n">
-        <v>1.48</v>
+        <v>1.05</v>
       </c>
       <c r="T39" t="n">
         <v>1.11</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -8138,13 +8138,13 @@
         <v>2.96</v>
       </c>
       <c r="I40" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K40" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L40" t="n">
         <v>1.5</v>
@@ -8171,16 +8171,16 @@
         <v>4.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U40" t="n">
         <v>1.79</v>
       </c>
       <c r="V40" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W40" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X40" t="n">
         <v>90</v>
@@ -8240,59 +8240,59 @@
         <v>6.8</v>
       </c>
       <c r="AQ40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.94</v>
+        <v>2.26</v>
       </c>
       <c r="AT40" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AV40" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="AW40" t="n">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="AX40" t="n">
-        <v>2.68</v>
+        <v>2.1</v>
       </c>
       <c r="AY40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.96</v>
+        <v>2.28</v>
       </c>
       <c r="BB40" t="n">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.88</v>
+        <v>2.22</v>
       </c>
       <c r="BD40" t="n">
-        <v>2.94</v>
+        <v>2.28</v>
       </c>
       <c r="BE40" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="BF40" t="n">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="BG40" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
         <v>2.96</v>
       </c>
       <c r="K41" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L41" t="n">
         <v>1.47</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
         <v>7.4</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AS42" t="n">
         <v>4.5</v>
@@ -8664,13 +8664,13 @@
         <v>4.3</v>
       </c>
       <c r="BC42" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF42" t="n">
         <v>4.3</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
         <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J43" t="n">
         <v>3</v>
@@ -8732,13 +8732,13 @@
         <v>1.46</v>
       </c>
       <c r="M43" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N43" t="n">
         <v>2.66</v>
       </c>
       <c r="O43" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="P43" t="n">
         <v>1.56</v>
@@ -8750,7 +8750,7 @@
         <v>1.2</v>
       </c>
       <c r="S43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T43" t="n">
         <v>2.08</v>
@@ -8759,7 +8759,7 @@
         <v>1.79</v>
       </c>
       <c r="V43" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W43" t="n">
         <v>1.73</v>
@@ -8786,7 +8786,7 @@
         <v>21</v>
       </c>
       <c r="AE43" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
         <v>16</v>
@@ -8825,10 +8825,10 @@
         <v>9.6</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT43" t="n">
         <v>6.4</v>
@@ -8852,29 +8852,29 @@
         <v>20</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB43" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC43" t="n">
         <v>4.7</v>
       </c>
       <c r="BD43" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF43" t="n">
         <v>4.7</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -8908,16 +8908,16 @@
         <v>1.58</v>
       </c>
       <c r="G44" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="H44" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I44" t="n">
         <v>6.8</v>
       </c>
       <c r="J44" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K44" t="n">
         <v>4.7</v>
@@ -8935,10 +8935,10 @@
         <v>1.21</v>
       </c>
       <c r="P44" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R44" t="n">
         <v>1.56</v>
@@ -8956,7 +8956,7 @@
         <v>1.17</v>
       </c>
       <c r="W44" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="X44" t="n">
         <v>21</v>
@@ -8986,7 +8986,7 @@
         <v>11</v>
       </c>
       <c r="AG44" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH44" t="n">
         <v>19.5</v>
@@ -9001,7 +9001,7 @@
         <v>15</v>
       </c>
       <c r="AL44" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM44" t="n">
         <v>95</v>
@@ -9019,10 +9019,10 @@
         <v>24</v>
       </c>
       <c r="AR44" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT44" t="n">
         <v>9.800000000000001</v>
@@ -9037,7 +9037,7 @@
         <v>65</v>
       </c>
       <c r="AX44" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY44" t="n">
         <v>9.4</v>
@@ -9046,16 +9046,16 @@
         <v>17.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BB44" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC44" t="n">
         <v>13.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE44" t="n">
         <v>80</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -9102,10 +9102,10 @@
         <v>1.04</v>
       </c>
       <c r="G45" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="H45" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="I45" t="n">
         <v>1000</v>
@@ -9123,7 +9123,7 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O45" t="n">
         <v>1.01</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9305,7 @@
         <v>990</v>
       </c>
       <c r="J46" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K46" t="n">
         <v>950</v>
@@ -9317,7 +9317,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O46" t="n">
         <v>1.01</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -9681,16 +9681,16 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G48" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H48" t="n">
         <v>3.7</v>
       </c>
       <c r="I48" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J48" t="n">
         <v>2.8</v>
@@ -9729,10 +9729,10 @@
         <v>1.69</v>
       </c>
       <c r="V48" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W48" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X48" t="n">
         <v>9.800000000000001</v>
@@ -9750,13 +9750,13 @@
         <v>8.4</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD48" t="n">
         <v>22</v>
       </c>
       <c r="AE48" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF48" t="n">
         <v>16</v>
@@ -9771,7 +9771,7 @@
         <v>120</v>
       </c>
       <c r="AJ48" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK48" t="n">
         <v>42</v>
@@ -9780,25 +9780,25 @@
         <v>80</v>
       </c>
       <c r="AM48" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN48" t="n">
         <v>44</v>
       </c>
       <c r="AO48" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP48" t="n">
         <v>6</v>
       </c>
       <c r="AQ48" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR48" t="n">
         <v>19.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT48" t="n">
         <v>5.3</v>
@@ -9810,7 +9810,7 @@
         <v>13</v>
       </c>
       <c r="AW48" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX48" t="n">
         <v>9.6</v>
@@ -9822,29 +9822,29 @@
         <v>17.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB48" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="BC48" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF48" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BG48" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -9875,100 +9875,100 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="G49" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="H49" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I49" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="J49" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="K49" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="L49" t="n">
         <v>1.48</v>
       </c>
       <c r="M49" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N49" t="n">
-        <v>1.37</v>
+        <v>2.44</v>
       </c>
       <c r="O49" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="P49" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="R49" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="S49" t="n">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="T49" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U49" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V49" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W49" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y49" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA49" t="n">
         <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC49" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF49" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI49" t="n">
         <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK49" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL49" t="n">
         <v>1000</v>
@@ -9977,68 +9977,68 @@
         <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO49" t="n">
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -10081,7 +10081,7 @@
         <v>1000</v>
       </c>
       <c r="J50" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K50" t="n">
         <v>950</v>
@@ -10093,7 +10093,7 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O50" t="n">
         <v>1.01</v>
@@ -10102,7 +10102,7 @@
         <v>1.24</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R50" t="n">
         <v>1.12</v>
@@ -10177,62 +10177,62 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>2.18</v>
       </c>
       <c r="G51" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="H51" t="n">
         <v>3.2</v>
@@ -10293,7 +10293,7 @@
         <v>1.38</v>
       </c>
       <c r="P51" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q51" t="n">
         <v>2.02</v>
@@ -10314,7 +10314,7 @@
         <v>1.3</v>
       </c>
       <c r="W51" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="X51" t="n">
         <v>90</v>
@@ -10371,62 +10371,62 @@
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.55</v>
+        <v>1.02</v>
       </c>
       <c r="BG51" t="n">
-        <v>2.26</v>
+        <v>1.02</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -10457,58 +10457,58 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G52" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="H52" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I52" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J52" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K52" t="n">
-        <v>85</v>
+        <v>4.4</v>
       </c>
       <c r="L52" t="n">
         <v>1.34</v>
       </c>
       <c r="M52" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N52" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O52" t="n">
         <v>1.31</v>
       </c>
       <c r="P52" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="R52" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S52" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="T52" t="n">
         <v>1.78</v>
       </c>
       <c r="U52" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="V52" t="n">
         <v>1.15</v>
       </c>
       <c r="W52" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X52" t="n">
         <v>970</v>
@@ -10541,7 +10541,7 @@
         <v>970</v>
       </c>
       <c r="AH52" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI52" t="n">
         <v>1000</v>
@@ -10565,28 +10565,28 @@
         <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AR52" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AS52" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AT52" t="n">
         <v>3</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AV52" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AW52" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AX52" t="n">
         <v>3.2</v>
@@ -10595,32 +10595,32 @@
         <v>3.2</v>
       </c>
       <c r="AZ52" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BA52" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="BB52" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="BC52" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BE52" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BF52" t="n">
         <v>3.35</v>
       </c>
       <c r="BG52" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -10651,10 +10651,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G53" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H53" t="n">
         <v>3.65</v>
@@ -10672,19 +10672,19 @@
         <v>1.45</v>
       </c>
       <c r="M53" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N53" t="n">
         <v>2.68</v>
       </c>
       <c r="O53" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P53" t="n">
         <v>1.62</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R53" t="n">
         <v>1.22</v>
@@ -10759,7 +10759,7 @@
         <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ53" t="n">
         <v>4.2</v>
@@ -10768,13 +10768,13 @@
         <v>5</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV53" t="n">
         <v>4.5</v>
@@ -10789,32 +10789,32 @@
         <v>4</v>
       </c>
       <c r="AZ53" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="BB53" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC53" t="n">
         <v>5</v>
       </c>
       <c r="BD53" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BF53" t="n">
         <v>5</v>
       </c>
       <c r="BG53" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -10863,13 +10863,13 @@
         <v>3.4</v>
       </c>
       <c r="L54" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M54" t="n">
         <v>1.08</v>
       </c>
       <c r="N54" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O54" t="n">
         <v>1.35</v>
@@ -10881,10 +10881,10 @@
         <v>2.08</v>
       </c>
       <c r="R54" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S54" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T54" t="n">
         <v>1.78</v>
@@ -10902,19 +10902,19 @@
         <v>13.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z54" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA54" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB54" t="n">
         <v>11.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD54" t="n">
         <v>13.5</v>
@@ -10962,7 +10962,7 @@
         <v>16</v>
       </c>
       <c r="AS54" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT54" t="n">
         <v>9.6</v>
@@ -10974,7 +10974,7 @@
         <v>11</v>
       </c>
       <c r="AW54" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX54" t="n">
         <v>16</v>
@@ -10986,29 +10986,29 @@
         <v>15</v>
       </c>
       <c r="BA54" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB54" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC54" t="n">
         <v>30</v>
       </c>
       <c r="BD54" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE54" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF54" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG54" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -11039,22 +11039,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G55" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="H55" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="J55" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K55" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -11063,34 +11063,34 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>1.56</v>
+        <v>2.54</v>
       </c>
       <c r="O55" t="n">
         <v>1.39</v>
       </c>
       <c r="P55" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R55" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S55" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T55" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U55" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V55" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="W55" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -11236,13 +11236,13 @@
         <v>2.06</v>
       </c>
       <c r="G56" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H56" t="n">
         <v>4.3</v>
       </c>
       <c r="I56" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J56" t="n">
         <v>3.4</v>
@@ -11263,7 +11263,7 @@
         <v>1.4</v>
       </c>
       <c r="P56" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q56" t="n">
         <v>2.2</v>
@@ -11272,19 +11272,19 @@
         <v>1.29</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T56" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U56" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V56" t="n">
         <v>1.28</v>
       </c>
       <c r="W56" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="X56" t="n">
         <v>11.5</v>
@@ -11332,7 +11332,7 @@
         <v>46</v>
       </c>
       <c r="AM56" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN56" t="n">
         <v>18.5</v>
@@ -11353,7 +11353,7 @@
         <v>38</v>
       </c>
       <c r="AT56" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU56" t="n">
         <v>7</v>
@@ -11368,7 +11368,7 @@
         <v>10.5</v>
       </c>
       <c r="AY56" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ56" t="n">
         <v>18</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -11445,7 +11445,7 @@
         <v>3.95</v>
       </c>
       <c r="L57" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M57" t="n">
         <v>1.09</v>
@@ -11460,7 +11460,7 @@
         <v>1.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R57" t="n">
         <v>1.26</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
         <v>3.5</v>
       </c>
       <c r="L58" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M58" t="n">
         <v>1.08</v>
@@ -11669,7 +11669,7 @@
         <v>2.04</v>
       </c>
       <c r="V58" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W58" t="n">
         <v>1.37</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -11815,58 +11815,58 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.38</v>
+        <v>1.99</v>
       </c>
       <c r="G59" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="H59" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I59" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
-        <v>1.09</v>
+        <v>2.9</v>
       </c>
       <c r="K59" t="n">
         <v>3.75</v>
       </c>
       <c r="L59" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M59" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N59" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="O59" t="n">
         <v>1.35</v>
       </c>
       <c r="P59" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V59" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q59" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S59" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W59" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         <v>3.4</v>
       </c>
       <c r="L60" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M60" t="n">
         <v>1.08</v>
@@ -12039,10 +12039,10 @@
         <v>1.35</v>
       </c>
       <c r="P60" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R60" t="n">
         <v>1.31</v>
@@ -12069,10 +12069,10 @@
         <v>11</v>
       </c>
       <c r="Z60" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA60" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB60" t="n">
         <v>11.5</v>
@@ -12084,7 +12084,7 @@
         <v>13</v>
       </c>
       <c r="AE60" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF60" t="n">
         <v>21</v>
@@ -12111,7 +12111,7 @@
         <v>120</v>
       </c>
       <c r="AN60" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO60" t="n">
         <v>38</v>
@@ -12126,19 +12126,19 @@
         <v>14.5</v>
       </c>
       <c r="AS60" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT60" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU60" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV60" t="n">
         <v>10.5</v>
       </c>
       <c r="AW60" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX60" t="n">
         <v>16.5</v>
@@ -12150,29 +12150,29 @@
         <v>15</v>
       </c>
       <c r="BA60" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB60" t="n">
         <v>40</v>
       </c>
       <c r="BC60" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD60" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BE60" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF60" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG60" t="n">
         <v>21</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="G2" t="n">
         <v>5.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="I2" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.54</v>
@@ -781,146 +781,146 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
         <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V2" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="n">
         <v>24</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG2" t="n">
         <v>24</v>
       </c>
-      <c r="AF2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>23</v>
-      </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AL2" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AO2" t="n">
         <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>16.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="AY2" t="n">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.1</v>
+        <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.8</v>
+        <v>34</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.52</v>
+        <v>11.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.54</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="G3" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z3" t="n">
         <v>18.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3" t="n">
         <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF3" t="n">
         <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
         <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AO3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT3" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8</v>
-      </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AX3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="BB3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BC3" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BE3" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="BF3" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BG3" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -1151,82 +1151,82 @@
         <v>3.65</v>
       </c>
       <c r="H4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.54</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
         <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA4" t="n">
         <v>42</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC4" t="n">
         <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
         <v>23</v>
@@ -1235,34 +1235,34 @@
         <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="n">
         <v>55</v>
       </c>
       <c r="AL4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
         <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO4" t="n">
         <v>34</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
         <v>9.6</v>
@@ -1274,41 +1274,41 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.5</v>
+        <v>22</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -1342,88 +1342,88 @@
         <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H5" t="n">
         <v>6.4</v>
       </c>
       <c r="I5" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.35</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.92</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.85</v>
       </c>
       <c r="U5" t="n">
         <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z5" t="n">
         <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
         <v>120</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
         <v>110</v>
@@ -1432,7 +1432,7 @@
         <v>970</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AL5" t="n">
         <v>42</v>
@@ -1441,68 +1441,68 @@
         <v>160</v>
       </c>
       <c r="AN5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP5" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="AS5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY5" t="n">
         <v>5.6</v>
       </c>
-      <c r="AT5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW5" t="n">
+      <c r="AZ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB5" t="n">
         <v>7</v>
       </c>
-      <c r="AX5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA5" t="n">
+      <c r="BC5" t="n">
         <v>7</v>
       </c>
-      <c r="BB5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="G6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H6" t="n">
         <v>7.6</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
         <v>5.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
         <v>1.91</v>
@@ -1581,10 +1581,10 @@
         <v>1.89</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X6" t="n">
         <v>24</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
         <v>19</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1647,10 +1647,10 @@
         <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT6" t="n">
         <v>6.6</v>
@@ -1659,10 +1659,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX6" t="n">
         <v>6.8</v>
@@ -1671,32 +1671,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
         <v>9.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF6" t="n">
         <v>5.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -1727,46 +1727,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="G7" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="R7" t="n">
         <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="T7" t="n">
         <v>1.73</v>
@@ -1778,7 +1778,7 @@
         <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
@@ -1805,7 +1805,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -1829,52 +1829,52 @@
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO7" t="n">
         <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AR7" t="n">
         <v>5.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT7" t="n">
         <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW7" t="n">
         <v>5.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AZ7" t="n">
         <v>4.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB7" t="n">
         <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD7" t="n">
         <v>5.1</v>
@@ -1883,14 +1883,14 @@
         <v>5.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG7" t="n">
         <v>5.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M8" t="n">
         <v>1.13</v>
@@ -1948,34 +1948,34 @@
         <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
         <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="n">
         <v>9.6</v>
@@ -1984,7 +1984,7 @@
         <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB8" t="n">
         <v>7.8</v>
@@ -2008,13 +2008,13 @@
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
         <v>65</v>
@@ -2023,13 +2023,13 @@
         <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
         <v>9</v>
@@ -2047,7 +2047,7 @@
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW8" t="n">
         <v>46</v>
@@ -2059,13 +2059,13 @@
         <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="BB8" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BC8" t="n">
         <v>32</v>
@@ -2077,14 +2077,14 @@
         <v>17.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -2124,34 +2124,34 @@
         <v>2.34</v>
       </c>
       <c r="I9" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J9" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.45</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
         <v>4.5</v>
@@ -2181,7 +2181,7 @@
         <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
         <v>7.6</v>
@@ -2190,7 +2190,7 @@
         <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AF9" t="n">
         <v>25</v>
@@ -2220,10 +2220,10 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>7.2</v>
@@ -2235,7 +2235,7 @@
         <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9" t="n">
         <v>6.2</v>
@@ -2244,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AX9" t="n">
         <v>19.5</v>
@@ -2259,7 +2259,7 @@
         <v>18.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC9" t="n">
         <v>7.4</v>
@@ -2268,17 +2268,17 @@
         <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -2312,22 +2312,22 @@
         <v>2.64</v>
       </c>
       <c r="G10" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2336,31 +2336,31 @@
         <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P10" t="n">
         <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
         <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X10" t="n">
         <v>90</v>
@@ -2390,7 +2390,7 @@
         <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
         <v>1000</v>
@@ -2420,16 +2420,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR10" t="n">
         <v>15.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10" t="n">
         <v>6.6</v>
@@ -2450,7 +2450,7 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB10" t="n">
         <v>7.6</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G11" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H11" t="n">
         <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
         <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
         <v>1.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U11" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -2569,7 +2569,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
@@ -2608,19 +2608,19 @@
         <v>22</v>
       </c>
       <c r="AO11" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT11" t="n">
         <v>6.6</v>
@@ -2632,7 +2632,7 @@
         <v>15.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX11" t="n">
         <v>9.199999999999999</v>
@@ -2650,23 +2650,23 @@
         <v>19.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
         <v>16</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>1.87</v>
       </c>
       <c r="G12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
@@ -2715,13 +2715,13 @@
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.37</v>
@@ -2730,13 +2730,13 @@
         <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
         <v>1.9</v>
@@ -2748,7 +2748,7 @@
         <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2763,7 +2763,7 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
         <v>1000</v>
@@ -2805,19 +2805,19 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR12" t="n">
         <v>7.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU12" t="n">
         <v>6.8</v>
@@ -2826,10 +2826,10 @@
         <v>6.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="AX12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AY12" t="n">
         <v>4.9</v>
@@ -2838,7 +2838,7 @@
         <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="BB12" t="n">
         <v>6.4</v>
@@ -2856,11 +2856,11 @@
         <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>1.93</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
         <v>5.2</v>
@@ -2906,28 +2906,28 @@
         <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>1.35</v>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
         <v>2.06</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
         <v>3.7</v>
@@ -2939,10 +2939,10 @@
         <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X13" t="n">
         <v>15.5</v>
@@ -2951,19 +2951,19 @@
         <v>16</v>
       </c>
       <c r="Z13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC13" t="n">
         <v>8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
@@ -2987,7 +2987,7 @@
         <v>24</v>
       </c>
       <c r="AL13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -2996,10 +2996,10 @@
         <v>18</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
         <v>13.5</v>
@@ -3008,10 +3008,10 @@
         <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
@@ -3044,7 +3044,7 @@
         <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
         <v>11.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G14" t="n">
         <v>4.9</v>
       </c>
       <c r="H14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.48</v>
@@ -3115,10 +3115,10 @@
         <v>1.41</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R14" t="n">
         <v>1.27</v>
@@ -3127,37 +3127,37 @@
         <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="W14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB14" t="n">
         <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
         <v>28</v>
@@ -3196,59 +3196,59 @@
         <v>9.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AT14" t="n">
         <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>6</v>
       </c>
       <c r="BA14" t="n">
         <v>7</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD14" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7.2</v>
       </c>
       <c r="BE14" t="n">
         <v>40</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -3285,46 +3285,46 @@
         <v>12</v>
       </c>
       <c r="H15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L15" t="n">
         <v>1.47</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.38</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
         <v>3.45</v>
       </c>
       <c r="T15" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="V15" t="n">
         <v>2.6</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AR15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AX15" t="n">
         <v>3.4</v>
       </c>
-      <c r="AS15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AY15" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -3473,46 +3473,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.02</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
-        <v>1.02</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="J16" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.15</v>
+        <v>1.96</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>1.32</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -3521,10 +3521,10 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -3667,64 +3667,64 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="H17" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="V17" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="X17" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3733,37 +3733,37 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AK17" t="n">
         <v>21</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.6</v>
+        <v>3.25</v>
       </c>
       <c r="AV17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW17" t="n">
         <v>4.3</v>
       </c>
-      <c r="AW17" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AX17" t="n">
-        <v>6.8</v>
+        <v>3.15</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>14.5</v>
+        <v>3.65</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.4</v>
+        <v>3.1</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -3861,49 +3861,49 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="G18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H18" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="I18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="K18" t="n">
         <v>7.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
         <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R18" t="n">
         <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T18" t="n">
-        <v>2.92</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
         <v>1.41</v>
@@ -3912,10 +3912,10 @@
         <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="X18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="n">
         <v>60</v>
@@ -3939,7 +3939,7 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AG18" t="n">
         <v>15</v>
@@ -3951,7 +3951,7 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AK18" t="n">
         <v>21</v>
@@ -3963,68 +3963,68 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>13</v>
+        <v>5.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="AV18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>6.8</v>
       </c>
-      <c r="AW18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BA18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>15.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.41</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H19" t="n">
         <v>6.8</v>
@@ -4106,7 +4106,7 @@
         <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="G20" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE20" t="n">
         <v>3.7</v>
       </c>
-      <c r="I20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA20" t="n">
+      <c r="BF20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG20" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4446,19 @@
         <v>1.65</v>
       </c>
       <c r="G21" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="H21" t="n">
-        <v>1.09</v>
+        <v>5.7</v>
       </c>
       <c r="I21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21" t="n">
         <v>3.1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.5</v>
@@ -4470,7 +4470,7 @@
         <v>2.38</v>
       </c>
       <c r="O21" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P21" t="n">
         <v>1.46</v>
@@ -4482,19 +4482,19 @@
         <v>1.16</v>
       </c>
       <c r="S21" t="n">
-        <v>1.56</v>
+        <v>3.45</v>
       </c>
       <c r="T21" t="n">
         <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V21" t="n">
         <v>1.14</v>
       </c>
       <c r="W21" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4560,7 +4560,7 @@
         <v>1.53</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AT21" t="n">
         <v>3.15</v>
@@ -4596,17 +4596,17 @@
         <v>1.32</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BF21" t="n">
         <v>4.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G22" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="H22" t="n">
         <v>3.05</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J22" t="n">
         <v>3.5</v>
@@ -4655,46 +4655,46 @@
         <v>3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P22" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W22" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X22" t="n">
         <v>12.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
         <v>20</v>
@@ -4703,16 +4703,16 @@
         <v>55</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
         <v>13.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF22" t="n">
         <v>16</v>
@@ -4721,34 +4721,34 @@
         <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
         <v>38</v>
       </c>
       <c r="AK22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN22" t="n">
         <v>28</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AO22" t="n">
         <v>42</v>
       </c>
-      <c r="AM22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>36</v>
-      </c>
       <c r="AP22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
         <v>18</v>
@@ -4757,16 +4757,16 @@
         <v>46</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AX22" t="n">
         <v>14.5</v>
@@ -4775,7 +4775,7 @@
         <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
         <v>24</v>
@@ -4784,23 +4784,23 @@
         <v>32</v>
       </c>
       <c r="BC22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BF22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BG22" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -4831,73 +4831,73 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G23" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U23" t="n">
         <v>2.1</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="X23" t="n">
         <v>18.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC23" t="n">
         <v>10.5</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG23" t="n">
         <v>11</v>
@@ -4927,13 +4927,13 @@
         <v>21</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
@@ -4945,56 +4945,56 @@
         <v>14.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.1</v>
+        <v>46</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.9</v>
+        <v>25</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BF23" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.2</v>
+        <v>55</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -5025,170 +5025,170 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="J24" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.42</v>
+        <v>1.96</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.02</v>
+        <v>3.95</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.02</v>
+        <v>5.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.02</v>
+        <v>5.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.02</v>
+        <v>5.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.02</v>
+        <v>5.3</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -5219,46 +5219,46 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H25" t="n">
         <v>2.94</v>
       </c>
       <c r="I25" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K25" t="n">
         <v>3.65</v>
       </c>
       <c r="L25" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P25" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T25" t="n">
         <v>1.79</v>
@@ -5267,25 +5267,25 @@
         <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W25" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X25" t="n">
         <v>15</v>
       </c>
       <c r="Y25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
         <v>26</v>
       </c>
       <c r="AA25" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC25" t="n">
         <v>9.199999999999999</v>
@@ -5294,13 +5294,13 @@
         <v>17</v>
       </c>
       <c r="AE25" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF25" t="n">
         <v>20</v>
       </c>
       <c r="AG25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
         <v>22</v>
@@ -5324,65 +5324,65 @@
         <v>34</v>
       </c>
       <c r="AO25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP25" t="n">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>15.5</v>
+        <v>3.9</v>
       </c>
       <c r="AS25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF25" t="n">
         <v>4</v>
       </c>
-      <c r="AT25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BG25" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -5413,25 +5413,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G26" t="n">
         <v>2.52</v>
       </c>
       <c r="H26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I26" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
@@ -5443,31 +5443,31 @@
         <v>1.42</v>
       </c>
       <c r="P26" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R26" t="n">
         <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T26" t="n">
         <v>1.91</v>
       </c>
       <c r="U26" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V26" t="n">
         <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y26" t="n">
         <v>12</v>
@@ -5476,7 +5476,7 @@
         <v>26</v>
       </c>
       <c r="AA26" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AB26" t="n">
         <v>9.800000000000001</v>
@@ -5485,19 +5485,19 @@
         <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI26" t="n">
         <v>65</v>
@@ -5509,74 +5509,74 @@
         <v>32</v>
       </c>
       <c r="AL26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM26" t="n">
         <v>160</v>
       </c>
       <c r="AN26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO26" t="n">
         <v>60</v>
       </c>
       <c r="AP26" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR26" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA26" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BB26" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G27" t="n">
         <v>2.1</v>
@@ -5616,46 +5616,46 @@
         <v>4.3</v>
       </c>
       <c r="I27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
         <v>3.45</v>
       </c>
       <c r="L27" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="M27" t="n">
         <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O27" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="R27" t="n">
         <v>1.21</v>
       </c>
       <c r="S27" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="U27" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="V27" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W27" t="n">
         <v>1.91</v>
@@ -5664,22 +5664,22 @@
         <v>90</v>
       </c>
       <c r="Y27" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z27" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA27" t="n">
         <v>130</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AC27" t="n">
         <v>8.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE27" t="n">
         <v>85</v>
@@ -5721,56 +5721,56 @@
         <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="AU27" t="n">
         <v>6</v>
       </c>
       <c r="AV27" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="BA27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB27" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB27" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BC27" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BF27" t="n">
         <v>6</v>
       </c>
-      <c r="BE27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG27" t="n">
-        <v>4</v>
+        <v>2.52</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -5804,67 +5804,67 @@
         <v>2.68</v>
       </c>
       <c r="G28" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H28" t="n">
         <v>2.94</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J28" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L28" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="M28" t="n">
         <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P28" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R28" t="n">
         <v>1.19</v>
       </c>
       <c r="S28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="U28" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="V28" t="n">
         <v>1.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X28" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z28" t="n">
         <v>21</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB28" t="n">
         <v>8.800000000000001</v>
@@ -5873,7 +5873,7 @@
         <v>7.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
@@ -5888,7 +5888,7 @@
         <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
         <v>50</v>
@@ -5906,10 +5906,10 @@
         <v>48</v>
       </c>
       <c r="AO28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ28" t="n">
         <v>7.8</v>
@@ -5918,7 +5918,7 @@
         <v>14.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT28" t="n">
         <v>7.2</v>
@@ -5930,7 +5930,7 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX28" t="n">
         <v>14</v>
@@ -5942,29 +5942,29 @@
         <v>18.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BC28" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BG28" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G29" t="n">
         <v>2.46</v>
@@ -6004,37 +6004,37 @@
         <v>3.4</v>
       </c>
       <c r="I29" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K29" t="n">
         <v>3.65</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
         <v>1.34</v>
       </c>
       <c r="P29" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T29" t="n">
         <v>1.76</v>
@@ -6043,122 +6043,122 @@
         <v>2.06</v>
       </c>
       <c r="V29" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W29" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X29" t="n">
         <v>14.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA29" t="n">
         <v>75</v>
       </c>
       <c r="AB29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD29" t="n">
         <v>970</v>
       </c>
       <c r="AE29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF29" t="n">
         <v>970</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ29" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK29" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL29" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
         <v>12</v>
       </c>
       <c r="AW29" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="AX29" t="n">
         <v>11.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AZ29" t="n">
         <v>13</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.1</v>
+        <v>40</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BG29" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -6192,43 +6192,43 @@
         <v>2.2</v>
       </c>
       <c r="G30" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H30" t="n">
         <v>3.75</v>
       </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J30" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="K30" t="n">
         <v>3.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O30" t="n">
         <v>1.42</v>
       </c>
       <c r="P30" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q30" t="n">
         <v>2.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T30" t="n">
         <v>1.82</v>
@@ -6237,10 +6237,10 @@
         <v>1.79</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X30" t="n">
         <v>12</v>
@@ -6264,7 +6264,7 @@
         <v>19</v>
       </c>
       <c r="AE30" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF30" t="n">
         <v>970</v>
@@ -6276,7 +6276,7 @@
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
         <v>36</v>
@@ -6294,22 +6294,22 @@
         <v>29</v>
       </c>
       <c r="AO30" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR30" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AS30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU30" t="n">
         <v>5.9</v>
@@ -6318,41 +6318,41 @@
         <v>12.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AY30" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>15.5</v>
+        <v>5</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB30" t="n">
         <v>6.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="BE30" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BG30" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -6386,13 +6386,13 @@
         <v>2.4</v>
       </c>
       <c r="G31" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="H31" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J31" t="n">
         <v>3.05</v>
@@ -6401,46 +6401,46 @@
         <v>3.35</v>
       </c>
       <c r="L31" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="M31" t="n">
         <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="O31" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P31" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R31" t="n">
         <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U31" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V31" t="n">
         <v>1.37</v>
       </c>
       <c r="W31" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="X31" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z31" t="n">
         <v>24</v>
@@ -6449,10 +6449,10 @@
         <v>80</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD31" t="n">
         <v>970</v>
@@ -6473,10 +6473,10 @@
         <v>80</v>
       </c>
       <c r="AJ31" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL31" t="n">
         <v>65</v>
@@ -6488,65 +6488,65 @@
         <v>38</v>
       </c>
       <c r="AO31" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP31" t="n">
         <v>6.8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AR31" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AT31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX31" t="n">
         <v>6</v>
       </c>
-      <c r="AU31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AY31" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF31" t="n">
-        <v>25</v>
+        <v>7.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G32" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J32" t="n">
         <v>3.4</v>
@@ -6595,31 +6595,31 @@
         <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O32" t="n">
         <v>1.35</v>
       </c>
       <c r="P32" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S32" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T32" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U32" t="n">
         <v>2.18</v>
@@ -6628,7 +6628,7 @@
         <v>1.58</v>
       </c>
       <c r="W32" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X32" t="n">
         <v>13</v>
@@ -6637,7 +6637,7 @@
         <v>11</v>
       </c>
       <c r="Z32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA32" t="n">
         <v>40</v>
@@ -6652,13 +6652,13 @@
         <v>12</v>
       </c>
       <c r="AE32" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF32" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH32" t="n">
         <v>17</v>
@@ -6670,7 +6670,7 @@
         <v>50</v>
       </c>
       <c r="AK32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL32" t="n">
         <v>48</v>
@@ -6700,7 +6700,7 @@
         <v>10.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV32" t="n">
         <v>11</v>
@@ -6709,7 +6709,7 @@
         <v>25</v>
       </c>
       <c r="AX32" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AY32" t="n">
         <v>12</v>
@@ -6718,29 +6718,29 @@
         <v>14.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="BB32" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BC32" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD32" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BE32" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="BF32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -6771,46 +6771,46 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="G33" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="H33" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="K33" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N33" t="n">
-        <v>1.94</v>
+        <v>2.44</v>
       </c>
       <c r="O33" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="P33" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="R33" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S33" t="n">
-        <v>2.92</v>
+        <v>5.5</v>
       </c>
       <c r="T33" t="n">
         <v>1.11</v>
@@ -6819,10 +6819,10 @@
         <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="W33" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -6971,34 +6971,34 @@
         <v>2.38</v>
       </c>
       <c r="H34" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I34" t="n">
         <v>4.9</v>
       </c>
       <c r="J34" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="K34" t="n">
         <v>3.2</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="M34" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N34" t="n">
         <v>2.28</v>
       </c>
       <c r="O34" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="P34" t="n">
         <v>1.42</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="R34" t="n">
         <v>1.14</v>
@@ -7013,7 +7013,7 @@
         <v>1.63</v>
       </c>
       <c r="V34" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W34" t="n">
         <v>1.72</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K35" t="n">
         <v>950</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -7550,16 +7550,16 @@
         <v>2.14</v>
       </c>
       <c r="G37" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H37" t="n">
         <v>3.95</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J37" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K37" t="n">
         <v>3.3</v>
@@ -7577,10 +7577,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
         <v>1.01</v>
       </c>
       <c r="R38" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S38" t="n">
         <v>1.05</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O39" t="n">
         <v>1.01</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -8129,31 +8129,31 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="G40" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J40" t="n">
         <v>2.94</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.88</v>
       </c>
       <c r="K40" t="n">
         <v>3.25</v>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="M40" t="n">
         <v>1.12</v>
       </c>
       <c r="N40" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="O40" t="n">
         <v>1.53</v>
@@ -8162,13 +8162,13 @@
         <v>1.53</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="R40" t="n">
         <v>1.19</v>
       </c>
       <c r="S40" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T40" t="n">
         <v>2.02</v>
@@ -8177,7 +8177,7 @@
         <v>1.79</v>
       </c>
       <c r="V40" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W40" t="n">
         <v>1.52</v>
@@ -8243,10 +8243,10 @@
         <v>4.4</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AT40" t="n">
         <v>4.1</v>
@@ -8258,7 +8258,7 @@
         <v>3.1</v>
       </c>
       <c r="AW40" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AX40" t="n">
         <v>2.1</v>
@@ -8267,32 +8267,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BB40" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BC40" t="n">
         <v>2.24</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>2.22</v>
       </c>
       <c r="BD40" t="n">
         <v>2.28</v>
       </c>
       <c r="BE40" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BF40" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BG40" t="n">
         <v>7.4</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -8323,40 +8323,40 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H41" t="n">
         <v>2.64</v>
       </c>
       <c r="I41" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J41" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L41" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M41" t="n">
         <v>1.12</v>
       </c>
       <c r="N41" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O41" t="n">
         <v>1.52</v>
       </c>
       <c r="P41" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="R41" t="n">
         <v>1.19</v>
@@ -8428,10 +8428,10 @@
         <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ41" t="n">
         <v>6.8</v>
@@ -8467,16 +8467,16 @@
         <v>48</v>
       </c>
       <c r="BB41" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC41" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD41" t="n">
         <v>55</v>
       </c>
       <c r="BE41" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF41" t="n">
         <v>8.199999999999999</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -8517,43 +8517,43 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G42" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="H42" t="n">
         <v>3.3</v>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="J42" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="K42" t="n">
         <v>3.4</v>
       </c>
       <c r="L42" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
         <v>1.11</v>
       </c>
       <c r="N42" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="O42" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P42" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="R42" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -8565,10 +8565,10 @@
         <v>1.75</v>
       </c>
       <c r="V42" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W42" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="X42" t="n">
         <v>11</v>
@@ -8598,7 +8598,7 @@
         <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
         <v>1000</v>
@@ -8628,16 +8628,16 @@
         <v>6.6</v>
       </c>
       <c r="AQ42" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR42" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT42" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU42" t="n">
         <v>5.4</v>
@@ -8646,7 +8646,7 @@
         <v>11</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AX42" t="n">
         <v>11</v>
@@ -8655,32 +8655,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BC42" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -8711,46 +8711,46 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G43" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H43" t="n">
         <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K43" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L43" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N43" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O43" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="P43" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="R43" t="n">
         <v>1.2</v>
       </c>
       <c r="S43" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T43" t="n">
         <v>2.08</v>
@@ -8759,10 +8759,10 @@
         <v>1.79</v>
       </c>
       <c r="V43" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W43" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X43" t="n">
         <v>11</v>
@@ -8789,7 +8789,7 @@
         <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG43" t="n">
         <v>14</v>
@@ -8801,19 +8801,19 @@
         <v>110</v>
       </c>
       <c r="AJ43" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK43" t="n">
         <v>38</v>
       </c>
       <c r="AL43" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM43" t="n">
         <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AO43" t="n">
         <v>120</v>
@@ -8825,10 +8825,10 @@
         <v>9.6</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT43" t="n">
         <v>6.4</v>
@@ -8840,7 +8840,7 @@
         <v>15.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX43" t="n">
         <v>11.5</v>
@@ -8852,29 +8852,29 @@
         <v>20</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB43" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC43" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -8920,34 +8920,34 @@
         <v>4.5</v>
       </c>
       <c r="K44" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M44" t="n">
         <v>1.04</v>
       </c>
       <c r="N44" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O44" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P44" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R44" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="S44" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="T44" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U44" t="n">
         <v>2.2</v>
@@ -8971,10 +8971,10 @@
         <v>170</v>
       </c>
       <c r="AB44" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD44" t="n">
         <v>24</v>
@@ -8983,7 +8983,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG44" t="n">
         <v>9.800000000000001</v>
@@ -9007,25 +9007,25 @@
         <v>95</v>
       </c>
       <c r="AN44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ44" t="n">
         <v>24</v>
       </c>
       <c r="AR44" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS44" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT44" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU44" t="n">
         <v>9.4</v>
@@ -9046,29 +9046,29 @@
         <v>17.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BB44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC44" t="n">
         <v>13.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE44" t="n">
         <v>80</v>
       </c>
       <c r="BF44" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG44" t="n">
         <v>70</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
         <v>1.04</v>
       </c>
       <c r="G45" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="H45" t="n">
         <v>2.72</v>
@@ -9138,13 +9138,13 @@
         <v>1.12</v>
       </c>
       <c r="S45" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V45" t="n">
         <v>1.01</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
         <v>990</v>
       </c>
       <c r="H46" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I46" t="n">
         <v>990</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -9487,46 +9487,46 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="G47" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I47" t="n">
         <v>3.7</v>
       </c>
-      <c r="H47" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I47" t="n">
-        <v>4.3</v>
-      </c>
       <c r="J47" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="K47" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="L47" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="M47" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N47" t="n">
-        <v>1.1</v>
+        <v>2.28</v>
       </c>
       <c r="O47" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="P47" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="R47" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S47" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="T47" t="n">
         <v>1.11</v>
@@ -9535,10 +9535,10 @@
         <v>1.11</v>
       </c>
       <c r="V47" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W47" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -9681,16 +9681,16 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G48" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H48" t="n">
         <v>3.7</v>
       </c>
       <c r="I48" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>2.8</v>
@@ -9699,28 +9699,28 @@
         <v>3.4</v>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M48" t="n">
         <v>1.13</v>
       </c>
       <c r="N48" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O48" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P48" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="R48" t="n">
         <v>1.16</v>
       </c>
       <c r="S48" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T48" t="n">
         <v>2.1</v>
@@ -9729,10 +9729,10 @@
         <v>1.69</v>
       </c>
       <c r="V48" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W48" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X48" t="n">
         <v>9.800000000000001</v>
@@ -9774,7 +9774,7 @@
         <v>38</v>
       </c>
       <c r="AK48" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL48" t="n">
         <v>80</v>
@@ -9789,46 +9789,46 @@
         <v>130</v>
       </c>
       <c r="AP48" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="AQ48" t="n">
-        <v>8.6</v>
+        <v>3.55</v>
       </c>
       <c r="AR48" t="n">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS48" t="n">
         <v>4.7</v>
       </c>
       <c r="AT48" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="AU48" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="AV48" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AW48" t="n">
         <v>4.6</v>
       </c>
       <c r="AX48" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="AY48" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="AZ48" t="n">
-        <v>17.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA48" t="n">
         <v>4.7</v>
       </c>
       <c r="BB48" t="n">
-        <v>24</v>
+        <v>4.4</v>
       </c>
       <c r="BC48" t="n">
-        <v>24</v>
+        <v>4.4</v>
       </c>
       <c r="BD48" t="n">
         <v>4.6</v>
@@ -9840,11 +9840,11 @@
         <v>4.4</v>
       </c>
       <c r="BG48" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -9875,40 +9875,40 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G49" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H49" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I49" t="n">
         <v>5.4</v>
       </c>
       <c r="J49" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K49" t="n">
         <v>3.45</v>
       </c>
       <c r="L49" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="M49" t="n">
         <v>1.13</v>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O49" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P49" t="n">
         <v>1.48</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R49" t="n">
         <v>1.17</v>
@@ -9920,13 +9920,13 @@
         <v>2.22</v>
       </c>
       <c r="U49" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V49" t="n">
         <v>1.22</v>
       </c>
       <c r="W49" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X49" t="n">
         <v>8.6</v>
@@ -9983,10 +9983,10 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AQ49" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AR49" t="n">
         <v>7.4</v>
@@ -9995,31 +9995,31 @@
         <v>8.6</v>
       </c>
       <c r="AT49" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="AU49" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AV49" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="AW49" t="n">
         <v>8.4</v>
       </c>
       <c r="AX49" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AY49" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="AZ49" t="n">
-        <v>19.5</v>
+        <v>6.8</v>
       </c>
       <c r="BA49" t="n">
         <v>8.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>19.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC49" t="n">
         <v>7</v>
@@ -10031,14 +10031,14 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF49" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BG49" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -10108,13 +10108,13 @@
         <v>1.12</v>
       </c>
       <c r="S50" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T50" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U50" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -10263,58 +10263,58 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="G51" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="H51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N51" t="n">
         <v>3.2</v>
       </c>
-      <c r="I51" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O51" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P51" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="R51" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S51" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="n">
         <v>1.11</v>
       </c>
       <c r="U51" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V51" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W51" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="X51" t="n">
         <v>90</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -10460,55 +10460,55 @@
         <v>1.66</v>
       </c>
       <c r="G52" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="H52" t="n">
         <v>5.3</v>
       </c>
       <c r="I52" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J52" t="n">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="K52" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L52" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M52" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N52" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="O52" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P52" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="R52" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="S52" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
         <v>1.78</v>
       </c>
       <c r="U52" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="V52" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="W52" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X52" t="n">
         <v>970</v>
@@ -10541,10 +10541,10 @@
         <v>970</v>
       </c>
       <c r="AH52" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ52" t="n">
         <v>21</v>
@@ -10553,7 +10553,7 @@
         <v>970</v>
       </c>
       <c r="AL52" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM52" t="n">
         <v>1000</v>
@@ -10565,62 +10565,62 @@
         <v>1000</v>
       </c>
       <c r="AP52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT52" t="n">
         <v>3.45</v>
       </c>
-      <c r="AQ52" t="n">
+      <c r="AU52" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AZ52" t="n">
         <v>4</v>
       </c>
-      <c r="AR52" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ52" t="n">
+      <c r="BA52" t="n">
         <v>3.7</v>
       </c>
-      <c r="BA52" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BB52" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BC52" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE52" t="n">
         <v>3.75</v>
       </c>
-      <c r="BD52" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF52" t="n">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="BG52" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -10651,58 +10651,58 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G53" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H53" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="I53" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K53" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L53" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M53" t="n">
         <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="O53" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="P53" t="n">
         <v>1.62</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="R53" t="n">
         <v>1.22</v>
       </c>
       <c r="S53" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T53" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="U53" t="n">
         <v>1.86</v>
       </c>
       <c r="V53" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W53" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10759,62 +10759,62 @@
         <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ53" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR53" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AV53" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW53" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX53" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY53" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ53" t="n">
         <v>4.9</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="BB53" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC53" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC53" t="n">
-        <v>5</v>
-      </c>
       <c r="BD53" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BF53" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG53" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -10848,10 +10848,10 @@
         <v>2.78</v>
       </c>
       <c r="G54" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="H54" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I54" t="n">
         <v>2.92</v>
@@ -10860,43 +10860,43 @@
         <v>3.25</v>
       </c>
       <c r="K54" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L54" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M54" t="n">
         <v>1.08</v>
       </c>
       <c r="N54" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O54" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P54" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R54" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S54" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T54" t="n">
         <v>1.78</v>
       </c>
       <c r="U54" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V54" t="n">
         <v>1.52</v>
       </c>
       <c r="W54" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="X54" t="n">
         <v>13.5</v>
@@ -10917,7 +10917,7 @@
         <v>7.8</v>
       </c>
       <c r="AD54" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE54" t="n">
         <v>34</v>
@@ -10935,19 +10935,19 @@
         <v>48</v>
       </c>
       <c r="AJ54" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK54" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL54" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AM54" t="n">
         <v>120</v>
       </c>
       <c r="AN54" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO54" t="n">
         <v>32</v>
@@ -10956,13 +10956,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ54" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR54" t="n">
         <v>16</v>
       </c>
       <c r="AS54" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT54" t="n">
         <v>9.6</v>
@@ -10974,7 +10974,7 @@
         <v>11</v>
       </c>
       <c r="AW54" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX54" t="n">
         <v>16</v>
@@ -10986,29 +10986,29 @@
         <v>15</v>
       </c>
       <c r="BA54" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG54" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB54" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE54" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF54" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG54" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -11039,64 +11039,64 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G55" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="H55" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I55" t="n">
         <v>4.3</v>
       </c>
       <c r="J55" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K55" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M55" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N55" t="n">
-        <v>2.54</v>
+        <v>3.15</v>
       </c>
       <c r="O55" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P55" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="R55" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S55" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="T55" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="U55" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="V55" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W55" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="X55" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z55" t="n">
         <v>1000</v>
@@ -11105,25 +11105,25 @@
         <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC55" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD55" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE55" t="n">
         <v>1000</v>
       </c>
       <c r="AF55" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG55" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI55" t="n">
         <v>1000</v>
@@ -11132,77 +11132,77 @@
         <v>1000</v>
       </c>
       <c r="AK55" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL55" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM55" t="n">
         <v>1000</v>
       </c>
       <c r="AN55" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO55" t="n">
         <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -11236,16 +11236,16 @@
         <v>2.06</v>
       </c>
       <c r="G56" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H56" t="n">
         <v>4.3</v>
       </c>
       <c r="I56" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J56" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K56" t="n">
         <v>3.5</v>
@@ -11257,7 +11257,7 @@
         <v>1.09</v>
       </c>
       <c r="N56" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O56" t="n">
         <v>1.4</v>
@@ -11266,37 +11266,37 @@
         <v>1.78</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R56" t="n">
         <v>1.29</v>
       </c>
       <c r="S56" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T56" t="n">
         <v>1.95</v>
       </c>
       <c r="U56" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V56" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W56" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X56" t="n">
         <v>11.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z56" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA56" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB56" t="n">
         <v>8.199999999999999</v>
@@ -11305,10 +11305,10 @@
         <v>7.8</v>
       </c>
       <c r="AD56" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AE56" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF56" t="n">
         <v>12</v>
@@ -11335,7 +11335,7 @@
         <v>130</v>
       </c>
       <c r="AN56" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO56" t="n">
         <v>80</v>
@@ -11353,7 +11353,7 @@
         <v>38</v>
       </c>
       <c r="AT56" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU56" t="n">
         <v>7</v>
@@ -11371,7 +11371,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ56" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA56" t="n">
         <v>34</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -11427,31 +11427,31 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="G57" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H57" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I57" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J57" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K57" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L57" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M57" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N57" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O57" t="n">
         <v>1.42</v>
@@ -11460,46 +11460,46 @@
         <v>1.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R57" t="n">
         <v>1.26</v>
       </c>
       <c r="S57" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T57" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U57" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="V57" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W57" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X57" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y57" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Z57" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AA57" t="n">
         <v>310</v>
       </c>
       <c r="AB57" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AC57" t="n">
         <v>970</v>
       </c>
       <c r="AD57" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE57" t="n">
         <v>170</v>
@@ -11511,10 +11511,10 @@
         <v>970</v>
       </c>
       <c r="AH57" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI57" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ57" t="n">
         <v>970</v>
@@ -11523,13 +11523,13 @@
         <v>21</v>
       </c>
       <c r="AL57" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM57" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN57" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO57" t="n">
         <v>280</v>
@@ -11541,22 +11541,22 @@
         <v>16</v>
       </c>
       <c r="AR57" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="AS57" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="AT57" t="n">
         <v>5.8</v>
       </c>
       <c r="AU57" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV57" t="n">
         <v>7.2</v>
       </c>
       <c r="AW57" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="AX57" t="n">
         <v>7.4</v>
@@ -11565,10 +11565,10 @@
         <v>9</v>
       </c>
       <c r="AZ57" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BA57" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="BB57" t="n">
         <v>14</v>
@@ -11577,20 +11577,20 @@
         <v>6.6</v>
       </c>
       <c r="BD57" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE57" t="n">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="BF57" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BG57" t="n">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -11621,46 +11621,46 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G58" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H58" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I58" t="n">
         <v>2.4</v>
       </c>
       <c r="J58" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K58" t="n">
         <v>3.5</v>
       </c>
       <c r="L58" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M58" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N58" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O58" t="n">
         <v>1.37</v>
       </c>
       <c r="P58" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R58" t="n">
         <v>1.31</v>
       </c>
       <c r="S58" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T58" t="n">
         <v>1.86</v>
@@ -11720,7 +11720,7 @@
         <v>60</v>
       </c>
       <c r="AM58" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN58" t="n">
         <v>50</v>
@@ -11732,13 +11732,13 @@
         <v>5.4</v>
       </c>
       <c r="AQ58" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR58" t="n">
         <v>11</v>
       </c>
       <c r="AS58" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT58" t="n">
         <v>10.5</v>
@@ -11750,7 +11750,7 @@
         <v>10</v>
       </c>
       <c r="AW58" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AX58" t="n">
         <v>6.6</v>
@@ -11771,7 +11771,7 @@
         <v>7.6</v>
       </c>
       <c r="BD58" t="n">
-        <v>7.8</v>
+        <v>3.95</v>
       </c>
       <c r="BE58" t="n">
         <v>4</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -11815,58 +11815,58 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="G59" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="H59" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="J59" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="K59" t="n">
         <v>3.75</v>
       </c>
       <c r="L59" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M59" t="n">
         <v>1.08</v>
       </c>
       <c r="N59" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="O59" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P59" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="R59" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S59" t="n">
-        <v>1.94</v>
+        <v>4</v>
       </c>
       <c r="T59" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="U59" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="V59" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="W59" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -12009,16 +12009,16 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G60" t="n">
         <v>3.15</v>
       </c>
       <c r="H60" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I60" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J60" t="n">
         <v>3.25</v>
@@ -12027,37 +12027,37 @@
         <v>3.4</v>
       </c>
       <c r="L60" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="M60" t="n">
         <v>1.08</v>
       </c>
       <c r="N60" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O60" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P60" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="R60" t="n">
         <v>1.31</v>
       </c>
       <c r="S60" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T60" t="n">
         <v>1.8</v>
       </c>
       <c r="U60" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V60" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W60" t="n">
         <v>1.47</v>
@@ -12114,7 +12114,7 @@
         <v>36</v>
       </c>
       <c r="AO60" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AP60" t="n">
         <v>10.5</v>
@@ -12126,7 +12126,7 @@
         <v>14.5</v>
       </c>
       <c r="AS60" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT60" t="n">
         <v>9.6</v>
@@ -12138,7 +12138,7 @@
         <v>10.5</v>
       </c>
       <c r="AW60" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX60" t="n">
         <v>16.5</v>
@@ -12150,29 +12150,29 @@
         <v>15</v>
       </c>
       <c r="BA60" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB60" t="n">
         <v>40</v>
       </c>
       <c r="BC60" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD60" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF60" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BE60" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF60" t="n">
-        <v>7.2</v>
       </c>
       <c r="BG60" t="n">
         <v>21</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.4</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78</v>
+        <v>55</v>
       </c>
       <c r="I2" t="n">
-        <v>1.83</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>28</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>48</v>
       </c>
       <c r="L2" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.76</v>
       </c>
       <c r="U2" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2</v>
+        <v>21</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>24</v>
+        <v>6.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>150</v>
+        <v>990</v>
       </c>
       <c r="AL2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>220</v>
+        <v>990</v>
       </c>
       <c r="AO2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>1.41</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="AS2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>16.5</v>
       </c>
-      <c r="AT2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD2" t="n">
-        <v>11.5</v>
+        <v>1.41</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>1.41</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>1.05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.78</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>2.86</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>36</v>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD3" t="n">
         <v>4.9</v>
       </c>
-      <c r="T3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>40</v>
-      </c>
       <c r="BE3" t="n">
-        <v>75</v>
+        <v>4.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BG3" t="n">
-        <v>18.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="G4" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>2.58</v>
+        <v>8.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>1.46</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>1.53</v>
       </c>
       <c r="L4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>1.96</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>9.4</v>
       </c>
       <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN4" t="n">
         <v>75</v>
       </c>
-      <c r="AK4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>60</v>
-      </c>
       <c r="AO4" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.6</v>
+        <v>4.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>15.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="AZ4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE4" t="n">
         <v>16.5</v>
       </c>
-      <c r="BA4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF4" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BG4" t="n">
-        <v>22</v>
+        <v>4.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
         <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
         <v>4.5</v>
@@ -1369,61 +1369,61 @@
         <v>1.32</v>
       </c>
       <c r="P5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1.97</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.96</v>
       </c>
       <c r="R5" t="n">
         <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
         <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="V5" t="n">
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Z5" t="n">
         <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AE5" t="n">
         <v>120</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AI5" t="n">
         <v>110</v>
@@ -1447,62 +1447,62 @@
         <v>160</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.55</v>
+        <v>9.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
         <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1533,61 +1533,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="G6" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="H6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I6" t="n">
         <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="K6" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
         <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="X6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y6" t="n">
         <v>34</v>
@@ -1599,34 +1599,34 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
         <v>13.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
@@ -1644,59 +1644,59 @@
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23</v>
+        <v>5.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX6" t="n">
         <v>6.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1727,94 +1727,94 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="G7" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="I7" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W7" t="n">
         <v>2.88</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.28</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
       </c>
       <c r="Y7" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Z7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF7" t="n">
         <v>970</v>
       </c>
-      <c r="AD7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AJ7" t="n">
         <v>970</v>
@@ -1823,49 +1823,49 @@
         <v>970</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AN7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AO7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AV7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW7" t="n">
         <v>5.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
         <v>5.5</v>
@@ -1874,23 +1874,23 @@
         <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BE7" t="n">
         <v>5.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BG7" t="n">
         <v>5.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G8" t="n">
         <v>2.56</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.6</v>
-      </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J8" t="n">
         <v>3.1</v>
@@ -1939,7 +1939,7 @@
         <v>3.15</v>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M8" t="n">
         <v>1.13</v>
@@ -1954,52 +1954,52 @@
         <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y8" t="n">
         <v>9.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
         <v>6.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
         <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
@@ -2008,10 +2008,10 @@
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
         <v>36</v>
@@ -2020,25 +2020,25 @@
         <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN8" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
         <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2047,25 +2047,25 @@
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
         <v>46</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY8" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
         <v>60</v>
       </c>
       <c r="BB8" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BC8" t="n">
         <v>32</v>
@@ -2074,17 +2074,17 @@
         <v>55</v>
       </c>
       <c r="BE8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BF8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG8" t="n">
         <v>60</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.52</v>
@@ -2139,22 +2139,22 @@
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T9" t="n">
         <v>1.95</v>
@@ -2166,7 +2166,7 @@
         <v>1.54</v>
       </c>
       <c r="W9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
         <v>10.5</v>
@@ -2175,13 +2175,13 @@
         <v>8.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
         <v>7.6</v>
@@ -2193,10 +2193,10 @@
         <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
         <v>21</v>
@@ -2208,7 +2208,7 @@
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2220,10 +2220,10 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>7.2</v>
@@ -2259,26 +2259,26 @@
         <v>18.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BD9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF9" t="n">
-        <v>18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -2315,10 +2315,10 @@
         <v>2.86</v>
       </c>
       <c r="H10" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
         <v>3.2</v>
@@ -2342,22 +2342,22 @@
         <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
         <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.54</v>
@@ -2417,16 +2417,16 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="AT10" t="n">
         <v>8.800000000000001</v>
@@ -2435,7 +2435,7 @@
         <v>6.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
         <v>7.4</v>
@@ -2447,32 +2447,32 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
         <v>7.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BE10" t="n">
         <v>8.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>26</v>
+        <v>7.2</v>
       </c>
       <c r="BG10" t="n">
         <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -2503,64 +2503,64 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
         <v>34</v>
@@ -2569,104 +2569,104 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>55</v>
+        <v>8.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
         <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.8</v>
+        <v>46</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
@@ -2721,16 +2721,16 @@
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P12" t="n">
         <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
@@ -2739,7 +2739,7 @@
         <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
@@ -2853,14 +2853,14 @@
         <v>8.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -2897,13 +2897,13 @@
         <v>1.97</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
         <v>5.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
         <v>3.85</v>
@@ -2915,22 +2915,22 @@
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.35</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
         <v>2.06</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T13" t="n">
         <v>1.88</v>
@@ -2942,13 +2942,13 @@
         <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X13" t="n">
         <v>15.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z13" t="n">
         <v>38</v>
@@ -2960,7 +2960,7 @@
         <v>9.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
         <v>19.5</v>
@@ -2987,7 +2987,7 @@
         <v>24</v>
       </c>
       <c r="AL13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -2996,65 +2996,65 @@
         <v>18</v>
       </c>
       <c r="AO13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
         <v>11</v>
       </c>
       <c r="AQ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AW13" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
         <v>18.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BD13" t="n">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H14" t="n">
         <v>1.99</v>
       </c>
       <c r="I14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J14" t="n">
         <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
         <v>1.48</v>
@@ -3118,13 +3118,13 @@
         <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R14" t="n">
         <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T14" t="n">
         <v>1.98</v>
@@ -3133,34 +3133,34 @@
         <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W14" t="n">
         <v>1.27</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z14" t="n">
         <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AC14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
         <v>34</v>
@@ -3178,7 +3178,7 @@
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3196,10 +3196,10 @@
         <v>9.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
         <v>12.5</v>
@@ -3208,47 +3208,47 @@
         <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC14" t="n">
         <v>8.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="n">
         <v>40</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -3279,55 +3279,55 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="G15" t="n">
         <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="I15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S15" t="n">
         <v>4.5</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.45</v>
-      </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="W15" t="n">
         <v>1.09</v>
@@ -3336,113 +3336,113 @@
         <v>1000</v>
       </c>
       <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
         <v>7.6</v>
       </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="AR15" t="n">
         <v>3.75</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AV15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.15</v>
+        <v>2.24</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="BA15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG15" t="n">
         <v>3.3</v>
       </c>
-      <c r="BB15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="I16" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
         <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.41</v>
@@ -3503,16 +3503,16 @@
         <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -3521,10 +3521,10 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="W16" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -3667,49 +3667,49 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="G17" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="I17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="T17" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
         <v>1.86</v>
@@ -3718,13 +3718,13 @@
         <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3736,7 +3736,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD17" t="n">
         <v>32</v>
@@ -3757,80 +3757,80 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.7</v>
+        <v>15.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.8</v>
+        <v>19.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AT17" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.9</v>
+        <v>22</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.65</v>
+        <v>14</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G18" t="n">
         <v>1.24</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.28</v>
-      </c>
       <c r="H18" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="I18" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="K18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T18" t="n">
         <v>3.35</v>
       </c>
-      <c r="T18" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
         <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Z18" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AD18" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB18" t="n">
         <v>6.4</v>
       </c>
-      <c r="AG18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC18" t="n">
-        <v>5.6</v>
+        <v>17</v>
       </c>
       <c r="BD18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>1.56</v>
       </c>
       <c r="H19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
         <v>4.5</v>
@@ -4088,25 +4088,25 @@
         <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
         <v>2.68</v>
       </c>
       <c r="T19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U19" t="n">
         <v>1.88</v>
       </c>
       <c r="V19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -4249,64 +4249,64 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="G20" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="H20" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="T20" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="U20" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="n">
         <v>1000</v>
@@ -4318,10 +4318,10 @@
         <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
@@ -4336,7 +4336,7 @@
         <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ20" t="n">
         <v>1000</v>
@@ -4351,68 +4351,68 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>21</v>
+        <v>5.3</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.24</v>
+        <v>5.9</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
         <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>4.8</v>
       </c>
-      <c r="AY20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BA20" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB20" t="n">
         <v>6.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="BF20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>1.65</v>
       </c>
       <c r="G21" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H21" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I21" t="n">
         <v>8.199999999999999</v>
@@ -4470,7 +4470,7 @@
         <v>2.38</v>
       </c>
       <c r="O21" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P21" t="n">
         <v>1.46</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G22" t="n">
         <v>2.56</v>
       </c>
-      <c r="G22" t="n">
-        <v>2.6</v>
-      </c>
       <c r="H22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
         <v>3.55</v>
@@ -4661,37 +4661,37 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="U22" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
         <v>11</v>
@@ -4703,7 +4703,7 @@
         <v>55</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
         <v>7.6</v>
@@ -4712,16 +4712,16 @@
         <v>13.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI22" t="n">
         <v>55</v>
@@ -4730,25 +4730,25 @@
         <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO22" t="n">
         <v>42</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
         <v>18</v>
@@ -4757,7 +4757,7 @@
         <v>46</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU22" t="n">
         <v>7</v>
@@ -4769,16 +4769,16 @@
         <v>32</v>
       </c>
       <c r="AX22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY22" t="n">
         <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="BB22" t="n">
         <v>32</v>
@@ -4790,7 +4790,7 @@
         <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="BF22" t="n">
         <v>24</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
         <v>1.31</v>
@@ -4891,16 +4891,16 @@
         <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23" t="n">
         <v>21</v>
@@ -4945,10 +4945,10 @@
         <v>14.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT23" t="n">
         <v>7.6</v>
@@ -4972,7 +4972,7 @@
         <v>16.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BB23" t="n">
         <v>16.5</v>
@@ -4984,7 +4984,7 @@
         <v>25</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF23" t="n">
         <v>8.800000000000001</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -5025,73 +5025,73 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I24" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="J24" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
         <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P24" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>1.43</v>
+        <v>3.8</v>
       </c>
       <c r="T24" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U24" t="n">
         <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W24" t="n">
         <v>1.33</v>
       </c>
       <c r="X24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Z24" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC24" t="n">
         <v>9</v>
@@ -5100,7 +5100,7 @@
         <v>12</v>
       </c>
       <c r="AE24" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF24" t="n">
         <v>29</v>
@@ -5130,65 +5130,65 @@
         <v>60</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AP24" t="n">
         <v>4.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AR24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT24" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AU24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW24" t="n">
         <v>5</v>
       </c>
-      <c r="AT24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW24" t="n">
+      <c r="AX24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG24" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -5222,19 +5222,19 @@
         <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H25" t="n">
         <v>2.94</v>
       </c>
       <c r="I25" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.45</v>
@@ -5255,43 +5255,43 @@
         <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
         <v>3.9</v>
       </c>
       <c r="T25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U25" t="n">
         <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W25" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X25" t="n">
         <v>15</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA25" t="n">
         <v>60</v>
       </c>
       <c r="AB25" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE25" t="n">
         <v>42</v>
@@ -5300,10 +5300,10 @@
         <v>20</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI25" t="n">
         <v>65</v>
@@ -5312,77 +5312,77 @@
         <v>46</v>
       </c>
       <c r="AK25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO25" t="n">
         <v>48</v>
       </c>
       <c r="AP25" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AR25" t="n">
-        <v>3.9</v>
+        <v>17.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.75</v>
+        <v>13.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.8</v>
+        <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.2</v>
+        <v>36</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>4</v>
+        <v>19.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.2</v>
+        <v>29</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.32</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H26" t="n">
         <v>3.3</v>
@@ -5428,7 +5428,7 @@
         <v>3.15</v>
       </c>
       <c r="K26" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L26" t="n">
         <v>1.49</v>
@@ -5440,37 +5440,37 @@
         <v>3.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P26" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U26" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V26" t="n">
         <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X26" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z26" t="n">
         <v>26</v>
@@ -5482,10 +5482,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD26" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE26" t="n">
         <v>50</v>
@@ -5506,13 +5506,13 @@
         <v>36</v>
       </c>
       <c r="AK26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL26" t="n">
         <v>50</v>
       </c>
       <c r="AM26" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN26" t="n">
         <v>34</v>
@@ -5524,49 +5524,49 @@
         <v>9.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR26" t="n">
         <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AT26" t="n">
         <v>7.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV26" t="n">
         <v>12.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD26" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE26" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF26" t="n">
         <v>23</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G27" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="H27" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L27" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M27" t="n">
         <v>1.11</v>
@@ -5637,7 +5637,7 @@
         <v>1.5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q27" t="n">
         <v>2.52</v>
@@ -5649,40 +5649,40 @@
         <v>5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="U27" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
         <v>1.27</v>
       </c>
       <c r="W27" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="X27" t="n">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z27" t="n">
         <v>32</v>
       </c>
       <c r="AA27" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB27" t="n">
         <v>970</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD27" t="n">
         <v>970</v>
       </c>
       <c r="AE27" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="n">
         <v>970</v>
@@ -5691,16 +5691,16 @@
         <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
         <v>100</v>
       </c>
       <c r="AJ27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK27" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL27" t="n">
         <v>65</v>
@@ -5709,68 +5709,68 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO27" t="n">
         <v>120</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR27" t="n">
         <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>3.25</v>
+        <v>1.71</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AU27" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="AV27" t="n">
         <v>5.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>3.55</v>
+        <v>1.94</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AY27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ27" t="n">
-        <v>3.25</v>
+        <v>1.99</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.8</v>
+        <v>2.94</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.26</v>
+        <v>1.72</v>
       </c>
       <c r="BF27" t="n">
         <v>6</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.52</v>
+        <v>1.96</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -5804,10 +5804,10 @@
         <v>2.68</v>
       </c>
       <c r="G28" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H28" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I28" t="n">
         <v>3.25</v>
@@ -5819,7 +5819,7 @@
         <v>3.25</v>
       </c>
       <c r="L28" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
         <v>1.12</v>
@@ -5843,19 +5843,19 @@
         <v>5.2</v>
       </c>
       <c r="T28" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="V28" t="n">
         <v>1.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X28" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y28" t="n">
         <v>9.199999999999999</v>
@@ -5912,28 +5912,28 @@
         <v>7.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX28" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>14</v>
       </c>
       <c r="AY28" t="n">
         <v>11</v>
@@ -5942,29 +5942,29 @@
         <v>18.5</v>
       </c>
       <c r="BA28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG28" t="n">
         <v>9</v>
       </c>
-      <c r="BB28" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>32</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>44</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G29" t="n">
         <v>2.46</v>
       </c>
       <c r="H29" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I29" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
         <v>3.65</v>
@@ -6025,10 +6025,10 @@
         <v>1.34</v>
       </c>
       <c r="P29" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R29" t="n">
         <v>1.32</v>
@@ -6043,25 +6043,25 @@
         <v>2.06</v>
       </c>
       <c r="V29" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W29" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X29" t="n">
         <v>14.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
         <v>27</v>
       </c>
       <c r="AA29" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC29" t="n">
         <v>8</v>
@@ -6070,7 +6070,7 @@
         <v>970</v>
       </c>
       <c r="AE29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF29" t="n">
         <v>970</v>
@@ -6079,7 +6079,7 @@
         <v>970</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI29" t="n">
         <v>60</v>
@@ -6100,19 +6100,19 @@
         <v>22</v>
       </c>
       <c r="AO29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT29" t="n">
         <v>8</v>
@@ -6121,44 +6121,44 @@
         <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BA29" t="n">
-        <v>40</v>
+        <v>7.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF29" t="n">
         <v>6.4</v>
       </c>
-      <c r="BD29" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>6</v>
-      </c>
       <c r="BG29" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>2.36</v>
       </c>
       <c r="H30" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I30" t="n">
         <v>4.2</v>
@@ -6204,7 +6204,7 @@
         <v>3.1</v>
       </c>
       <c r="K30" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L30" t="n">
         <v>1.5</v>
@@ -6213,13 +6213,13 @@
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
         <v>1.42</v>
       </c>
       <c r="P30" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q30" t="n">
         <v>2.3</v>
@@ -6228,13 +6228,13 @@
         <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="U30" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="V30" t="n">
         <v>1.32</v>
@@ -6246,22 +6246,22 @@
         <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z30" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA30" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE30" t="n">
         <v>60</v>
@@ -6270,89 +6270,89 @@
         <v>970</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL30" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM30" t="n">
         <v>160</v>
       </c>
       <c r="AN30" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO30" t="n">
         <v>75</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AR30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD30" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>4</v>
-      </c>
       <c r="BE30" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G31" t="n">
         <v>2.5</v>
@@ -6392,7 +6392,7 @@
         <v>3.4</v>
       </c>
       <c r="I31" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
         <v>3.05</v>
@@ -6422,7 +6422,7 @@
         <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T31" t="n">
         <v>2.04</v>
@@ -6473,7 +6473,7 @@
         <v>80</v>
       </c>
       <c r="AJ31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK31" t="n">
         <v>36</v>
@@ -6485,22 +6485,22 @@
         <v>210</v>
       </c>
       <c r="AN31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO31" t="n">
         <v>85</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT31" t="n">
         <v>6.8</v>
@@ -6512,41 +6512,41 @@
         <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>17.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX31" t="n">
         <v>6</v>
       </c>
       <c r="AY31" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AZ31" t="n">
         <v>6.8</v>
       </c>
       <c r="BA31" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC31" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD31" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BF31" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.6</v>
+        <v>19.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="H32" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="I32" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="J32" t="n">
         <v>3.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L32" t="n">
         <v>1.44</v>
@@ -6601,61 +6601,61 @@
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O32" t="n">
         <v>1.35</v>
       </c>
       <c r="P32" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R32" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T32" t="n">
         <v>1.79</v>
       </c>
       <c r="U32" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W32" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X32" t="n">
         <v>13</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AB32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE32" t="n">
         <v>32</v>
       </c>
       <c r="AF32" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG32" t="n">
         <v>13</v>
@@ -6667,31 +6667,31 @@
         <v>44</v>
       </c>
       <c r="AJ32" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL32" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM32" t="n">
         <v>95</v>
       </c>
       <c r="AN32" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AO32" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AP32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ32" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS32" t="n">
         <v>34</v>
@@ -6709,38 +6709,38 @@
         <v>25</v>
       </c>
       <c r="AX32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="BB32" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BC32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD32" t="n">
         <v>27</v>
       </c>
       <c r="BE32" t="n">
-        <v>48</v>
+        <v>16.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BG32" t="n">
         <v>23</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G33" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H33" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="K33" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L33" t="n">
         <v>1.62</v>
@@ -6810,131 +6810,131 @@
         <v>1.15</v>
       </c>
       <c r="S33" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V33" t="n">
         <v>1.34</v>
       </c>
       <c r="W33" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE33" t="n">
         <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI33" t="n">
         <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="n">
         <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -6965,25 +6965,25 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G34" t="n">
         <v>2.38</v>
       </c>
       <c r="H34" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J34" t="n">
         <v>2.78</v>
       </c>
       <c r="K34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L34" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M34" t="n">
         <v>1.15</v>
@@ -7004,19 +7004,19 @@
         <v>1.14</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T34" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U34" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V34" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W34" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X34" t="n">
         <v>970</v>
@@ -7031,13 +7031,13 @@
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AC34" t="n">
         <v>970</v>
       </c>
       <c r="AD34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE34" t="n">
         <v>1000</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AQ34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BC34" t="n">
         <v>3.95</v>
       </c>
-      <c r="AR34" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD34" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="BE34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BF34" t="n">
         <v>2.66</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>5.3</v>
       </c>
       <c r="BG34" t="n">
         <v>2.54</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -7159,100 +7159,100 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="G35" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H35" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="I35" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J35" t="n">
-        <v>1.09</v>
+        <v>2.66</v>
       </c>
       <c r="K35" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="O35" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="R35" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S35" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA35" t="n">
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL35" t="n">
         <v>1000</v>
@@ -7267,62 +7267,62 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
         <v>990</v>
       </c>
       <c r="J36" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K36" t="n">
         <v>950</v>
@@ -7377,22 +7377,22 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O36" t="n">
         <v>1.3</v>
       </c>
       <c r="P36" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="R36" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="S36" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="T36" t="n">
         <v>1.11</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -7547,19 +7547,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G37" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H37" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I37" t="n">
         <v>4.6</v>
       </c>
       <c r="J37" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K37" t="n">
         <v>3.3</v>
@@ -7577,10 +7577,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
         <v>1.13</v>
       </c>
       <c r="S38" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="T38" t="n">
         <v>1.11</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -7959,13 +7959,13 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O39" t="n">
         <v>1.01</v>
       </c>
       <c r="P39" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q39" t="n">
         <v>1.01</v>
@@ -7974,7 +7974,7 @@
         <v>1.12</v>
       </c>
       <c r="S39" t="n">
-        <v>1.05</v>
+        <v>1.59</v>
       </c>
       <c r="T39" t="n">
         <v>1.11</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -8129,19 +8129,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" t="n">
         <v>2.92</v>
       </c>
-      <c r="H40" t="n">
-        <v>3</v>
-      </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J40" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="K40" t="n">
         <v>3.25</v>
@@ -8156,7 +8156,7 @@
         <v>2.62</v>
       </c>
       <c r="O40" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P40" t="n">
         <v>1.53</v>
@@ -8168,19 +8168,19 @@
         <v>1.19</v>
       </c>
       <c r="S40" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T40" t="n">
         <v>2.02</v>
       </c>
       <c r="U40" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V40" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W40" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X40" t="n">
         <v>90</v>
@@ -8195,7 +8195,7 @@
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC40" t="n">
         <v>1000</v>
@@ -8237,62 +8237,62 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AQ40" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AS40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BC40" t="n">
         <v>2.28</v>
       </c>
-      <c r="AT40" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BA40" t="n">
+      <c r="BD40" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BF40" t="n">
         <v>2.3</v>
       </c>
-      <c r="BB40" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>2.26</v>
-      </c>
       <c r="BG40" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -8332,10 +8332,10 @@
         <v>2.64</v>
       </c>
       <c r="I41" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K41" t="n">
         <v>3.25</v>
@@ -8371,7 +8371,7 @@
         <v>1.78</v>
       </c>
       <c r="V41" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W41" t="n">
         <v>1.44</v>
@@ -8434,46 +8434,46 @@
         <v>6.8</v>
       </c>
       <c r="AQ41" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR41" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS41" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AT41" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU41" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW41" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX41" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY41" t="n">
         <v>12</v>
       </c>
       <c r="AZ41" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>48</v>
+        <v>8.4</v>
       </c>
       <c r="BB41" t="n">
         <v>8.4</v>
       </c>
       <c r="BC41" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BD41" t="n">
-        <v>55</v>
+        <v>8.4</v>
       </c>
       <c r="BE41" t="n">
         <v>9.199999999999999</v>
@@ -8482,11 +8482,11 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG41" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -8517,64 +8517,64 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G42" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H42" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I42" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K42" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M42" t="n">
         <v>1.11</v>
       </c>
       <c r="N42" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O42" t="n">
         <v>1.51</v>
       </c>
       <c r="P42" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R42" t="n">
         <v>1.19</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U42" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V42" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W42" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X42" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z42" t="n">
         <v>1000</v>
@@ -8589,7 +8589,7 @@
         <v>8.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE42" t="n">
         <v>1000</v>
@@ -8625,62 +8625,62 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ42" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AS42" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT42" t="n">
         <v>6.4</v>
       </c>
       <c r="AU42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB42" t="n">
         <v>5.4</v>
       </c>
-      <c r="AV42" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW42" t="n">
+      <c r="BC42" t="n">
         <v>5.3</v>
       </c>
-      <c r="AX42" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA42" t="n">
+      <c r="BD42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF42" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB42" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>5</v>
-      </c>
       <c r="BG42" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
         <v>2.22</v>
       </c>
       <c r="G43" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H43" t="n">
         <v>4</v>
@@ -8723,7 +8723,7 @@
         <v>4.3</v>
       </c>
       <c r="J43" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
         <v>3.3</v>
@@ -8753,7 +8753,7 @@
         <v>5.3</v>
       </c>
       <c r="T43" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U43" t="n">
         <v>1.79</v>
@@ -8762,13 +8762,13 @@
         <v>1.31</v>
       </c>
       <c r="W43" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X43" t="n">
         <v>11</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z43" t="n">
         <v>34</v>
@@ -8825,10 +8825,10 @@
         <v>9.6</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT43" t="n">
         <v>6.4</v>
@@ -8840,7 +8840,7 @@
         <v>15.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX43" t="n">
         <v>11.5</v>
@@ -8852,29 +8852,29 @@
         <v>20</v>
       </c>
       <c r="BA43" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD43" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BE43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF43" t="n">
         <v>5</v>
       </c>
-      <c r="BC43" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG43" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -8908,61 +8908,61 @@
         <v>1.58</v>
       </c>
       <c r="G44" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H44" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I44" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J44" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K44" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L44" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M44" t="n">
         <v>1.04</v>
       </c>
       <c r="N44" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O44" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P44" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="R44" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="S44" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="T44" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="U44" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V44" t="n">
         <v>1.17</v>
       </c>
       <c r="W44" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X44" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y44" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="Z44" t="n">
         <v>55</v>
@@ -8971,19 +8971,19 @@
         <v>170</v>
       </c>
       <c r="AB44" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC44" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>10</v>
       </c>
       <c r="AD44" t="n">
         <v>24</v>
       </c>
       <c r="AE44" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF44" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG44" t="n">
         <v>9.800000000000001</v>
@@ -8992,7 +8992,7 @@
         <v>19.5</v>
       </c>
       <c r="AI44" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ44" t="n">
         <v>15</v>
@@ -9001,31 +9001,31 @@
         <v>15</v>
       </c>
       <c r="AL44" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AM44" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN44" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AO44" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AP44" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ44" t="n">
         <v>24</v>
       </c>
       <c r="AR44" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="AS44" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AT44" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU44" t="n">
         <v>9.4</v>
@@ -9037,38 +9037,38 @@
         <v>65</v>
       </c>
       <c r="AX44" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY44" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ44" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA44" t="n">
-        <v>16.5</v>
+        <v>55</v>
       </c>
       <c r="BB44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC44" t="n">
         <v>13.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE44" t="n">
-        <v>80</v>
+        <v>15.5</v>
       </c>
       <c r="BF44" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BG44" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
         <v>1.24</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R45" t="n">
         <v>1.12</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
         <v>990</v>
       </c>
       <c r="H46" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I46" t="n">
         <v>990</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G47" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H47" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>2.72</v>
       </c>
       <c r="K47" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L47" t="n">
         <v>1.67</v>
@@ -9511,40 +9511,40 @@
         <v>1.15</v>
       </c>
       <c r="N47" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
         <v>1.65</v>
       </c>
       <c r="P47" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T47" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="U47" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V47" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W47" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z47" t="n">
         <v>1000</v>
@@ -9553,10 +9553,10 @@
         <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD47" t="n">
         <v>1000</v>
@@ -9595,62 +9595,62 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
         <v>1.16</v>
       </c>
       <c r="S48" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T48" t="n">
         <v>2.1</v>
@@ -9789,62 +9789,62 @@
         <v>130</v>
       </c>
       <c r="AP48" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="AQ48" t="n">
         <v>3.55</v>
       </c>
       <c r="AR48" t="n">
-        <v>4.3</v>
+        <v>19</v>
       </c>
       <c r="AS48" t="n">
         <v>4.7</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU48" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="AV48" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AW48" t="n">
         <v>4.6</v>
       </c>
       <c r="AX48" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY48" t="n">
         <v>3.7</v>
       </c>
       <c r="AZ48" t="n">
-        <v>4.2</v>
+        <v>17.5</v>
       </c>
       <c r="BA48" t="n">
         <v>4.7</v>
       </c>
       <c r="BB48" t="n">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="BC48" t="n">
         <v>4.4</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE48" t="n">
         <v>4.8</v>
       </c>
       <c r="BF48" t="n">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="BG48" t="n">
         <v>4.8</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -9875,16 +9875,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G49" t="n">
         <v>2.18</v>
       </c>
       <c r="H49" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I49" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J49" t="n">
         <v>2.96</v>
@@ -9914,7 +9914,7 @@
         <v>1.17</v>
       </c>
       <c r="S49" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T49" t="n">
         <v>2.22</v>
@@ -9983,46 +9983,46 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AQ49" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR49" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="AS49" t="n">
         <v>8.6</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AU49" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV49" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AW49" t="n">
         <v>8.4</v>
       </c>
       <c r="AX49" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY49" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="AZ49" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BA49" t="n">
         <v>8.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BC49" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="BD49" t="n">
         <v>8</v>
@@ -10031,14 +10031,14 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF49" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BG49" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -10263,100 +10263,100 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="G51" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="H51" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" t="n">
         <v>3.35</v>
-      </c>
-      <c r="I51" t="n">
-        <v>4</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3.4</v>
       </c>
       <c r="L51" t="n">
         <v>1.48</v>
       </c>
       <c r="M51" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N51" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V51" t="n">
         <v>1.39</v>
       </c>
-      <c r="P51" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S51" t="n">
-        <v>4</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.35</v>
-      </c>
       <c r="W51" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X51" t="n">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="Y51" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA51" t="n">
         <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC51" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD51" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE51" t="n">
         <v>1000</v>
       </c>
       <c r="AF51" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI51" t="n">
         <v>1000</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK51" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL51" t="n">
         <v>1000</v>
@@ -10365,68 +10365,68 @@
         <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO51" t="n">
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.02</v>
+        <v>9.4</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.02</v>
+        <v>18</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.02</v>
+        <v>7.4</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.02</v>
+        <v>5.9</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.02</v>
+        <v>11.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.02</v>
+        <v>11</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.02</v>
+        <v>9.4</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.02</v>
+        <v>14.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.02</v>
+        <v>21</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.02</v>
+        <v>5.4</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.02</v>
+        <v>18.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G52" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H52" t="n">
         <v>5.3</v>
@@ -10469,7 +10469,7 @@
         <v>6.8</v>
       </c>
       <c r="J52" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K52" t="n">
         <v>4.5</v>
@@ -10481,16 +10481,16 @@
         <v>1.06</v>
       </c>
       <c r="N52" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
         <v>1.27</v>
       </c>
       <c r="P52" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R52" t="n">
         <v>1.44</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -10651,10 +10651,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G53" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H53" t="n">
         <v>3.85</v>
@@ -10666,7 +10666,7 @@
         <v>3.05</v>
       </c>
       <c r="K53" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L53" t="n">
         <v>1.53</v>
@@ -10693,7 +10693,7 @@
         <v>4.8</v>
       </c>
       <c r="T53" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U53" t="n">
         <v>1.86</v>
@@ -10702,7 +10702,7 @@
         <v>1.31</v>
       </c>
       <c r="W53" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10762,16 +10762,16 @@
         <v>3.9</v>
       </c>
       <c r="AQ53" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR53" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS53" t="n">
         <v>1.46</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AU53" t="n">
         <v>3.5</v>
@@ -10789,10 +10789,10 @@
         <v>4.1</v>
       </c>
       <c r="AZ53" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="BB53" t="n">
         <v>5.2</v>
@@ -10801,7 +10801,7 @@
         <v>5.1</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE53" t="n">
         <v>1.45</v>
@@ -10810,11 +10810,11 @@
         <v>5.1</v>
       </c>
       <c r="BG53" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G54" t="n">
         <v>2.9</v>
@@ -10860,7 +10860,7 @@
         <v>3.25</v>
       </c>
       <c r="K54" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L54" t="n">
         <v>1.44</v>
@@ -10875,13 +10875,13 @@
         <v>1.36</v>
       </c>
       <c r="P54" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R54" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S54" t="n">
         <v>3.9</v>
@@ -10947,7 +10947,7 @@
         <v>120</v>
       </c>
       <c r="AN54" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO54" t="n">
         <v>32</v>
@@ -10974,10 +10974,10 @@
         <v>11</v>
       </c>
       <c r="AW54" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX54" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="AY54" t="n">
         <v>11</v>
@@ -10986,7 +10986,7 @@
         <v>15</v>
       </c>
       <c r="BA54" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB54" t="n">
         <v>7.8</v>
@@ -10995,10 +10995,10 @@
         <v>7.4</v>
       </c>
       <c r="BD54" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE54" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF54" t="n">
         <v>7.4</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -11042,10 +11042,10 @@
         <v>2.12</v>
       </c>
       <c r="G55" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H55" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
         <v>4.3</v>
@@ -11090,7 +11090,7 @@
         <v>1.31</v>
       </c>
       <c r="W55" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X55" t="n">
         <v>13.5</v>
@@ -11105,7 +11105,7 @@
         <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC55" t="n">
         <v>9.199999999999999</v>
@@ -11156,7 +11156,7 @@
         <v>5.2</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT55" t="n">
         <v>7</v>
@@ -11180,16 +11180,16 @@
         <v>17</v>
       </c>
       <c r="BA55" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD55" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>5.6</v>
       </c>
       <c r="BE55" t="n">
         <v>6</v>
@@ -11198,11 +11198,11 @@
         <v>16.5</v>
       </c>
       <c r="BG55" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -11233,19 +11233,19 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G56" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="H56" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I56" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K56" t="n">
         <v>3.5</v>
@@ -11257,16 +11257,16 @@
         <v>1.09</v>
       </c>
       <c r="N56" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O56" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P56" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R56" t="n">
         <v>1.29</v>
@@ -11275,58 +11275,58 @@
         <v>4.2</v>
       </c>
       <c r="T56" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U56" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V56" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W56" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="X56" t="n">
         <v>11.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z56" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA56" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB56" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC56" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD56" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE56" t="n">
         <v>60</v>
       </c>
       <c r="AF56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG56" t="n">
         <v>11</v>
       </c>
       <c r="AH56" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI56" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ56" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK56" t="n">
         <v>25</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>24</v>
       </c>
       <c r="AL56" t="n">
         <v>46</v>
@@ -11335,46 +11335,46 @@
         <v>130</v>
       </c>
       <c r="AN56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO56" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP56" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ56" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR56" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AS56" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT56" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU56" t="n">
         <v>7</v>
       </c>
       <c r="AV56" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW56" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AX56" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY56" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ56" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA56" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB56" t="n">
         <v>22</v>
@@ -11389,14 +11389,14 @@
         <v>65</v>
       </c>
       <c r="BF56" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BG56" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
         <v>1.66</v>
       </c>
       <c r="G57" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H57" t="n">
         <v>7</v>
@@ -11439,7 +11439,7 @@
         <v>7.8</v>
       </c>
       <c r="J57" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K57" t="n">
         <v>3.8</v>
@@ -11472,13 +11472,13 @@
         <v>2.16</v>
       </c>
       <c r="U57" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V57" t="n">
         <v>1.15</v>
       </c>
       <c r="W57" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X57" t="n">
         <v>13</v>
@@ -11493,7 +11493,7 @@
         <v>310</v>
       </c>
       <c r="AB57" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC57" t="n">
         <v>970</v>
@@ -11541,56 +11541,56 @@
         <v>16</v>
       </c>
       <c r="AR57" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS57" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AT57" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU57" t="n">
         <v>7.2</v>
       </c>
       <c r="AV57" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW57" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AX57" t="n">
         <v>7.4</v>
       </c>
       <c r="AY57" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="AZ57" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BA57" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BB57" t="n">
         <v>14</v>
       </c>
       <c r="BC57" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BD57" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE57" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BF57" t="n">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG57" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -11624,10 +11624,10 @@
         <v>3.45</v>
       </c>
       <c r="G58" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H58" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I58" t="n">
         <v>2.4</v>
@@ -11639,46 +11639,46 @@
         <v>3.5</v>
       </c>
       <c r="L58" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M58" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N58" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O58" t="n">
         <v>1.37</v>
       </c>
       <c r="P58" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R58" t="n">
         <v>1.31</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T58" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U58" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V58" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W58" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X58" t="n">
         <v>970</v>
       </c>
       <c r="Y58" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="Z58" t="n">
         <v>970</v>
@@ -11711,7 +11711,7 @@
         <v>48</v>
       </c>
       <c r="AJ58" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK58" t="n">
         <v>46</v>
@@ -11723,16 +11723,16 @@
         <v>120</v>
       </c>
       <c r="AN58" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO58" t="n">
         <v>24</v>
       </c>
       <c r="AP58" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ58" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AR58" t="n">
         <v>11</v>
@@ -11753,38 +11753,38 @@
         <v>7</v>
       </c>
       <c r="AX58" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY58" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ58" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA58" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB58" t="n">
-        <v>3.95</v>
+        <v>2.84</v>
       </c>
       <c r="BC58" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD58" t="n">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="BE58" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="BF58" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG58" t="n">
         <v>17</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -11815,170 +11815,170 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G59" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H59" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ59" t="n">
         <v>3.55</v>
       </c>
-      <c r="I59" t="n">
+      <c r="AR59" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD59" t="n">
         <v>4.2</v>
       </c>
-      <c r="J59" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K59" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N59" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S59" t="n">
-        <v>4</v>
-      </c>
-      <c r="T59" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD59" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE59" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -12012,88 +12012,88 @@
         <v>2.96</v>
       </c>
       <c r="G60" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H60" t="n">
         <v>2.66</v>
       </c>
       <c r="I60" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="J60" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K60" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L60" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M60" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N60" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O60" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="P60" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="R60" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S60" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="T60" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="U60" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="V60" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W60" t="n">
         <v>1.47</v>
       </c>
       <c r="X60" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="Y60" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA60" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AB60" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC60" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AD60" t="n">
         <v>13</v>
       </c>
       <c r="AE60" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG60" t="n">
         <v>14</v>
       </c>
       <c r="AH60" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI60" t="n">
         <v>46</v>
@@ -12102,34 +12102,34 @@
         <v>55</v>
       </c>
       <c r="AK60" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL60" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM60" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AN60" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AO60" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AP60" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT60" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AQ60" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>9.6</v>
       </c>
       <c r="AU60" t="n">
         <v>6.8</v>
@@ -12138,41 +12138,41 @@
         <v>10.5</v>
       </c>
       <c r="AW60" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="AX60" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY60" t="n">
         <v>11</v>
       </c>
       <c r="AZ60" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BA60" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="BB60" t="n">
-        <v>40</v>
+        <v>5.9</v>
       </c>
       <c r="BC60" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="BD60" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BE60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BF60" t="n">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="BG60" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66</v>
+        <v>1.16</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="I2" t="n">
+        <v>44</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>380</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>7.2</v>
       </c>
-      <c r="J2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="AK2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>130</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>160</v>
+      </c>
+      <c r="BF2" t="n">
         <v>4.5</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="X2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>6</v>
-      </c>
       <c r="BG2" t="n">
-        <v>7.4</v>
+        <v>260</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -951,88 +951,88 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="G3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="H3" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="I3" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="T3" t="n">
         <v>1.92</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="X3" t="n">
         <v>28</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG3" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>42</v>
@@ -1041,10 +1041,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK3" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
         <v>40</v>
@@ -1053,37 +1053,37 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="AS3" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW3" t="n">
         <v>10</v>
       </c>
-      <c r="AV3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AX3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
         <v>8.800000000000001</v>
@@ -1092,29 +1092,29 @@
         <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.8</v>
+        <v>55</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="G4" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="I4" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K4" t="n">
         <v>5.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="T4" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AE4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI4" t="n">
         <v>110</v>
       </c>
-      <c r="AF4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>95</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
         <v>140</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>5.7</v>
       </c>
       <c r="AO4" t="n">
         <v>130</v>
       </c>
       <c r="AP4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.5</v>
+        <v>24</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="BB4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>26</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -1345,10 +1345,10 @@
         <v>2.54</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J5" t="n">
         <v>3.1</v>
@@ -1357,46 +1357,46 @@
         <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P5" t="n">
         <v>1.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z5" t="n">
         <v>22</v>
@@ -1408,22 +1408,22 @@
         <v>7.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
         <v>980</v>
@@ -1432,25 +1432,25 @@
         <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AN5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AO5" t="n">
         <v>85</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
         <v>20</v>
@@ -1468,41 +1468,41 @@
         <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BB5" t="n">
         <v>32</v>
       </c>
       <c r="BC5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD5" t="n">
         <v>50</v>
       </c>
       <c r="BE5" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BF5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG5" t="n">
         <v>60</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -1533,37 +1533,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
         <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
         <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
         <v>2</v>
@@ -1572,19 +1572,19 @@
         <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1617,7 +1617,7 @@
         <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1635,68 +1635,68 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H7" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J7" t="n">
         <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
         <v>1.52</v>
@@ -1751,16 +1751,16 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O7" t="n">
         <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
         <v>1.23</v>
@@ -1769,10 +1769,10 @@
         <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
         <v>1.54</v>
@@ -1793,7 +1793,7 @@
         <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>7.6</v>
@@ -1805,7 +1805,7 @@
         <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG7" t="n">
         <v>15.5</v>
@@ -1817,10 +1817,10 @@
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1838,7 +1838,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR7" t="n">
         <v>12.5</v>
@@ -1850,16 +1850,16 @@
         <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW7" t="n">
         <v>12</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AY7" t="n">
         <v>13</v>
@@ -1868,29 +1868,29 @@
         <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD7" t="n">
         <v>22</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7" t="n">
         <v>10.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -1921,85 +1921,85 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
         <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG8" t="n">
         <v>22</v>
@@ -2011,7 +2011,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK8" t="n">
         <v>1000</v>
@@ -2026,22 +2026,22 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
         <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
         <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
@@ -2053,38 +2053,38 @@
         <v>22</v>
       </c>
       <c r="AX8" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
         <v>4.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
         <v>3.45</v>
@@ -2139,40 +2139,40 @@
         <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
         <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
         <v>1.78</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
         <v>34</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC9" t="n">
         <v>7.6</v>
@@ -2190,25 +2190,25 @@
         <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>110</v>
       </c>
       <c r="AJ9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
         <v>60</v>
@@ -2223,7 +2223,7 @@
         <v>180</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>10</v>
@@ -2232,25 +2232,25 @@
         <v>19.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
         <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
@@ -2268,17 +2268,17 @@
         <v>46</v>
       </c>
       <c r="BE9" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF9" t="n">
         <v>12.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>1.46</v>
@@ -2333,40 +2333,40 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P10" t="n">
         <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
         <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
@@ -2375,10 +2375,10 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2390,7 +2390,7 @@
         <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
         <v>1000</v>
@@ -2423,56 +2423,56 @@
         <v>12.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AU10" t="n">
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G11" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
         <v>3.45</v>
@@ -2536,34 +2536,34 @@
         <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2575,13 +2575,13 @@
         <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
@@ -2593,10 +2593,10 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AK11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL11" t="n">
         <v>44</v>
@@ -2605,7 +2605,7 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
@@ -2617,13 +2617,13 @@
         <v>12.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU11" t="n">
         <v>7</v>
@@ -2632,41 +2632,41 @@
         <v>15.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC11" t="n">
         <v>18.5</v>
       </c>
-      <c r="BC11" t="n">
-        <v>16</v>
-      </c>
       <c r="BD11" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF11" t="n">
         <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.48</v>
@@ -2721,70 +2721,70 @@
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P12" t="n">
         <v>1.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
         <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
         <v>1.93</v>
       </c>
       <c r="V12" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X12" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z12" t="n">
         <v>12</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
         <v>21</v>
       </c>
-      <c r="AC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>20</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR12" t="n">
         <v>10.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY12" t="n">
         <v>16</v>
       </c>
-      <c r="AX12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.4</v>
+        <v>50</v>
       </c>
       <c r="BE12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BG12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I13" t="n">
         <v>1.61</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
         <v>4.4</v>
@@ -2915,34 +2915,34 @@
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>1.38</v>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
         <v>2.18</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="V13" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2951,7 +2951,7 @@
         <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AQ13" t="n">
         <v>4.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J14" t="n">
         <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.38</v>
@@ -3112,19 +3112,19 @@
         <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -3285,49 +3285,49 @@
         <v>1.24</v>
       </c>
       <c r="H15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
         <v>6.4</v>
       </c>
       <c r="K15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.98</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
         <v>5.1</v>
@@ -3339,31 +3339,31 @@
         <v>65</v>
       </c>
       <c r="Z15" t="n">
-        <v>450</v>
+        <v>390</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
         <v>6.2</v>
       </c>
-      <c r="AC15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>160</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AG15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
@@ -3372,7 +3372,7 @@
         <v>8</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>110</v>
@@ -3390,59 +3390,59 @@
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW15" t="n">
         <v>8</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB15" t="n">
         <v>6.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF15" t="n">
         <v>5.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H16" t="n">
         <v>5.1</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K16" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.31</v>
@@ -3497,34 +3497,34 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>1.11</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
         <v>1.64</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U16" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3581,16 +3581,16 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.3</v>
+        <v>2.56</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="AT16" t="n">
         <v>3.7</v>
@@ -3599,44 +3599,44 @@
         <v>3.9</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AW16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC16" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA16" t="n">
+      <c r="BD16" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BE16" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -3670,13 +3670,13 @@
         <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H17" t="n">
         <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
@@ -3691,13 +3691,13 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
         <v>1.77</v>
@@ -3706,22 +3706,22 @@
         <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
         <v>2.94</v>
       </c>
       <c r="X17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="n">
         <v>26</v>
@@ -3748,10 +3748,10 @@
         <v>10.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -3763,7 +3763,7 @@
         <v>19</v>
       </c>
       <c r="AL17" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -3775,16 +3775,16 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT17" t="n">
         <v>8</v>
@@ -3796,7 +3796,7 @@
         <v>17.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX17" t="n">
         <v>8.6</v>
@@ -3805,10 +3805,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>21</v>
+        <v>5.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
@@ -3820,17 +3820,17 @@
         <v>16</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF17" t="n">
         <v>7.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -3861,64 +3861,64 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="G18" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="H18" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
         <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="U18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="X18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3927,10 +3927,10 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3939,10 +3939,10 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
         <v>15</v>
@@ -3954,7 +3954,7 @@
         <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT18" t="n">
         <v>11.5</v>
       </c>
       <c r="AU18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF18" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG18" t="n">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         <v>1.65</v>
       </c>
       <c r="G19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H19" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
         <v>8.199999999999999</v>
@@ -4091,10 +4091,10 @@
         <v>2.46</v>
       </c>
       <c r="R19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
         <v>2.3</v>
@@ -4106,7 +4106,7 @@
         <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.58</v>
       </c>
       <c r="G20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H20" t="n">
         <v>3.1</v>
@@ -4267,7 +4267,7 @@
         <v>3.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
@@ -4279,28 +4279,28 @@
         <v>1.42</v>
       </c>
       <c r="P20" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
         <v>2.26</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
         <v>4.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V20" t="n">
         <v>1.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X20" t="n">
         <v>12</v>
@@ -4315,25 +4315,25 @@
         <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD20" t="n">
         <v>13.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF20" t="n">
         <v>15.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI20" t="n">
         <v>55</v>
@@ -4357,10 +4357,10 @@
         <v>42</v>
       </c>
       <c r="AP20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>18.5</v>
@@ -4390,7 +4390,7 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB20" t="n">
         <v>34</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -4446,167 +4446,167 @@
         <v>1.78</v>
       </c>
       <c r="G21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U21" t="n">
         <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X21" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z21" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG21" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA21" t="n">
         <v>15</v>
       </c>
-      <c r="AR21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ21" t="n">
+      <c r="BB21" t="n">
         <v>17</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>15.5</v>
       </c>
       <c r="BC21" t="n">
         <v>15</v>
       </c>
       <c r="BD21" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BE21" t="n">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG21" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -4643,13 +4643,13 @@
         <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I22" t="n">
         <v>2.44</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K22" t="n">
         <v>3.8</v>
@@ -4664,22 +4664,22 @@
         <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
         <v>1.77</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
         <v>3.85</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
@@ -4742,19 +4742,19 @@
         <v>60</v>
       </c>
       <c r="AO22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP22" t="n">
         <v>4.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR22" t="n">
         <v>4.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT22" t="n">
         <v>4.3</v>
@@ -4763,10 +4763,10 @@
         <v>3.7</v>
       </c>
       <c r="AV22" t="n">
-        <v>4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW22" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
         <v>5.1</v>
@@ -4778,7 +4778,7 @@
         <v>4.8</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB22" t="n">
         <v>5.7</v>
@@ -4796,11 +4796,11 @@
         <v>5.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="G23" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="H23" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="I23" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
         <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
         <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
         <v>3.75</v>
       </c>
       <c r="T23" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y23" t="n">
         <v>14.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA23" t="n">
         <v>85</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE23" t="n">
         <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ23" t="n">
         <v>34</v>
       </c>
       <c r="AK23" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL23" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AO23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AU23" t="n">
         <v>6.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.6</v>
+        <v>40</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BB23" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.5</v>
+        <v>29</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.5</v>
+        <v>42</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -5028,22 +5028,22 @@
         <v>2.2</v>
       </c>
       <c r="G24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
         <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M24" t="n">
         <v>1.1</v>
@@ -5052,13 +5052,13 @@
         <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
@@ -5067,22 +5067,22 @@
         <v>4.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U24" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
         <v>1.74</v>
       </c>
       <c r="X24" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y24" t="n">
-        <v>970</v>
+        <v>220</v>
       </c>
       <c r="Z24" t="n">
         <v>42</v>
@@ -5094,7 +5094,7 @@
         <v>8.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD24" t="n">
         <v>970</v>
@@ -5106,43 +5106,43 @@
         <v>970</v>
       </c>
       <c r="AG24" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI24" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AJ24" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AK24" t="n">
         <v>46</v>
       </c>
       <c r="AL24" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AM24" t="n">
         <v>160</v>
       </c>
       <c r="AN24" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AO24" t="n">
         <v>75</v>
       </c>
       <c r="AP24" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR24" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT24" t="n">
         <v>7.2</v>
@@ -5151,44 +5151,44 @@
         <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AY24" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD24" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BE24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF24" t="n">
         <v>8</v>
       </c>
-      <c r="BC24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG24" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -5219,73 +5219,73 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="G25" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="H25" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J25" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
         <v>3.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
         <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q25" t="n">
         <v>2.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U25" t="n">
         <v>1.98</v>
       </c>
       <c r="V25" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="X25" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="Y25" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AA25" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC25" t="n">
         <v>9</v>
@@ -5294,95 +5294,95 @@
         <v>17.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AF25" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ25" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK25" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL25" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AM25" t="n">
         <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AO25" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AS25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC25" t="n">
         <v>21</v>
       </c>
-      <c r="AT25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU25" t="n">
+      <c r="BD25" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE25" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF25" t="n">
         <v>6</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G26" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H26" t="n">
         <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K26" t="n">
         <v>3.3</v>
@@ -5443,10 +5443,10 @@
         <v>1.5</v>
       </c>
       <c r="P26" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R26" t="n">
         <v>1.21</v>
@@ -5455,19 +5455,19 @@
         <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U26" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V26" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W26" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X26" t="n">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="Y26" t="n">
         <v>970</v>
@@ -5497,7 +5497,7 @@
         <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI26" t="n">
         <v>100</v>
@@ -5506,7 +5506,7 @@
         <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL26" t="n">
         <v>65</v>
@@ -5515,68 +5515,68 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO26" t="n">
         <v>120</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AX26" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.98</v>
+        <v>18.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="BB26" t="n">
-        <v>17.5</v>
+        <v>2.02</v>
       </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>3.5</v>
       </c>
       <c r="BD26" t="n">
         <v>2.92</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="BF26" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -5610,19 +5610,19 @@
         <v>2.68</v>
       </c>
       <c r="G27" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H27" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J27" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L27" t="n">
         <v>1.57</v>
@@ -5631,49 +5631,49 @@
         <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O27" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P27" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="R27" t="n">
         <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
         <v>1.79</v>
       </c>
       <c r="V27" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W27" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC27" t="n">
         <v>7.4</v>
@@ -5682,7 +5682,7 @@
         <v>14.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF27" t="n">
         <v>17.5</v>
@@ -5694,7 +5694,7 @@
         <v>23</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="n">
         <v>50</v>
@@ -5712,19 +5712,19 @@
         <v>48</v>
       </c>
       <c r="AO27" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AP27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ27" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AR27" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AT27" t="n">
         <v>7.4</v>
@@ -5733,10 +5733,10 @@
         <v>6.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX27" t="n">
         <v>14.5</v>
@@ -5745,32 +5745,32 @@
         <v>11</v>
       </c>
       <c r="AZ27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB27" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BC27" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF27" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG27" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -5801,49 +5801,49 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="H28" t="n">
         <v>3.3</v>
       </c>
       <c r="I28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.7</v>
       </c>
-      <c r="J28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U28" t="n">
         <v>2.06</v>
@@ -5852,119 +5852,119 @@
         <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="X28" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="Y28" t="n">
         <v>970</v>
       </c>
       <c r="Z28" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA28" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF28" t="n">
         <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
         <v>970</v>
       </c>
       <c r="AI28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ28" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL28" t="n">
         <v>42</v>
       </c>
       <c r="AM28" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN28" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB28" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA28" t="n">
+      <c r="BC28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE28" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB28" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF28" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
         <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L29" t="n">
         <v>1.56</v>
@@ -6046,7 +6046,7 @@
         <v>1.37</v>
       </c>
       <c r="W29" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X29" t="n">
         <v>9.6</v>
@@ -6055,7 +6055,7 @@
         <v>18.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AA29" t="n">
         <v>80</v>
@@ -6079,37 +6079,37 @@
         <v>970</v>
       </c>
       <c r="AH29" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI29" t="n">
         <v>80</v>
       </c>
       <c r="AJ29" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AK29" t="n">
         <v>55</v>
       </c>
       <c r="AL29" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AM29" t="n">
         <v>210</v>
       </c>
       <c r="AN29" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AO29" t="n">
         <v>85</v>
       </c>
       <c r="AP29" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ29" t="n">
         <v>5.1</v>
       </c>
       <c r="AR29" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS29" t="n">
         <v>9</v>
@@ -6133,13 +6133,13 @@
         <v>5.8</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="BA29" t="n">
         <v>5.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC29" t="n">
         <v>5.3</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -6198,31 +6198,31 @@
         <v>2.82</v>
       </c>
       <c r="I30" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="J30" t="n">
         <v>3.45</v>
       </c>
       <c r="K30" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
         <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R30" t="n">
         <v>1.36</v>
@@ -6231,13 +6231,13 @@
         <v>3.65</v>
       </c>
       <c r="T30" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U30" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V30" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W30" t="n">
         <v>1.56</v>
@@ -6246,19 +6246,19 @@
         <v>13.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="n">
         <v>44</v>
       </c>
       <c r="AB30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
         <v>12.5</v>
@@ -6267,7 +6267,7 @@
         <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG30" t="n">
         <v>12</v>
@@ -6279,13 +6279,13 @@
         <v>44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK30" t="n">
         <v>30</v>
       </c>
       <c r="AL30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM30" t="n">
         <v>90</v>
@@ -6306,19 +6306,19 @@
         <v>17</v>
       </c>
       <c r="AS30" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT30" t="n">
         <v>10.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV30" t="n">
         <v>11.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AX30" t="n">
         <v>16.5</v>
@@ -6327,7 +6327,7 @@
         <v>11</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA30" t="n">
         <v>36</v>
@@ -6336,23 +6336,23 @@
         <v>34</v>
       </c>
       <c r="BC30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD30" t="n">
         <v>38</v>
       </c>
       <c r="BE30" t="n">
-        <v>16.5</v>
+        <v>70</v>
       </c>
       <c r="BF30" t="n">
         <v>24</v>
       </c>
       <c r="BG30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="G31" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="H31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.35</v>
-      </c>
-      <c r="I31" t="n">
-        <v>4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.3</v>
       </c>
       <c r="L31" t="n">
         <v>1.62</v>
@@ -6407,64 +6407,64 @@
         <v>1.13</v>
       </c>
       <c r="N31" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O31" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P31" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="R31" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S31" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="U31" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="W31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="X31" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA31" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC31" t="n">
         <v>7.6</v>
       </c>
       <c r="AD31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF31" t="n">
         <v>19.5</v>
       </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
+      <c r="AG31" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>14</v>
       </c>
       <c r="AH31" t="n">
         <v>27</v>
@@ -6473,10 +6473,10 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AK31" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AL31" t="n">
         <v>80</v>
@@ -6485,34 +6485,34 @@
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AO31" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS31" t="n">
         <v>6</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS31" t="n">
+      <c r="AT31" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT31" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AU31" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX31" t="n">
         <v>11</v>
@@ -6521,32 +6521,32 @@
         <v>4.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB31" t="n">
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF31" t="n">
         <v>6</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G32" t="n">
         <v>2.38</v>
@@ -6589,7 +6589,7 @@
         <v>4.8</v>
       </c>
       <c r="J32" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K32" t="n">
         <v>3.25</v>
@@ -6625,7 +6625,7 @@
         <v>1.62</v>
       </c>
       <c r="V32" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W32" t="n">
         <v>1.72</v>
@@ -6649,7 +6649,7 @@
         <v>970</v>
       </c>
       <c r="AD32" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
@@ -6661,7 +6661,7 @@
         <v>970</v>
       </c>
       <c r="AH32" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI32" t="n">
         <v>1000</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
         <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
         <v>1.27</v>
@@ -6998,7 +6998,7 @@
         <v>1.83</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R34" t="n">
         <v>1.38</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT34" t="n">
         <v>3.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AV34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB34" t="n">
         <v>3.95</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="BC34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE34" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX34" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD34" t="n">
+      <c r="BF34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG34" t="n">
         <v>4.3</v>
       </c>
-      <c r="BE34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -7159,19 +7159,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="G35" t="n">
-        <v>2.72</v>
+        <v>2.14</v>
       </c>
       <c r="H35" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="I35" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="J35" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K35" t="n">
         <v>3.35</v>
@@ -7189,10 +7189,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -7356,13 +7356,13 @@
         <v>1.78</v>
       </c>
       <c r="G36" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H36" t="n">
         <v>4.6</v>
       </c>
       <c r="I36" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
         <v>2.92</v>
@@ -7401,10 +7401,10 @@
         <v>1.58</v>
       </c>
       <c r="V36" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W36" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G37" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H37" t="n">
         <v>3.35</v>
@@ -7562,7 +7562,7 @@
         <v>2.64</v>
       </c>
       <c r="K37" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L37" t="n">
         <v>1.55</v>
@@ -7574,7 +7574,7 @@
         <v>2.1</v>
       </c>
       <c r="O37" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P37" t="n">
         <v>1.4</v>
@@ -7598,7 +7598,7 @@
         <v>1.31</v>
       </c>
       <c r="W37" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X37" t="n">
         <v>8.6</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AQ37" t="n">
         <v>3.15</v>
       </c>
       <c r="AR37" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AW37" t="n">
         <v>4.2</v>
       </c>
       <c r="AX37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY37" t="n">
         <v>3.5</v>
       </c>
-      <c r="AY37" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AZ37" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF37" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB37" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE37" t="n">
+      <c r="BG37" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -7753,10 +7753,10 @@
         <v>3.25</v>
       </c>
       <c r="J38" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="K38" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L38" t="n">
         <v>1.58</v>
@@ -7768,7 +7768,7 @@
         <v>2.66</v>
       </c>
       <c r="O38" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P38" t="n">
         <v>1.52</v>
@@ -7789,10 +7789,10 @@
         <v>1.8</v>
       </c>
       <c r="V38" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W38" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
         <v>90</v>
@@ -7807,7 +7807,7 @@
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC38" t="n">
         <v>1000</v>
@@ -7849,62 +7849,62 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ38" t="n">
         <v>7</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="AT38" t="n">
         <v>4.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>3.15</v>
+        <v>2.26</v>
       </c>
       <c r="AX38" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AY38" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ38" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="BB38" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="BC38" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="BE38" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BF38" t="n">
         <v>2.06</v>
       </c>
-      <c r="BF38" t="n">
-        <v>2</v>
-      </c>
       <c r="BG38" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -7941,13 +7941,13 @@
         <v>3.3</v>
       </c>
       <c r="H39" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I39" t="n">
         <v>2.9</v>
       </c>
       <c r="J39" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
         <v>3.25</v>
@@ -7965,7 +7965,7 @@
         <v>1.52</v>
       </c>
       <c r="P39" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q39" t="n">
         <v>2.6</v>
@@ -7986,7 +7986,7 @@
         <v>1.53</v>
       </c>
       <c r="W39" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X39" t="n">
         <v>10.5</v>
@@ -8040,19 +8040,19 @@
         <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP39" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ39" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR39" t="n">
         <v>14</v>
       </c>
       <c r="AS39" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="AT39" t="n">
         <v>7.8</v>
@@ -8073,32 +8073,32 @@
         <v>12</v>
       </c>
       <c r="AZ39" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="BB39" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC39" t="n">
         <v>38</v>
       </c>
       <c r="BD39" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG39" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BG39" t="n">
-        <v>8</v>
-      </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -8129,61 +8129,61 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G40" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="H40" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I40" t="n">
         <v>3.9</v>
       </c>
       <c r="J40" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K40" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="M40" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="P40" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="R40" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S40" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="U40" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="V40" t="n">
         <v>1.35</v>
       </c>
       <c r="W40" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X40" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y40" t="n">
         <v>1000</v>
@@ -8195,10 +8195,10 @@
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD40" t="n">
         <v>18.5</v>
@@ -8210,7 +8210,7 @@
         <v>1000</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH40" t="n">
         <v>1000</v>
@@ -8237,62 +8237,62 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="AQ40" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AR40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS40" t="n">
         <v>5.9</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AT40" t="n">
         <v>7</v>
       </c>
-      <c r="AT40" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AU40" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE40" t="n">
         <v>6</v>
       </c>
-      <c r="AV40" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF40" t="n">
-        <v>26</v>
+        <v>5.2</v>
       </c>
       <c r="BG40" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G41" t="n">
         <v>2.34</v>
@@ -8332,37 +8332,37 @@
         <v>4</v>
       </c>
       <c r="I41" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J41" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K41" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L41" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
         <v>1.12</v>
       </c>
       <c r="N41" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="O41" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P41" t="n">
         <v>1.57</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R41" t="n">
         <v>1.2</v>
       </c>
       <c r="S41" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T41" t="n">
         <v>2.1</v>
@@ -8437,7 +8437,7 @@
         <v>9.6</v>
       </c>
       <c r="AR41" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS41" t="n">
         <v>5.7</v>
@@ -8458,7 +8458,7 @@
         <v>11.5</v>
       </c>
       <c r="AY41" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ41" t="n">
         <v>20</v>
@@ -8467,10 +8467,10 @@
         <v>5.7</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC41" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD41" t="n">
         <v>5.5</v>
@@ -8479,14 +8479,14 @@
         <v>5.8</v>
       </c>
       <c r="BF41" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="BG41" t="n">
         <v>5.7</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -8517,19 +8517,19 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="G42" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="H42" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I42" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J42" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K42" t="n">
         <v>4.8</v>
@@ -8541,22 +8541,22 @@
         <v>1.04</v>
       </c>
       <c r="N42" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O42" t="n">
         <v>1.2</v>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R42" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S42" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="T42" t="n">
         <v>1.74</v>
@@ -8565,40 +8565,40 @@
         <v>2.26</v>
       </c>
       <c r="V42" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W42" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="X42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y42" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Z42" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA42" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC42" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE42" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF42" t="n">
         <v>11</v>
       </c>
       <c r="AG42" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH42" t="n">
         <v>19.5</v>
@@ -8607,10 +8607,10 @@
         <v>70</v>
       </c>
       <c r="AJ42" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK42" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL42" t="n">
         <v>29</v>
@@ -8619,22 +8619,22 @@
         <v>90</v>
       </c>
       <c r="AN42" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AO42" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AP42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR42" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS42" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT42" t="n">
         <v>10</v>
@@ -8643,7 +8643,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW42" t="n">
         <v>65</v>
@@ -8661,7 +8661,7 @@
         <v>55</v>
       </c>
       <c r="BB42" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC42" t="n">
         <v>13.5</v>
@@ -8670,17 +8670,17 @@
         <v>25</v>
       </c>
       <c r="BE42" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="BF42" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BG42" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
         <v>1.26</v>
       </c>
       <c r="G43" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="H43" t="n">
         <v>9</v>
@@ -8723,7 +8723,7 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K43" t="n">
         <v>6.2</v>
@@ -8738,7 +8738,7 @@
         <v>2.88</v>
       </c>
       <c r="O43" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P43" t="n">
         <v>1.65</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -8929,16 +8929,16 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O44" t="n">
         <v>1.01</v>
       </c>
       <c r="P44" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="R44" t="n">
         <v>1.13</v>
@@ -8956,7 +8956,7 @@
         <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="G45" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="H45" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="J45" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K45" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L45" t="n">
         <v>1.67</v>
@@ -9129,7 +9129,7 @@
         <v>1.65</v>
       </c>
       <c r="P45" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q45" t="n">
         <v>3.05</v>
@@ -9144,19 +9144,19 @@
         <v>2.18</v>
       </c>
       <c r="U45" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="V45" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W45" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="X45" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z45" t="n">
         <v>1000</v>
@@ -9165,10 +9165,10 @@
         <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD45" t="n">
         <v>1000</v>
@@ -9210,59 +9210,59 @@
         <v>5.5</v>
       </c>
       <c r="AQ45" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT45" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>5.7</v>
       </c>
       <c r="AU45" t="n">
         <v>5.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX45" t="n">
-        <v>3.7</v>
+        <v>12.5</v>
       </c>
       <c r="AY45" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ45" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="BA45" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BB45" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BC45" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BF45" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BG45" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -9293,19 +9293,19 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.32</v>
+        <v>2.76</v>
       </c>
       <c r="G46" t="n">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="H46" t="n">
-        <v>3.7</v>
+        <v>2.86</v>
       </c>
       <c r="I46" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K46" t="n">
         <v>3</v>
@@ -9317,7 +9317,7 @@
         <v>1.13</v>
       </c>
       <c r="N46" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O46" t="n">
         <v>1.55</v>
@@ -9326,52 +9326,52 @@
         <v>1.48</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R46" t="n">
         <v>1.17</v>
       </c>
       <c r="S46" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T46" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U46" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V46" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="W46" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="X46" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AA46" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AB46" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC46" t="n">
         <v>7.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF46" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AG46" t="n">
         <v>15</v>
@@ -9380,83 +9380,83 @@
         <v>27</v>
       </c>
       <c r="AI46" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AJ46" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AK46" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AL46" t="n">
         <v>80</v>
       </c>
       <c r="AM46" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN46" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AO46" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AP46" t="n">
         <v>6</v>
       </c>
       <c r="AQ46" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AR46" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AS46" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT46" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>5.3</v>
       </c>
       <c r="AU46" t="n">
         <v>5.4</v>
       </c>
       <c r="AV46" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AW46" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AX46" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AY46" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ46" t="n">
         <v>17.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB46" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC46" t="n">
         <v>22</v>
       </c>
       <c r="BD46" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BE46" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF46" t="n">
         <v>23</v>
       </c>
       <c r="BG46" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -9487,101 +9487,101 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="G47" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H47" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I47" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K47" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L47" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="M47" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="O47" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="P47" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.74</v>
+        <v>2.36</v>
       </c>
       <c r="R47" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="S47" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="T47" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="V47" t="n">
         <v>1.24</v>
       </c>
       <c r="W47" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="X47" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="Y47" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Z47" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA47" t="n">
         <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD47" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE47" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF47" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG47" t="n">
         <v>12.5</v>
       </c>
       <c r="AH47" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK47" t="n">
         <v>28</v>
       </c>
-      <c r="AI47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>32</v>
-      </c>
       <c r="AL47" t="n">
         <v>1000</v>
       </c>
@@ -9589,68 +9589,68 @@
         <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AO47" t="n">
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ47" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR47" t="n">
-        <v>22</v>
+        <v>5.9</v>
       </c>
       <c r="AS47" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="AT47" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU47" t="n">
         <v>6.4</v>
       </c>
       <c r="AV47" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX47" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY47" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ47" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BA47" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB47" t="n">
         <v>19.5</v>
       </c>
       <c r="BC47" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BD47" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BF47" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BG47" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -9681,100 +9681,100 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="G48" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="H48" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="I48" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="K48" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="O48" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="P48" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="R48" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="S48" t="n">
-        <v>2.46</v>
+        <v>1.05</v>
       </c>
       <c r="T48" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U48" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="V48" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W48" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="X48" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y48" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z48" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA48" t="n">
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC48" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD48" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE48" t="n">
         <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI48" t="n">
         <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK48" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL48" t="n">
         <v>1000</v>
@@ -9783,68 +9783,68 @@
         <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO48" t="n">
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -9878,13 +9878,13 @@
         <v>2.42</v>
       </c>
       <c r="G49" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="H49" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>3.05</v>
@@ -9902,31 +9902,31 @@
         <v>3.35</v>
       </c>
       <c r="O49" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P49" t="n">
         <v>1.76</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R49" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S49" t="n">
         <v>3.95</v>
       </c>
       <c r="T49" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U49" t="n">
         <v>2.02</v>
       </c>
       <c r="V49" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W49" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="X49" t="n">
         <v>13</v>
@@ -9947,16 +9947,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD49" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE49" t="n">
         <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AG49" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH49" t="n">
         <v>21</v>
@@ -9989,56 +9989,56 @@
         <v>10</v>
       </c>
       <c r="AR49" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT49" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU49" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV49" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW49" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX49" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY49" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ49" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB49" t="n">
         <v>5.8</v>
       </c>
       <c r="BC49" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG49" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -10117,7 +10117,7 @@
         <v>2.08</v>
       </c>
       <c r="V50" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W50" t="n">
         <v>2.36</v>
@@ -10135,16 +10135,16 @@
         <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AE50" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF50" t="n">
         <v>970</v>
@@ -10153,7 +10153,7 @@
         <v>970</v>
       </c>
       <c r="AH50" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI50" t="n">
         <v>85</v>
@@ -10177,62 +10177,62 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="AQ50" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="AR50" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AS50" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AT50" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV50" t="n">
         <v>3.45</v>
       </c>
-      <c r="AU50" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AV50" t="n">
+      <c r="AW50" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BB50" t="n">
         <v>3.4</v>
       </c>
-      <c r="AW50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX50" t="n">
+      <c r="BC50" t="n">
         <v>3.45</v>
       </c>
-      <c r="AY50" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BD50" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BE50" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="BF50" t="n">
-        <v>2.86</v>
+        <v>3.8</v>
       </c>
       <c r="BG50" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -10263,61 +10263,61 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="G51" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="H51" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="I51" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="K51" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L51" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M51" t="n">
         <v>1.11</v>
       </c>
       <c r="N51" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O51" t="n">
         <v>1.47</v>
       </c>
       <c r="P51" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R51" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S51" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T51" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U51" t="n">
         <v>1.86</v>
       </c>
       <c r="V51" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W51" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="X51" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y51" t="n">
         <v>1000</v>
@@ -10371,62 +10371,62 @@
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT51" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ51" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AU51" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AV51" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AX51" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW51" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AY51" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="AZ51" t="n">
         <v>5</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.56</v>
+        <v>3.1</v>
       </c>
       <c r="BB51" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="BC51" t="n">
-        <v>5.1</v>
+        <v>2.96</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.1</v>
+        <v>2.96</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -10463,13 +10463,13 @@
         <v>2.78</v>
       </c>
       <c r="H52" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I52" t="n">
         <v>3.05</v>
       </c>
       <c r="J52" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K52" t="n">
         <v>3.45</v>
@@ -10481,22 +10481,22 @@
         <v>1.08</v>
       </c>
       <c r="N52" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O52" t="n">
         <v>1.37</v>
       </c>
       <c r="P52" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q52" t="n">
         <v>2.1</v>
       </c>
       <c r="R52" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S52" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T52" t="n">
         <v>1.78</v>
@@ -10511,13 +10511,13 @@
         <v>1.56</v>
       </c>
       <c r="X52" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y52" t="n">
         <v>12</v>
       </c>
       <c r="Z52" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA52" t="n">
         <v>55</v>
@@ -10559,10 +10559,10 @@
         <v>120</v>
       </c>
       <c r="AN52" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO52" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP52" t="n">
         <v>10.5</v>
@@ -10571,7 +10571,7 @@
         <v>9.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS52" t="n">
         <v>8.199999999999999</v>
@@ -10601,7 +10601,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB52" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BC52" t="n">
         <v>16</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -10651,16 +10651,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G53" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H53" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I53" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
         <v>3.2</v>
@@ -10675,19 +10675,19 @@
         <v>1.1</v>
       </c>
       <c r="N53" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O53" t="n">
         <v>1.42</v>
       </c>
       <c r="P53" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q53" t="n">
         <v>2.3</v>
       </c>
       <c r="R53" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S53" t="n">
         <v>4.4</v>
@@ -10699,13 +10699,13 @@
         <v>1.91</v>
       </c>
       <c r="V53" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W53" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X53" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y53" t="n">
         <v>13.5</v>
@@ -10744,10 +10744,10 @@
         <v>1000</v>
       </c>
       <c r="AK53" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL53" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM53" t="n">
         <v>1000</v>
@@ -10759,25 +10759,25 @@
         <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ53" t="n">
         <v>10.5</v>
       </c>
       <c r="AR53" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AS53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT53" t="n">
         <v>7</v>
       </c>
       <c r="AU53" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW53" t="n">
         <v>48</v>
@@ -10792,29 +10792,29 @@
         <v>17</v>
       </c>
       <c r="BA53" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD53" t="n">
         <v>6</v>
       </c>
-      <c r="BB53" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BE53" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF53" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG53" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -10845,170 +10845,170 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G54" t="n">
         <v>1.72</v>
       </c>
       <c r="H54" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I54" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J54" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K54" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L54" t="n">
         <v>1.49</v>
       </c>
       <c r="M54" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N54" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O54" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P54" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R54" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S54" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T54" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="U54" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V54" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W54" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z54" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA54" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AB54" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD54" t="n">
         <v>6.8</v>
       </c>
-      <c r="AC54" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>280</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BE54" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF54" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BG54" t="n">
-        <v>2.72</v>
+        <v>7.8</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -11039,10 +11039,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G55" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H55" t="n">
         <v>4.1</v>
@@ -11051,13 +11051,13 @@
         <v>4.2</v>
       </c>
       <c r="J55" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K55" t="n">
         <v>3.4</v>
       </c>
-      <c r="K55" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L55" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M55" t="n">
         <v>1.09</v>
@@ -11069,10 +11069,10 @@
         <v>1.41</v>
       </c>
       <c r="P55" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R55" t="n">
         <v>1.29</v>
@@ -11081,16 +11081,16 @@
         <v>4.2</v>
       </c>
       <c r="T55" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U55" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V55" t="n">
         <v>1.31</v>
       </c>
       <c r="W55" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X55" t="n">
         <v>11.5</v>
@@ -11117,7 +11117,7 @@
         <v>55</v>
       </c>
       <c r="AF55" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG55" t="n">
         <v>10.5</v>
@@ -11132,7 +11132,7 @@
         <v>27</v>
       </c>
       <c r="AK55" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL55" t="n">
         <v>46</v>
@@ -11156,7 +11156,7 @@
         <v>25</v>
       </c>
       <c r="AS55" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AT55" t="n">
         <v>7.8</v>
@@ -11171,38 +11171,38 @@
         <v>48</v>
       </c>
       <c r="AX55" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY55" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ55" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA55" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BB55" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC55" t="n">
         <v>22</v>
       </c>
       <c r="BD55" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE55" t="n">
         <v>65</v>
       </c>
       <c r="BF55" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG55" t="n">
         <v>50</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -11236,19 +11236,19 @@
         <v>3.45</v>
       </c>
       <c r="G56" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H56" t="n">
         <v>2.34</v>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="J56" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K56" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L56" t="n">
         <v>1.44</v>
@@ -11263,7 +11263,7 @@
         <v>1.36</v>
       </c>
       <c r="P56" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q56" t="n">
         <v>2.1</v>
@@ -11281,10 +11281,10 @@
         <v>2.08</v>
       </c>
       <c r="V56" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W56" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X56" t="n">
         <v>970</v>
@@ -11371,7 +11371,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ56" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BA56" t="n">
         <v>7.8</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -11445,13 +11445,13 @@
         <v>3.65</v>
       </c>
       <c r="L57" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M57" t="n">
         <v>1.09</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O57" t="n">
         <v>1.4</v>
@@ -11460,10 +11460,10 @@
         <v>1.75</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R57" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S57" t="n">
         <v>4.1</v>
@@ -11481,7 +11481,7 @@
         <v>1.79</v>
       </c>
       <c r="X57" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y57" t="n">
         <v>1000</v>
@@ -11577,7 +11577,7 @@
         <v>4</v>
       </c>
       <c r="BD57" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE57" t="n">
         <v>4.5</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
         <v>2.96</v>
       </c>
       <c r="G58" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H58" t="n">
         <v>2.66</v>
@@ -11645,22 +11645,22 @@
         <v>1.07</v>
       </c>
       <c r="N58" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O58" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P58" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R58" t="n">
         <v>1.41</v>
       </c>
       <c r="S58" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T58" t="n">
         <v>1.67</v>
@@ -11672,7 +11672,7 @@
         <v>1.57</v>
       </c>
       <c r="W58" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X58" t="n">
         <v>18</v>
@@ -11696,7 +11696,7 @@
         <v>13</v>
       </c>
       <c r="AE58" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF58" t="n">
         <v>22</v>
@@ -11765,7 +11765,7 @@
         <v>6.4</v>
       </c>
       <c r="BB58" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC58" t="n">
         <v>6.2</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,66 +743,66 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CA Bartolome Mitre</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Boca Unidos</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M2" t="n">
         <v>1.01</v>
       </c>
-      <c r="G2" t="n">
-        <v>950</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="N2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.01</v>
       </c>
-      <c r="I2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1.01</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>15</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="S2" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -811,37 +811,37 @@
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -859,75 +859,75 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="AR2" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="AS2" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,114 +937,114 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>San Antonio FC</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.39</v>
+        <v>5.3</v>
       </c>
       <c r="G3" t="n">
-        <v>1.48</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="I3" t="n">
-        <v>55</v>
+        <v>6.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>1.53</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>1.55</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N3" t="n">
-        <v>2.22</v>
+        <v>1.07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.76</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.4</v>
+        <v>110</v>
       </c>
       <c r="R3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>11.5</v>
+        <v>290</v>
       </c>
       <c r="T3" t="n">
-        <v>2.46</v>
+        <v>16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.56</v>
+        <v>1.05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>1.61</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.38</v>
+        <v>6.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.9</v>
+        <v>32</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>330</v>
       </c>
       <c r="AE3" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>7.2</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>360</v>
       </c>
       <c r="AH3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1053,75 +1053,75 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1000</v>
+        <v>1.57</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AS3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.18</v>
+        <v>5.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.6</v>
+        <v>170</v>
       </c>
       <c r="AW3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="AY3" t="n">
-        <v>12.5</v>
+        <v>170</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.199999999999999</v>
+        <v>340</v>
       </c>
       <c r="BC3" t="n">
-        <v>11</v>
+        <v>360</v>
       </c>
       <c r="BD3" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BF3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.18</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.19</v>
+        <v>5.3</v>
       </c>
       <c r="H4" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>27</v>
+        <v>2.06</v>
       </c>
       <c r="J4" t="n">
-        <v>8.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1169,153 +1169,153 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.45</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>5.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="V4" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="W4" t="n">
-        <v>6</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>55</v>
+        <v>9.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="n">
-        <v>170</v>
+        <v>380</v>
       </c>
       <c r="AN4" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="AO4" t="n">
-        <v>340</v>
+        <v>140</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AU4" t="n">
-        <v>13</v>
+        <v>3.8</v>
       </c>
       <c r="AV4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW4" t="n">
         <v>40</v>
       </c>
-      <c r="AW4" t="n">
-        <v>150</v>
-      </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BC4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="BD4" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="BE4" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.4</v>
+        <v>50</v>
       </c>
       <c r="BG4" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:31:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.26</v>
+        <v>1.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.62</v>
+        <v>1.39</v>
       </c>
       <c r="H5" t="n">
-        <v>3.45</v>
+        <v>14.5</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.86</v>
+        <v>4.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.14</v>
+        <v>3.75</v>
       </c>
       <c r="S5" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>3.9</v>
       </c>
       <c r="AH5" t="n">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
         <v>75</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="AV5" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.28</v>
+        <v>1000</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.58</v>
+        <v>19</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.58</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.68</v>
+        <v>25</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.36</v>
+        <v>7.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.42</v>
+        <v>60</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Atletico Nacional Medellin</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G6" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.82</v>
+        <v>2.36</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Y6" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG6" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AH6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY6" t="n">
         <v>11</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
+      <c r="AZ6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG6" t="n">
         <v>42</v>
       </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Club Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.28</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.3</v>
-      </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
         <v>1.76</v>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>550</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.4</v>
+        <v>990</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>990</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>990</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>1.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>23</v>
+        <v>1.25</v>
       </c>
       <c r="AS7" t="n">
-        <v>60</v>
+        <v>1.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>1.17</v>
       </c>
       <c r="AV7" t="n">
-        <v>14.5</v>
+        <v>1.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>40</v>
+        <v>1.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>12</v>
+        <v>1.19</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>1.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>55</v>
+        <v>1.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>26</v>
+        <v>1.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>1.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>34</v>
+        <v>1.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>90</v>
+        <v>1.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>21</v>
+        <v>1.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>50</v>
+        <v>1.3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Greenville Triumph SC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Westchester SC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.78</v>
+        <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82</v>
+        <v>1.33</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>1.47</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>4.4</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>21</v>
-      </c>
       <c r="BA8" t="n">
-        <v>40</v>
+        <v>5.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>17</v>
+        <v>3.85</v>
       </c>
       <c r="BC8" t="n">
-        <v>18.5</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>44</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>65</v>
+        <v>5.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>14</v>
+        <v>5.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>70</v>
+        <v>5.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,960 +2101,184 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:31:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>2.36</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>2.42</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.41</v>
       </c>
-      <c r="P9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="X9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>17</v>
-      </c>
       <c r="AE9" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
         <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="AN9" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>18.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BD9" t="n">
         <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="BF9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BG9" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>20:20:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Deportivo Pasto</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Atletico Nacional Medellin</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>46</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2026-03-29 18:33:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>San Luis</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Club Deportes Santa Cruz</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X11" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2026-03-29 18:33:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Greenville Triumph SC</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Westchester SC</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="H12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X12" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2026-03-29 18:33:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Llaneros FC</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Once Caldas</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
